--- a/editorial/NTK_Backstory_Candidates.xlsx
+++ b/editorial/NTK_Backstory_Candidates.xlsx
@@ -7,6 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Candidates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lens candidates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Lenses" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -15,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <color indexed="8"/>
@@ -36,6 +38,9 @@
       <b val="1"/>
       <color indexed="8"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -176,7 +181,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -235,6 +240,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2973,4 +2979,3015 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" style="17" min="1" max="1"/>
+    <col width="8" customWidth="1" style="17" min="2" max="2"/>
+    <col width="6" customWidth="1" style="17" min="3" max="3"/>
+    <col width="12" customWidth="1" style="17" min="4" max="4"/>
+    <col width="11" customWidth="1" style="17" min="5" max="5"/>
+    <col width="34" customWidth="1" style="17" min="6" max="6"/>
+    <col width="54" customWidth="1" style="17" min="7" max="7"/>
+    <col width="34" customWidth="1" style="17" min="8" max="8"/>
+    <col width="6" customWidth="1" style="17" min="9" max="9"/>
+    <col width="6" customWidth="1" style="17" min="10" max="10"/>
+    <col width="40" customWidth="1" style="17" min="11" max="11"/>
+    <col width="14" customWidth="1" style="17" min="12" max="12"/>
+    <col width="24" customWidth="1" style="17" min="13" max="13"/>
+    <col width="18" customWidth="1" style="17" min="14" max="14"/>
+    <col width="11" customWidth="1" style="17" min="15" max="15"/>
+    <col width="12" customWidth="1" style="17" min="16" max="16"/>
+    <col width="60" customWidth="1" style="17" min="17" max="17"/>
+    <col width="60" customWidth="1" style="17" min="18" max="18"/>
+    <col width="9" customWidth="1" style="17" min="19" max="19"/>
+    <col width="60" customWidth="1" style="17" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Decade</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Day / Month</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>Sort Date</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Issue (Theme)</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>Pg. No.</t>
+        </is>
+      </c>
+      <c r="J1" s="20" t="inlineStr">
+        <is>
+          <t>Vol.</t>
+        </is>
+      </c>
+      <c r="K1" s="20" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="L1" s="20" t="inlineStr">
+        <is>
+          <t>NTK Row</t>
+        </is>
+      </c>
+      <c r="M1" s="20" t="inlineStr">
+        <is>
+          <t>Sub-genre</t>
+        </is>
+      </c>
+      <c r="N1" s="20" t="inlineStr">
+        <is>
+          <t>Era</t>
+        </is>
+      </c>
+      <c r="O1" s="20" t="inlineStr">
+        <is>
+          <t>Date Status</t>
+        </is>
+      </c>
+      <c r="P1" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Q1" s="20" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="R1" s="20" t="inlineStr">
+        <is>
+          <t>Why it's here</t>
+        </is>
+      </c>
+      <c r="S1" s="20" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="T1" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n">
+        <v>1910</v>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>2 November</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>1917-11-02</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>Balfour Declaration</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="inlineStr">
+        <is>
+          <t>Arthur James Balfour</t>
+        </is>
+      </c>
+      <c r="I2" s="18" t="n"/>
+      <c r="J2" s="18" t="n"/>
+      <c r="K2" s="18" t="inlineStr">
+        <is>
+          <t>Letter to Lord Rothschild, British Foreign Office (Avalon Project, Yale)</t>
+        </is>
+      </c>
+      <c r="L2" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M2" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N2" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O2" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P2" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q2" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/balfour.asp</t>
+        </is>
+      </c>
+      <c r="R2" s="18" t="inlineStr">
+        <is>
+          <t>Britain's statement of support for a Jewish national home in Palestine; the earliest document most later ones answer.</t>
+        </is>
+      </c>
+      <c r="S2" s="18" t="n"/>
+      <c r="T2" s="18" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>29 November</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>1947-11-29</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>UN General Assembly Resolution 181 (II): Future Government of Palestine (the Partition Plan)</t>
+        </is>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
+        <is>
+          <t>United Nations General Assembly</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="18" t="n"/>
+      <c r="K3" s="18" t="inlineStr">
+        <is>
+          <t>UN Information System on the Question of Palestine (UNISPAL)</t>
+        </is>
+      </c>
+      <c r="L3" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N3" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O3" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P3" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q3" s="18" t="inlineStr">
+        <is>
+          <t>https://www.un.org/unispal/document/auto-insert-185393/</t>
+        </is>
+      </c>
+      <c r="R3" s="18" t="inlineStr">
+        <is>
+          <t>The UN vote to divide Palestine into a Jewish and an Arab state; the legal starting point for both sides' claims.</t>
+        </is>
+      </c>
+      <c r="S3" s="18" t="n"/>
+      <c r="T3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>14 May</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>1948-05-14</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>Declaration of the Establishment of the State of Israel</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Provisional Council of State (David Ben-Gurion)</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="18" t="n"/>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M4" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O4" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P4" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q4" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/israel.asp</t>
+        </is>
+      </c>
+      <c r="R4" s="18" t="inlineStr">
+        <is>
+          <t>Israel's founding statement, issued the day the British Mandate ended.</t>
+        </is>
+      </c>
+      <c r="S4" s="18" t="n"/>
+      <c r="T4" s="18" t="inlineStr">
+        <is>
+          <t>The Knesset's own page was down during the check, so this links Avalon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>22 November</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>1967-11-22</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 242</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="n"/>
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O5" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P5" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q5" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/un242.asp</t>
+        </is>
+      </c>
+      <c r="R5" s="18" t="inlineStr">
+        <is>
+          <t>The land-for-peace resolution after the Six-Day War; cited in nearly every later negotiation.</t>
+        </is>
+      </c>
+      <c r="S5" s="18" t="n"/>
+      <c r="T5" s="18" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>18 August</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>1988-08-18</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>Covenant of the Islamic Resistance Movement (Hamas)</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>Hamas</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>Hamas founding charter, English translation (Avalon Project, Yale)</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O6" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P6" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q6" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/hamas.asp</t>
+        </is>
+      </c>
+      <c r="R6" s="18" t="inlineStr">
+        <is>
+          <t>Hamas's founding text: the other side's own statement of aims, set beside Israel's Declaration.</t>
+        </is>
+      </c>
+      <c r="S6" s="18" t="n"/>
+      <c r="T6" s="18" t="inlineStr">
+        <is>
+          <t>SENSITIVE: your call whether to include. Hamas issued a revised document in 2017.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>13 September</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>1993-09-13</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Declaration of Principles on Interim Self-Government Arrangements (Oslo I)</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>Israel and the Palestine Liberation Organization</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M7" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O7" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P7" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q7" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/isrplo.asp</t>
+        </is>
+      </c>
+      <c r="R7" s="18" t="inlineStr">
+        <is>
+          <t>The first agreement in which Israel and the PLO recognized each other; the framework of the peace process.</t>
+        </is>
+      </c>
+      <c r="S7" s="18" t="n"/>
+      <c r="T7" s="18" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>1970</v>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>3 December</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>1979-12-03</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Islamic Republic of Iran (as amended 1989)</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>Islamic Republic of Iran</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N8" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O8" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P8" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q8" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Iran_1989</t>
+        </is>
+      </c>
+      <c r="R8" s="18" t="inlineStr">
+        <is>
+          <t>Iran's governing text since the revolution; defines the Supreme Leader's role the news keeps returning to.</t>
+        </is>
+      </c>
+      <c r="S8" s="18" t="n"/>
+      <c r="T8" s="18" t="inlineStr">
+        <is>
+          <t>Constitute is a repository of official translations, not a government site. Date is when the 1979 constitution was approved; the text is the 1989 amended version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>19 January</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>1981-01-19</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Algiers Accords: General Declaration</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Government of Algeria, for Iran and the United States</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>Iran-United States Claims Tribunal</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O9" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P9" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q9" s="18" t="inlineStr">
+        <is>
+          <t>https://iusct.com/wp-content/uploads/2021/02/1-General-Declaration_.pdf</t>
+        </is>
+      </c>
+      <c r="R9" s="18" t="inlineStr">
+        <is>
+          <t>The agreement that ended the hostage crisis; it also pledged non-interference in Iran's internal affairs.</t>
+        </is>
+      </c>
+      <c r="S9" s="18" t="n"/>
+      <c r="T9" s="18" t="inlineStr">
+        <is>
+          <t>Hosted by the tribunal the accords created.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>20 July</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>1987-07-20</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 598</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/598(1987)</t>
+        </is>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O10" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P10" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q10" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/598(1987)</t>
+        </is>
+      </c>
+      <c r="R10" s="18" t="inlineStr">
+        <is>
+          <t>The ceasefire resolution that ended the Iran-Iraq war.</t>
+        </is>
+      </c>
+      <c r="S10" s="18" t="n"/>
+      <c r="T10" s="18" t="inlineStr">
+        <is>
+          <t>The UN document viewer is JavaScript and the check could not read it. Open to confirm it is the right resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>14 July</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Joint Comprehensive Plan of Action</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>Iran, China, France, Germany, Russia, United Kingdom, United States and the EU</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Department of State, text of the agreement</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P11" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q11" s="18" t="inlineStr">
+        <is>
+          <t>https://2009-2017.state.gov/documents/organization/245317.pdf</t>
+        </is>
+      </c>
+      <c r="R11" s="18" t="inlineStr">
+        <is>
+          <t>The 2015 nuclear deal: what it limited, and what the 2018 withdrawal ended.</t>
+        </is>
+      </c>
+      <c r="S11" s="18" t="n"/>
+      <c r="T11" s="18" t="inlineStr">
+        <is>
+          <t>PDF opened (200); text not machine-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>8 May</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>2018-05-08</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>National Security Presidential Memorandum on Ceasing United States Participation in the JCPOA</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>Public Papers of the Presidents (American Presidency Project)</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N12" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O12" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P12" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q12" s="18" t="inlineStr">
+        <is>
+          <t>https://www.presidency.ucsb.edu/documents/national-security-presidential-memorandum-ceasing-united-states-participation-the-joint</t>
+        </is>
+      </c>
+      <c r="R12" s="18" t="inlineStr">
+        <is>
+          <t>The order that withdrew the United States from the deal; the proximate cause of later escalation.</t>
+        </is>
+      </c>
+      <c r="S12" s="18" t="n"/>
+      <c r="T12" s="18" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n">
+        <v>1810</v>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>28 April</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>1817-04-28</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>Rush-Bagot Agreement</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>Richard Rush and Charles Bagot</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>Exchange of notes; Treaty Law Division, Government of Canada</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O13" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P13" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q13" s="18" t="inlineStr">
+        <is>
+          <t>https://www.treaty-accord.gc.ca/text-texte.aspx?id=101662</t>
+        </is>
+      </c>
+      <c r="R13" s="18" t="inlineStr">
+        <is>
+          <t>The demilitarization of the Great Lakes; the first step toward the undefended border.</t>
+        </is>
+      </c>
+      <c r="S13" s="18" t="n"/>
+      <c r="T13" s="18" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>18 August</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>1940-08-18</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>Ogdensburg Agreement: Joint Statement on Defence</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>Franklin D. Roosevelt and W. L. Mackenzie King</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>Joint statement issued at Ogdensburg, New York (Ruhr University Bochum source collection)</t>
+        </is>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N14" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O14" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P14" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q14" s="18" t="inlineStr">
+        <is>
+          <t>https://www.ruhr-uni-bochum.de/gna/Quellensammlung/09/09_jointstatementissuedatOgdensburg_1940.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="18" t="inlineStr">
+        <is>
+          <t>The agreement that made the two countries one defence partnership.</t>
+        </is>
+      </c>
+      <c r="S14" s="18" t="n"/>
+      <c r="T14" s="18" t="inlineStr">
+        <is>
+          <t>Weakest host in the round: a German university's document collection, not an archive. Prefer a Library and Archives Canada or FDR Library copy if you know one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>17 April</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>1982-04-17</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>Constitution Act, 1982 (with the Canadian Charter of Rights and Freedoms)</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>Parliament of Canada</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>Justice Laws Website, Government of Canada</t>
+        </is>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O15" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P15" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q15" s="18" t="inlineStr">
+        <is>
+          <t>https://laws-lois.justice.gc.ca/eng/const/page-12.html</t>
+        </is>
+      </c>
+      <c r="R15" s="18" t="inlineStr">
+        <is>
+          <t>Canada's own founding text, patriated in 1982; the neighbour's constitutional model.</t>
+        </is>
+      </c>
+      <c r="S15" s="18" t="n"/>
+      <c r="T15" s="18" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>2 January</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>1988-01-02</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>Canada-United States Free Trade Agreement</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>Governments of Canada and the United States</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>Text of the agreement, Global Affairs Canada</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N16" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O16" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P16" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q16" s="18" t="inlineStr">
+        <is>
+          <t>https://www.international.gc.ca/trade-commerce/assets/pdfs/agreements-accords/cusfta-e.pdf</t>
+        </is>
+      </c>
+      <c r="R16" s="18" t="inlineStr">
+        <is>
+          <t>The agreement that began today's integrated North American economy.</t>
+        </is>
+      </c>
+      <c r="S16" s="18" t="n"/>
+      <c r="T16" s="18" t="inlineStr">
+        <is>
+          <t>10 MB PDF opened (200); text not machine-checked. Alternative: the U.S. House document at govinfo (H. Doc. 100-216).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>30 November</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>2018-11-30</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>United States-Mexico-Canada Agreement</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Governments of the United States, Mexico and Canada</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>Office of the United States Trade Representative</t>
+        </is>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M17" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N17" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O17" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P17" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q17" s="18" t="inlineStr">
+        <is>
+          <t>https://ustr.gov/trade-agreements/free-trade-agreements/united-states-mexico-canada-agreement/agreement-between</t>
+        </is>
+      </c>
+      <c r="R17" s="18" t="inlineStr">
+        <is>
+          <t>The trade pact now under strain.</t>
+        </is>
+      </c>
+      <c r="S17" s="18" t="n"/>
+      <c r="T17" s="18" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>1 February</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>Executive Order 14193: Imposing Duties To Address the Flow of Illicit Drugs Across Our Northern Border</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>Federal Register</t>
+        </is>
+      </c>
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N18" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O18" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P18" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q18" s="18" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2025/02/07/2025-02406/imposing-duties-to-address-the-flow-of-illicit-drugs-across-our-northern-border</t>
+        </is>
+      </c>
+      <c r="R18" s="18" t="inlineStr">
+        <is>
+          <t>The first tariffs on Canada of the second Trump term.</t>
+        </is>
+      </c>
+      <c r="S18" s="18" t="n"/>
+      <c r="T18" s="18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>4 April</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>1949-04-04</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>The North Atlantic Treaty</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>Parties to the North Atlantic Treaty</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M19" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N19" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O19" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P19" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q19" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/official_texts_17120.htm</t>
+        </is>
+      </c>
+      <c r="R19" s="18" t="inlineStr">
+        <is>
+          <t>The founding text, including the Article 5 mutual defence pledge.</t>
+        </is>
+      </c>
+      <c r="S19" s="18" t="n"/>
+      <c r="T19" s="18" t="inlineStr">
+        <is>
+          <t>The matrix already holds two 1949 speeches on the treaty with no link; this is the treaty itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>14 December</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>1967-12-14</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>The Future Tasks of the Alliance (the Harmel Report)</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>North Atlantic Council</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L20" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N20" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O20" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P20" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q20" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/official_texts_26700.htm</t>
+        </is>
+      </c>
+      <c r="R20" s="18" t="inlineStr">
+        <is>
+          <t>The statement that paired deterrence with detente and set NATO's course for decades.</t>
+        </is>
+      </c>
+      <c r="S20" s="18" t="n"/>
+      <c r="T20" s="18" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>12 September</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>2001-09-12</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>Statement by the North Atlantic Council (Article 5 and the 11 September attacks)</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>North Atlantic Council</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L21" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M21" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N21" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O21" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P21" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q21" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/official_texts_18553.htm</t>
+        </is>
+      </c>
+      <c r="R21" s="18" t="inlineStr">
+        <is>
+          <t>The first and only time Article 5 has been invoked.</t>
+        </is>
+      </c>
+      <c r="S21" s="18" t="n"/>
+      <c r="T21" s="18" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>5 September</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>Wales Summit Declaration</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>Heads of State and Government, North Atlantic Council</t>
+        </is>
+      </c>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L22" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M22" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N22" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O22" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P22" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q22" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/official_texts_112964.htm</t>
+        </is>
+      </c>
+      <c r="R22" s="18" t="inlineStr">
+        <is>
+          <t>The pledge to spend two percent of GDP on defence, after Russia's seizure of Crimea.</t>
+        </is>
+      </c>
+      <c r="S22" s="18" t="n"/>
+      <c r="T22" s="18" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>25 June</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>The Hague Summit Declaration</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>Heads of State and Government, North Atlantic Council</t>
+        </is>
+      </c>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L23" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M23" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N23" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O23" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P23" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q23" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/en/about-us/official-texts-and-resources/official-texts/2025/06/25/the-hague-summit-declaration</t>
+        </is>
+      </c>
+      <c r="R23" s="18" t="inlineStr">
+        <is>
+          <t>The new commitment: 3.5% of GDP on core defence plus 1.5% on related spending, by 2035.</t>
+        </is>
+      </c>
+      <c r="S23" s="18" t="n"/>
+      <c r="T23" s="18" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>1780</v>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>26 August</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>1789-08-26</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>Declaration of the Rights of Man and of the Citizen</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>National Constituent Assembly</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L24" s="18" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="M24" s="18" t="inlineStr">
+        <is>
+          <t>civil rights law</t>
+        </is>
+      </c>
+      <c r="N24" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O24" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P24" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q24" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/18th_century/rightsof.asp</t>
+        </is>
+      </c>
+      <c r="R24" s="18" t="inlineStr">
+        <is>
+          <t>France's founding statement of rights and popular sovereignty; the language of every later protest.</t>
+        </is>
+      </c>
+      <c r="S24" s="18" t="n"/>
+      <c r="T24" s="18" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>4 October</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>1958-10-04</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of 4 October 1958 (the Fifth Republic)</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>French Republic</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="inlineStr">
+        <is>
+          <t>Constitutional Council of France, English translation</t>
+        </is>
+      </c>
+      <c r="L25" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M25" s="18" t="inlineStr">
+        <is>
+          <t>executive power</t>
+        </is>
+      </c>
+      <c r="N25" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O25" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P25" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q25" s="18" t="inlineStr">
+        <is>
+          <t>https://www.conseil-constitutionnel.fr/en/constitution-of-4-october-1958</t>
+        </is>
+      </c>
+      <c r="R25" s="18" t="inlineStr">
+        <is>
+          <t>The text that gave France its strong presidency and Article 49.3, the tool used to pass the 2023 pension reform and budgets.</t>
+        </is>
+      </c>
+      <c r="S25" s="18" t="n"/>
+      <c r="T25" s="18" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>7 March</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>1966-03-07</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>Letter from President de Gaulle to President Johnson on France's withdrawal from NATO's integrated command</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>Charles de Gaulle</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>Foreign Relations of the United States, 1964-1968, Vol. XIII</t>
+        </is>
+      </c>
+      <c r="L26" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M26" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N26" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O26" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P26" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q26" s="18" t="inlineStr">
+        <is>
+          <t>https://history.state.gov/historicaldocuments/frus1964-68v13/d137</t>
+        </is>
+      </c>
+      <c r="R26" s="18" t="inlineStr">
+        <is>
+          <t>France leaves NATO's command structure but not the alliance.</t>
+        </is>
+      </c>
+      <c r="S26" s="18" t="n"/>
+      <c r="T26" s="18" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>14 February</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>2003-02-14</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>Statement by Dominique de Villepin to the UN Security Council on Iraq</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>Dominique de Villepin</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council verbatim record S/PV.4701</t>
+        </is>
+      </c>
+      <c r="L27" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M27" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N27" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O27" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P27" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q27" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/PV.4701</t>
+        </is>
+      </c>
+      <c r="R27" s="18" t="inlineStr">
+        <is>
+          <t>The French case against the Iraq war, and the sharpest moment of the transatlantic split.</t>
+        </is>
+      </c>
+      <c r="S27" s="18" t="n"/>
+      <c r="T27" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; could not be read. A text copy is at the Global Policy Forum archive: https://archive.globalpolicy.org/political-issues-in-iraq/important-documents-on-iraq/34911.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>17 April</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>Adresse aux Français (address on the pension reform)</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
+          <t>Emmanuel Macron</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>Elysee, official site</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M28" s="18" t="inlineStr">
+        <is>
+          <t>wages and bargaining power</t>
+        </is>
+      </c>
+      <c r="N28" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O28" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P28" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q28" s="18" t="inlineStr">
+        <is>
+          <t>https://www.elysee.fr/emmanuel-macron/2023/04/17/adresse-aux-francais-2</t>
+        </is>
+      </c>
+      <c r="R28" s="18" t="inlineStr">
+        <is>
+          <t>The president's answer to the 2023 strikes; a precedent for today's protests.</t>
+        </is>
+      </c>
+      <c r="S28" s="18" t="n"/>
+      <c r="T28" s="18" t="inlineStr">
+        <is>
+          <t>In French; no official English text found. Your call whether a French-language primary text is acceptable. School-protest history (the 1881-82 Ferry education laws) has no English official text I could verify.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="17" min="1" max="1"/>
+    <col width="70" customWidth="1" style="17" min="2" max="2"/>
+    <col width="18" customWidth="1" style="17" min="3" max="3"/>
+    <col width="16" customWidth="1" style="17" min="4" max="4"/>
+    <col width="40" customWidth="1" style="17" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>WHY LENSES ARE A SEPARATE LIST (decided 2026-10-06; see docs/decisions.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A lens (a country, an alliance, a technology) is a tag on an object like Column E's Issue (Theme), but on a different axis: Column E says which American argument an object belongs to; a lens says who or what it is about. An object can have one theme and several lenses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>The objects follow the same rules as every matrix object: a primary text, a verified outward link, the link checker. What differs is the selection rule: a row's Beginnings are spread across time before its start year; a lens's are the three nearest before the story's origin. One kind of data, two rules, both in code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>For now lenses stay in editorial/lenses.json and these candidates carry a Lens column. A Lens column in the matrix itself (blank NTK Row allowed for purely foreign objects) is the likely end state. It changes the matrix schema, so it waits for a decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A lens needs at least three linked objects before a story's origin to produce Beginnings. Fewer, and the page shows the origin alone: a thin lens is a to-do, not a failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Matches by</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Linked objects in the matrix today</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Candidates in this round</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>title: telecommunications, fairness doctrine, patriot act, internet, computer, privacy, section 230, antitrust, sherman act, wiretap</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>title: china, chinese communist, taiwan, formosa, shanghai; row: Taiwan</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>title: soviet, moscow, russia, kremlin</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>title: iran, iranian, persian gulf</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>title: israel, israeli, zionism, zionist; sub-genre: Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>lebanon</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>title: lebanon, lebanese, beirut</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>syria</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>title: syria, syrian</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>iraq</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>title: iraq, iraqi, kuwait, gulf war; listed ids: 2003-02-05-address-to-the-united-nations-security-council</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>title: canada, canadian</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>title: nato, north atlantic</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>title: argentina, argentine</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>australia</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>title: australia, australian</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>brazil</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>title: brazil, brazilian</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>title: france, french</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>title: germany, german, germans</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>title: india, indian subcontinent, indian ocean</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>title: indonesia, indonesian</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>title: italy, italian</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>japan</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>title: japan, japanese</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>title: mexico, mexican, mexicans</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>saudi-arabia</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>title: saudi, saudi arabia</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>south-africa</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>title: south africa, south african, apartheid</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>south-korea</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>title: south korea, south korean, korea, korean; row: Korea</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>turkey</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>title: turkey, turkish, ottoman</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>title: great britain, britain, british, england, united kingdom</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/editorial/NTK_Backstory_Candidates.xlsx
+++ b/editorial/NTK_Backstory_Candidates.xlsx
@@ -2987,7 +2987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:T97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" style="17" min="1" max="1"/>
@@ -5426,6 +5426,5918 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>30 May</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>1968-05-30</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>Allocution radiodiffusée du général de Gaulle (30 May 1968)</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>Charles de Gaulle</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="18" t="inlineStr">
+        <is>
+          <t>Fondation Charles de Gaulle</t>
+        </is>
+      </c>
+      <c r="L29" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M29" s="18" t="inlineStr">
+        <is>
+          <t>executive power</t>
+        </is>
+      </c>
+      <c r="N29" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O29" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P29" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q29" s="18" t="inlineStr">
+        <is>
+          <t>http://www.charles-de-gaulle.org/announcement/30-mai-1968-declaration-radiodiffusee-du-general-de-gaulle-dans-lequel-il-annonce-la-dissolution-de-lassemblee-nationale-le-maintien-du-premier-ministre-le-remaniement-du-gouvernement-l/</t>
+        </is>
+      </c>
+      <c r="R29" s="18" t="inlineStr">
+        <is>
+          <t>The president answers the May 1968 student and strike revolt by dissolving the Assembly; the template for how France's presidents respond to the street.</t>
+        </is>
+      </c>
+      <c r="S29" s="18" t="n"/>
+      <c r="T29" s="18" t="inlineStr">
+        <is>
+          <t>In French from the Charles de Gaulle Foundation. An English translation is at the Virginia Tech teaching module (secondary host). No primary text of the Grenelle agreements or of the student movement could be verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>lebanon</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>22 October</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>1989-10-22</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>The Taif Agreement (National Reconciliation Accord)</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>Lebanese parliamentarians, meeting at Taif</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>UN Peacemaker / Lebanese Parliament</t>
+        </is>
+      </c>
+      <c r="L30" s="18" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="M30" s="18" t="inlineStr">
+        <is>
+          <t>civil rights law</t>
+        </is>
+      </c>
+      <c r="N30" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O30" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P30" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q30" s="18" t="inlineStr">
+        <is>
+          <t>https://www.un.int/lebanon/sites/www.un.int/files/Lebanon/the_taif_agreement_english_version_.pdf</t>
+        </is>
+      </c>
+      <c r="R30" s="18" t="inlineStr">
+        <is>
+          <t>Ended the civil war and set the sectarian power-sharing still in force.</t>
+        </is>
+      </c>
+      <c r="S30" s="18" t="n"/>
+      <c r="T30" s="18" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>lebanon</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>2 September</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>2004-09-02</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 1559</t>
+        </is>
+      </c>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/1559(2004)</t>
+        </is>
+      </c>
+      <c r="L31" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M31" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N31" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O31" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P31" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q31" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1559(2004)</t>
+        </is>
+      </c>
+      <c r="R31" s="18" t="inlineStr">
+        <is>
+          <t>Called for foreign forces to leave Lebanon and for militias, meaning Hezbollah, to disband.</t>
+        </is>
+      </c>
+      <c r="S31" s="18" t="n"/>
+      <c r="T31" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>lebanon</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>11 August</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>2006-08-11</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 1701</t>
+        </is>
+      </c>
+      <c r="H32" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L32" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M32" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N32" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O32" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P32" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q32" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="R32" s="18" t="inlineStr">
+        <is>
+          <t>Ended the 2006 Israel-Hezbollah war and set the terms the 2024 ceasefire still cites.</t>
+        </is>
+      </c>
+      <c r="S32" s="18" t="n"/>
+      <c r="T32" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>lebanon</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>1926</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>23 May</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>1926-05-23</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of Lebanon</t>
+        </is>
+      </c>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>Republic of Lebanon</t>
+        </is>
+      </c>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L33" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M33" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N33" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O33" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P33" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q33" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Lebanon_2004</t>
+        </is>
+      </c>
+      <c r="R33" s="18" t="inlineStr">
+        <is>
+          <t>The state's governing text; the sectarian quotas live in it and the Taif amendments.</t>
+        </is>
+      </c>
+      <c r="S33" s="18" t="n"/>
+      <c r="T33" s="18" t="inlineStr">
+        <is>
+          <t>Date is the original 1926 text; the page is the text as amended to 2004.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>syria</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>30 June</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>2012-06-30</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>Final Communiqué of the Action Group for Syria (Geneva Communiqué)</t>
+        </is>
+      </c>
+      <c r="H34" s="18" t="inlineStr">
+        <is>
+          <t>Action Group for Syria</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="18" t="inlineStr">
+        <is>
+          <t>United Nations</t>
+        </is>
+      </c>
+      <c r="L34" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M34" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N34" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O34" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P34" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q34" s="18" t="inlineStr">
+        <is>
+          <t>https://peacemaker.un.org/sites/default/files/document/files/2024/05/sy120630final20communique20of20the20action20group20for20syria.pdf</t>
+        </is>
+      </c>
+      <c r="R34" s="18" t="inlineStr">
+        <is>
+          <t>The plan for a political transition that was never carried out.</t>
+        </is>
+      </c>
+      <c r="S34" s="18" t="n"/>
+      <c r="T34" s="18" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>syria</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>27 September</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>2013-09-27</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 2118</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/2118(2013)</t>
+        </is>
+      </c>
+      <c r="L35" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M35" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N35" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O35" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P35" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q35" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2118(2013)</t>
+        </is>
+      </c>
+      <c r="R35" s="18" t="inlineStr">
+        <is>
+          <t>Required Syria to give up its chemical weapons after the Ghouta attack.</t>
+        </is>
+      </c>
+      <c r="S35" s="18" t="n"/>
+      <c r="T35" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>syria</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>18 December</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>2015-12-18</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 2254</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="n"/>
+      <c r="J36" s="18" t="n"/>
+      <c r="K36" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/2254(2015)</t>
+        </is>
+      </c>
+      <c r="L36" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M36" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N36" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O36" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P36" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q36" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2254(2015)</t>
+        </is>
+      </c>
+      <c r="R36" s="18" t="inlineStr">
+        <is>
+          <t>The UN road map for a ceasefire, a constitution and elections.</t>
+        </is>
+      </c>
+      <c r="S36" s="18" t="n"/>
+      <c r="T36" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>syria</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>12 December</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>2003-12-12</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>Syria Accountability and Lebanese Sovereignty Restoration Act of 2003</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="18" t="inlineStr">
+        <is>
+          <t>Pub. L. 108-175, GovInfo</t>
+        </is>
+      </c>
+      <c r="L37" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M37" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N37" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P37" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q37" s="18" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/PLAW-108publ175/pdf/PLAW-108publ175.pdf</t>
+        </is>
+      </c>
+      <c r="R37" s="18" t="inlineStr">
+        <is>
+          <t>The first U.S. sanctions law aimed at the Syrian government.</t>
+        </is>
+      </c>
+      <c r="S37" s="18" t="n"/>
+      <c r="T37" s="18" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>iraq</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>3 April</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>1991-04-03</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 687</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/687(1991)</t>
+        </is>
+      </c>
+      <c r="L38" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M38" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N38" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O38" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P38" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q38" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/687(1991)</t>
+        </is>
+      </c>
+      <c r="R38" s="18" t="inlineStr">
+        <is>
+          <t>The ceasefire terms after the Gulf War, including weapons inspections.</t>
+        </is>
+      </c>
+      <c r="S38" s="18" t="n"/>
+      <c r="T38" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>iraq</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>8 November</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>2002-11-08</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 1441</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/1441(2002)</t>
+        </is>
+      </c>
+      <c r="L39" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M39" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N39" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O39" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P39" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q39" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1441(2002)</t>
+        </is>
+      </c>
+      <c r="R39" s="18" t="inlineStr">
+        <is>
+          <t>The 'final opportunity' resolution on inspections, argued over before the 2003 invasion.</t>
+        </is>
+      </c>
+      <c r="S39" s="18" t="n"/>
+      <c r="T39" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>iraq</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>15 October</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>2005-10-15</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of Iraq</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>Republic of Iraq</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="n"/>
+      <c r="J40" s="18" t="n"/>
+      <c r="K40" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L40" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M40" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N40" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O40" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P40" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q40" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Iraq_2005</t>
+        </is>
+      </c>
+      <c r="R40" s="18" t="inlineStr">
+        <is>
+          <t>The post-invasion governing text; federalism and Islam's role are still contested.</t>
+        </is>
+      </c>
+      <c r="S40" s="18" t="n"/>
+      <c r="T40" s="18" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>iraq</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>17 November</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>2008-11-17</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>Agreement on the Withdrawal of United States Forces from Iraq (Status of Forces Agreement)</t>
+        </is>
+      </c>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>United States and Iraq</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="18" t="n"/>
+      <c r="K41" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Department of State</t>
+        </is>
+      </c>
+      <c r="L41" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M41" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N41" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O41" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P41" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q41" s="18" t="inlineStr">
+        <is>
+          <t>https://2009-2017.state.gov/documents/organization/122074.pdf</t>
+        </is>
+      </c>
+      <c r="R41" s="18" t="inlineStr">
+        <is>
+          <t>The agreement that set the 2011 U.S. withdrawal date.</t>
+        </is>
+      </c>
+      <c r="S41" s="18" t="n"/>
+      <c r="T41" s="18" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>saudi-arabia</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>23 January</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>1980-01-23</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>State of the Union Address (the Carter Doctrine)</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>Jimmy Carter</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="n"/>
+      <c r="J42" s="18" t="n"/>
+      <c r="K42" s="18" t="inlineStr">
+        <is>
+          <t>Public Papers of the Presidents (American Presidency Project)</t>
+        </is>
+      </c>
+      <c r="L42" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M42" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N42" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O42" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P42" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q42" s="18" t="inlineStr">
+        <is>
+          <t>https://www.presidency.ucsb.edu/documents/the-state-the-union-address-delivered-before-joint-session-the-congress</t>
+        </is>
+      </c>
+      <c r="R42" s="18" t="inlineStr">
+        <is>
+          <t>The U.S. pledge to defend the Persian Gulf, the basis of the American security role in Saudi Arabia.</t>
+        </is>
+      </c>
+      <c r="S42" s="18" t="n"/>
+      <c r="T42" s="18" t="inlineStr">
+        <is>
+          <t>An American text about the Gulf; kept under Saudi Arabia and Iran. Checked: the 23 January 1980 address, with the Persian Gulf passage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>saudi-arabia</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>1 March</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>1992-03-01</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>Basic Law of Governance of Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>Kingdom of Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="n"/>
+      <c r="J43" s="18" t="n"/>
+      <c r="K43" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L43" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M43" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N43" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O43" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P43" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q43" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Saudi_Arabia_2005</t>
+        </is>
+      </c>
+      <c r="R43" s="18" t="inlineStr">
+        <is>
+          <t>The kingdom's governing text: the Quran as constitution, the king's powers.</t>
+        </is>
+      </c>
+      <c r="S43" s="18" t="n"/>
+      <c r="T43" s="18" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>saudi-arabia</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>28 March</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>2002-03-28</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t>Arab Peace Initiative</t>
+        </is>
+      </c>
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>League of Arab States, proposed by Crown Prince Abdullah of Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="I44" s="18" t="n"/>
+      <c r="J44" s="18" t="n"/>
+      <c r="K44" s="18" t="inlineStr">
+        <is>
+          <t>League of Arab States, English text</t>
+        </is>
+      </c>
+      <c r="L44" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M44" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N44" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O44" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P44" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q44" s="18" t="inlineStr">
+        <is>
+          <t>https://www.un.org/unispal/document/auto-insert-181223/</t>
+        </is>
+      </c>
+      <c r="R44" s="18" t="inlineStr">
+        <is>
+          <t>The Saudi-led offer of normalization for a return to the 1967 lines; central again in Gaza diplomacy.</t>
+        </is>
+      </c>
+      <c r="S44" s="18" t="n"/>
+      <c r="T44" s="18" t="inlineStr">
+        <is>
+          <t>Letter from Lebanon to the UN transmitting the text (excerpts); a full copy is at palestineinarabic.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>saudi-arabia</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>25 April</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>2016-04-25</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>Saudi Vision 2030</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>Kingdom of Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="n"/>
+      <c r="J45" s="18" t="n"/>
+      <c r="K45" s="18" t="inlineStr">
+        <is>
+          <t>Vision 2030 official site</t>
+        </is>
+      </c>
+      <c r="L45" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M45" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N45" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O45" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P45" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q45" s="18" t="inlineStr">
+        <is>
+          <t>https://www.vision2030.gov.sa/media/rc0b5oy1/saudi_vision203.pdf</t>
+        </is>
+      </c>
+      <c r="R45" s="18" t="inlineStr">
+        <is>
+          <t>The economic plan to move beyond oil.</t>
+        </is>
+      </c>
+      <c r="S45" s="18" t="n"/>
+      <c r="T45" s="18" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>turkey</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>24 July</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>1923-07-24</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>Treaty of Lausanne</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="inlineStr">
+        <is>
+          <t>Allied Powers and Turkey</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="n"/>
+      <c r="J46" s="18" t="n"/>
+      <c r="K46" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Foreign Affairs of the Republic of Turkey</t>
+        </is>
+      </c>
+      <c r="L46" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M46" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N46" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O46" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P46" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q46" s="18" t="inlineStr">
+        <is>
+          <t>https://www.mfa.gov.tr/lausanne-peace-treaty-part-i_-political-clauses.en.mfa</t>
+        </is>
+      </c>
+      <c r="R46" s="18" t="inlineStr">
+        <is>
+          <t>The treaty that set modern Turkey's borders and minority rules.</t>
+        </is>
+      </c>
+      <c r="S46" s="18" t="n"/>
+      <c r="T46" s="18" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>turkey</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>7 November</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>1982-11-07</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Republic of Turkey (as amended)</t>
+        </is>
+      </c>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>Republic of Turkey</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="n"/>
+      <c r="J47" s="18" t="n"/>
+      <c r="K47" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L47" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M47" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N47" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O47" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P47" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q47" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Turkey_2017</t>
+        </is>
+      </c>
+      <c r="R47" s="18" t="inlineStr">
+        <is>
+          <t>The governing text; the 2017 amendments created the executive presidency.</t>
+        </is>
+      </c>
+      <c r="S47" s="18" t="n"/>
+      <c r="T47" s="18" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>south-africa</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>26 June</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>1955-06-26</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>The Freedom Charter</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>Congress of the People</t>
+        </is>
+      </c>
+      <c r="I48" s="18" t="n"/>
+      <c r="J48" s="18" t="n"/>
+      <c r="K48" s="18" t="inlineStr">
+        <is>
+          <t>African National Congress</t>
+        </is>
+      </c>
+      <c r="L48" s="18" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="M48" s="18" t="inlineStr">
+        <is>
+          <t>civil rights law</t>
+        </is>
+      </c>
+      <c r="N48" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O48" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P48" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q48" s="18" t="inlineStr">
+        <is>
+          <t>https://www.anc1912.org.za/the-freedom-charter-2/</t>
+        </is>
+      </c>
+      <c r="R48" s="18" t="inlineStr">
+        <is>
+          <t>The anti-apartheid movement's founding statement of rights.</t>
+        </is>
+      </c>
+      <c r="S48" s="18" t="n"/>
+      <c r="T48" s="18" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>south-africa</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>20 April</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>1964-04-20</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>Statement from the Dock at the Rivonia Trial</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>Nelson Mandela</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="n"/>
+      <c r="J49" s="18" t="n"/>
+      <c r="K49" s="18" t="inlineStr">
+        <is>
+          <t>African National Congress</t>
+        </is>
+      </c>
+      <c r="L49" s="18" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="M49" s="18" t="inlineStr">
+        <is>
+          <t>civil rights law</t>
+        </is>
+      </c>
+      <c r="N49" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O49" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P49" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q49" s="18" t="inlineStr">
+        <is>
+          <t>http://www.mandela.gov.za/mandela_speeches/before/640420_trial.htm</t>
+        </is>
+      </c>
+      <c r="R49" s="18" t="inlineStr">
+        <is>
+          <t>'An ideal for which I am prepared to die.'</t>
+        </is>
+      </c>
+      <c r="S49" s="18" t="n"/>
+      <c r="T49" s="18" t="inlineStr">
+        <is>
+          <t>Also on the UN site: https://static.un.org/en/events/mandeladay/court_statement_1964.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>south-africa</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>10 December</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>1996-12-10</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Republic of South Africa, 1996</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
+        <is>
+          <t>Constitutional Assembly of South Africa</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="n"/>
+      <c r="J50" s="18" t="n"/>
+      <c r="K50" s="18" t="inlineStr">
+        <is>
+          <t>Government of South Africa</t>
+        </is>
+      </c>
+      <c r="L50" s="18" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="M50" s="18" t="inlineStr">
+        <is>
+          <t>civil rights law</t>
+        </is>
+      </c>
+      <c r="N50" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O50" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P50" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q50" s="18" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/documents/constitution-republic-south-africa-1996</t>
+        </is>
+      </c>
+      <c r="R50" s="18" t="inlineStr">
+        <is>
+          <t>The post-apartheid constitution, a model for rights-based constitutions.</t>
+        </is>
+      </c>
+      <c r="S50" s="18" t="n"/>
+      <c r="T50" s="18" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>south-africa</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>29 December</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>2023-12-29</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t>Application Instituting Proceedings: South Africa v. Israel (Genocide Convention)</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>Republic of South Africa</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="18" t="n"/>
+      <c r="K51" s="18" t="inlineStr">
+        <is>
+          <t>International Court of Justice</t>
+        </is>
+      </c>
+      <c r="L51" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M51" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N51" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O51" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P51" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q51" s="18" t="inlineStr">
+        <is>
+          <t>https://www.icj-cij.org/sites/default/files/case-related/192/192-20231228-app-01-00-en.pdf</t>
+        </is>
+      </c>
+      <c r="R51" s="18" t="inlineStr">
+        <is>
+          <t>South Africa's case against Israel at the ICJ, now at the center of the Gaza argument.</t>
+        </is>
+      </c>
+      <c r="S51" s="18" t="n"/>
+      <c r="T51" s="18" t="inlineStr">
+        <is>
+          <t>PDF; text not machine-checked. The ICJ site refuses scripts; the case-file URL follows the court's own pattern. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="n">
+        <v>1210</v>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>15 June</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>1215-06-15</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>Magna Carta</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>King John and the barons of England</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="n"/>
+      <c r="J52" s="18" t="n"/>
+      <c r="K52" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L52" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M52" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N52" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O52" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P52" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q52" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/medieval/magframe.asp</t>
+        </is>
+      </c>
+      <c r="R52" s="18" t="inlineStr">
+        <is>
+          <t>The oldest text on limiting a ruler's power, behind the American Constitution.</t>
+        </is>
+      </c>
+      <c r="S52" s="18" t="n"/>
+      <c r="T52" s="18" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>1689</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>16 December</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>1689-12-16</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G53" s="18" t="inlineStr">
+        <is>
+          <t>The English Bill of Rights</t>
+        </is>
+      </c>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>Parliament of England</t>
+        </is>
+      </c>
+      <c r="I53" s="18" t="n"/>
+      <c r="J53" s="18" t="n"/>
+      <c r="K53" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L53" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M53" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N53" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O53" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P53" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q53" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/17th_century/england.asp</t>
+        </is>
+      </c>
+      <c r="R53" s="18" t="inlineStr">
+        <is>
+          <t>Parliament's limits on the Crown; a direct source for the American Bill of Rights.</t>
+        </is>
+      </c>
+      <c r="S53" s="18" t="n"/>
+      <c r="T53" s="18" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="n">
+        <v>1780</v>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>1783</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>3 September</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>1783-09-03</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G54" s="18" t="inlineStr">
+        <is>
+          <t>Treaty of Paris (1783)</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="inlineStr">
+        <is>
+          <t>Great Britain and the United States</t>
+        </is>
+      </c>
+      <c r="I54" s="18" t="n"/>
+      <c r="J54" s="18" t="n"/>
+      <c r="K54" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L54" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M54" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N54" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O54" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P54" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q54" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/18th_century/paris.asp</t>
+        </is>
+      </c>
+      <c r="R54" s="18" t="inlineStr">
+        <is>
+          <t>Britain recognizes the United States.</t>
+        </is>
+      </c>
+      <c r="S54" s="18" t="n"/>
+      <c r="T54" s="18" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>5 March</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>1946-03-05</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t>The Sinews of Peace (the 'Iron Curtain' speech)</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>Winston Churchill</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="n"/>
+      <c r="J55" s="18" t="n"/>
+      <c r="K55" s="18" t="inlineStr">
+        <is>
+          <t>The Churchill Centre / Winston Churchill Foundation</t>
+        </is>
+      </c>
+      <c r="L55" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M55" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N55" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O55" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P55" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q55" s="18" t="inlineStr">
+        <is>
+          <t>https://winstonchurchill.org/resources/speeches/1946-1963-elder-statesman/the-sinews-of-peace/</t>
+        </is>
+      </c>
+      <c r="R55" s="18" t="inlineStr">
+        <is>
+          <t>Britain's wartime leader calls for a Western alliance against the USSR.</t>
+        </is>
+      </c>
+      <c r="S55" s="18" t="n"/>
+      <c r="T55" s="18" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>29 March</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>2017-03-29</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t>Prime Minister's letter to President of the European Council triggering Article 50</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="inlineStr">
+        <is>
+          <t>Theresa May</t>
+        </is>
+      </c>
+      <c r="I56" s="18" t="n"/>
+      <c r="J56" s="18" t="n"/>
+      <c r="K56" s="18" t="inlineStr">
+        <is>
+          <t>UK Government</t>
+        </is>
+      </c>
+      <c r="L56" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M56" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N56" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O56" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P56" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q56" s="18" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/prime-ministers-letter-to-donald-tusk-triggering-article-50</t>
+        </is>
+      </c>
+      <c r="R56" s="18" t="inlineStr">
+        <is>
+          <t>The formal start of Britain's exit from the European Union.</t>
+        </is>
+      </c>
+      <c r="S56" s="18" t="n"/>
+      <c r="T56" s="18" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>23 May</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>1949-05-23</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t>Basic Law for the Federal Republic of Germany</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>Parliamentary Council</t>
+        </is>
+      </c>
+      <c r="I57" s="18" t="n"/>
+      <c r="J57" s="18" t="n"/>
+      <c r="K57" s="18" t="inlineStr">
+        <is>
+          <t>Federal Ministry of Justice, English translation</t>
+        </is>
+      </c>
+      <c r="L57" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M57" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N57" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O57" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P57" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q57" s="18" t="inlineStr">
+        <is>
+          <t>https://www.gesetze-im-internet.de/englisch_gg/</t>
+        </is>
+      </c>
+      <c r="R57" s="18" t="inlineStr">
+        <is>
+          <t>Postwar Germany's constitution, built to prevent another dictatorship.</t>
+        </is>
+      </c>
+      <c r="S57" s="18" t="n"/>
+      <c r="T57" s="18" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>22 January</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>1963-01-22</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G58" s="18" t="inlineStr">
+        <is>
+          <t>Treaty on Franco-German Cooperation (Élysée Treaty)</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="inlineStr">
+        <is>
+          <t>Konrad Adenauer and Charles de Gaulle</t>
+        </is>
+      </c>
+      <c r="I58" s="18" t="n"/>
+      <c r="J58" s="18" t="n"/>
+      <c r="K58" s="18" t="inlineStr">
+        <is>
+          <t>Federal Foreign Office / Elysee</t>
+        </is>
+      </c>
+      <c r="L58" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M58" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N58" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O58" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P58" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q58" s="18" t="inlineStr">
+        <is>
+          <t>https://www.cvce.eu/en/obj/treaty_between_the_french_republic_and_the_federal_republic_of_germany_on_french_german_cooperation_22_january_1963-en-68956f73-75cb-4749-a6e2-344c8aad84ba.html</t>
+        </is>
+      </c>
+      <c r="R58" s="18" t="inlineStr">
+        <is>
+          <t>Reconciliation between France and Germany, the core of the European project.</t>
+        </is>
+      </c>
+      <c r="S58" s="18" t="n"/>
+      <c r="T58" s="18" t="inlineStr">
+        <is>
+          <t>CVCE (University of Luxembourg's archive) showed a bot check. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>27 February</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>2022-02-27</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>Policy statement by Chancellor Olaf Scholz (the Zeitenwende speech)</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>Olaf Scholz</t>
+        </is>
+      </c>
+      <c r="I59" s="18" t="n"/>
+      <c r="J59" s="18" t="n"/>
+      <c r="K59" s="18" t="inlineStr">
+        <is>
+          <t>Federal Government of Germany</t>
+        </is>
+      </c>
+      <c r="L59" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M59" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N59" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O59" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P59" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q59" s="18" t="inlineStr">
+        <is>
+          <t>https://www.bundesregierung.de/breg-en/news/policy-statement-by-olaf-scholz-chancellor-of-the-federal-republic-of-germany-and-member-of-the-german-bundestag-27-february-2022-in-berlin-2008378</t>
+        </is>
+      </c>
+      <c r="R59" s="18" t="inlineStr">
+        <is>
+          <t>Germany's turn on defence spending after Russia's invasion of Ukraine.</t>
+        </is>
+      </c>
+      <c r="S59" s="18" t="n"/>
+      <c r="T59" s="18" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>japan</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>26 July</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>1945-07-26</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t>Potsdam Declaration: Proclamation Defining Terms for Japanese Surrender</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
+        <is>
+          <t>Truman, Churchill and Chiang Kai-shek</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="n"/>
+      <c r="J60" s="18" t="n"/>
+      <c r="K60" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L60" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M60" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N60" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O60" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P60" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q60" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/decade17.asp</t>
+        </is>
+      </c>
+      <c r="R60" s="18" t="inlineStr">
+        <is>
+          <t>The terms Japan accepted after the bombs.</t>
+        </is>
+      </c>
+      <c r="S60" s="18" t="n"/>
+      <c r="T60" s="18" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>japan</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>3 May</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>1947-05-03</t>
+        </is>
+      </c>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G61" s="18" t="inlineStr">
+        <is>
+          <t>The Constitution of Japan</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>Government of Japan</t>
+        </is>
+      </c>
+      <c r="I61" s="18" t="n"/>
+      <c r="J61" s="18" t="n"/>
+      <c r="K61" s="18" t="inlineStr">
+        <is>
+          <t>Prime Minister of Japan and His Cabinet</t>
+        </is>
+      </c>
+      <c r="L61" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M61" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N61" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O61" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P61" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q61" s="18" t="inlineStr">
+        <is>
+          <t>https://www.japaneselawtranslation.go.jp/en/laws/view/174</t>
+        </is>
+      </c>
+      <c r="R61" s="18" t="inlineStr">
+        <is>
+          <t>Article 9's renunciation of war, written under the Occupation.</t>
+        </is>
+      </c>
+      <c r="S61" s="18" t="n"/>
+      <c r="T61" s="18" t="inlineStr">
+        <is>
+          <t>Japan's official law-translation site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>japan</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>19 January</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>1960-01-19</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>Treaty of Mutual Cooperation and Security between Japan and the United States</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="inlineStr">
+        <is>
+          <t>Japan and the United States</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="n"/>
+      <c r="J62" s="18" t="n"/>
+      <c r="K62" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Foreign Affairs of Japan</t>
+        </is>
+      </c>
+      <c r="L62" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M62" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N62" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O62" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P62" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q62" s="18" t="inlineStr">
+        <is>
+          <t>https://www.mofa.go.jp/region/n-america/us/q&amp;a/ref/1.html</t>
+        </is>
+      </c>
+      <c r="R62" s="18" t="inlineStr">
+        <is>
+          <t>The bilateral security treaty still in force.</t>
+        </is>
+      </c>
+      <c r="S62" s="18" t="n"/>
+      <c r="T62" s="18" t="inlineStr">
+        <is>
+          <t>Japan's foreign ministry refuses scripts; URL not machine-checked. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>15 August</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>1947-08-15</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G63" s="18" t="inlineStr">
+        <is>
+          <t>Indian Independence Act 1947</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>Parliament of the United Kingdom</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="n"/>
+      <c r="J63" s="18" t="n"/>
+      <c r="K63" s="18" t="inlineStr">
+        <is>
+          <t>UK Parliament, legislation.gov.uk</t>
+        </is>
+      </c>
+      <c r="L63" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M63" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N63" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O63" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P63" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q63" s="18" t="inlineStr">
+        <is>
+          <t>https://www.legislation.gov.uk/ukpga/Geo6/10-11/30/contents/enacted</t>
+        </is>
+      </c>
+      <c r="R63" s="18" t="inlineStr">
+        <is>
+          <t>The law that ended British rule and created India and Pakistan.</t>
+        </is>
+      </c>
+      <c r="S63" s="18" t="n"/>
+      <c r="T63" s="18" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>26 January</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>1950-01-26</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of India</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>Constituent Assembly of India</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="n"/>
+      <c r="J64" s="18" t="n"/>
+      <c r="K64" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project / Government of India</t>
+        </is>
+      </c>
+      <c r="L64" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M64" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N64" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O64" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P64" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q64" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/India_2016</t>
+        </is>
+      </c>
+      <c r="R64" s="18" t="inlineStr">
+        <is>
+          <t>The world's largest democracy's governing text.</t>
+        </is>
+      </c>
+      <c r="S64" s="18" t="n"/>
+      <c r="T64" s="18" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>18 July</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>2005-07-18</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>Joint Statement by President Bush and Prime Minister Singh (civil nuclear cooperation)</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>George W. Bush and Manmohan Singh</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="n"/>
+      <c r="J65" s="18" t="n"/>
+      <c r="K65" s="18" t="inlineStr">
+        <is>
+          <t>The White House archives</t>
+        </is>
+      </c>
+      <c r="L65" s="18" t="inlineStr">
+        <is>
+          <t>The Bomb</t>
+        </is>
+      </c>
+      <c r="M65" s="18" t="inlineStr">
+        <is>
+          <t>arms control and treaties</t>
+        </is>
+      </c>
+      <c r="N65" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O65" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P65" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q65" s="18" t="inlineStr">
+        <is>
+          <t>https://georgewbush-whitehouse.archives.gov/news/releases/2005/07/20050718-6.html</t>
+        </is>
+      </c>
+      <c r="R65" s="18" t="inlineStr">
+        <is>
+          <t>The U.S.-India nuclear deal that ended India's nuclear isolation.</t>
+        </is>
+      </c>
+      <c r="S65" s="18" t="n"/>
+      <c r="T65" s="18" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>2 February</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>1848-02-02</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>Treaty of Guadalupe Hidalgo</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>United States and Mexico</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="n"/>
+      <c r="J66" s="18" t="n"/>
+      <c r="K66" s="18" t="inlineStr">
+        <is>
+          <t>National Archives</t>
+        </is>
+      </c>
+      <c r="L66" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M66" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N66" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O66" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P66" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q66" s="18" t="inlineStr">
+        <is>
+          <t>https://www.archives.gov/milestone-documents/treaty-of-guadalupe-hidalgo</t>
+        </is>
+      </c>
+      <c r="R66" s="18" t="inlineStr">
+        <is>
+          <t>The treaty that ended the Mexican-American War and moved the border.</t>
+        </is>
+      </c>
+      <c r="S66" s="18" t="n"/>
+      <c r="T66" s="18" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="n">
+        <v>1910</v>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>16 January</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>1917-01-16</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="inlineStr">
+        <is>
+          <t>The Zimmermann Telegram</t>
+        </is>
+      </c>
+      <c r="H67" s="18" t="inlineStr">
+        <is>
+          <t>Arthur Zimmermann</t>
+        </is>
+      </c>
+      <c r="I67" s="18" t="n"/>
+      <c r="J67" s="18" t="n"/>
+      <c r="K67" s="18" t="inlineStr">
+        <is>
+          <t>National Archives</t>
+        </is>
+      </c>
+      <c r="L67" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M67" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N67" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O67" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P67" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q67" s="18" t="inlineStr">
+        <is>
+          <t>https://www.archives.gov/education/lessons/zimmermann</t>
+        </is>
+      </c>
+      <c r="R67" s="18" t="inlineStr">
+        <is>
+          <t>Germany's offer to Mexico that helped bring the United States into World War I.</t>
+        </is>
+      </c>
+      <c r="S67" s="18" t="n"/>
+      <c r="T67" s="18" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="n">
+        <v>1910</v>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>5 February</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>1917-02-05</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of Mexico, 1917</t>
+        </is>
+      </c>
+      <c r="H68" s="18" t="inlineStr">
+        <is>
+          <t>Constituent Congress of Mexico</t>
+        </is>
+      </c>
+      <c r="I68" s="18" t="n"/>
+      <c r="J68" s="18" t="n"/>
+      <c r="K68" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L68" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M68" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N68" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O68" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P68" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q68" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Mexico_2015</t>
+        </is>
+      </c>
+      <c r="R68" s="18" t="inlineStr">
+        <is>
+          <t>The first constitution to write in social rights, land and labor.</t>
+        </is>
+      </c>
+      <c r="S68" s="18" t="n"/>
+      <c r="T68" s="18" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>1 January</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>1994-01-01</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>North American Free Trade Agreement</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>Governments of the United States, Mexico and Canada</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="n"/>
+      <c r="J69" s="18" t="n"/>
+      <c r="K69" s="18" t="inlineStr">
+        <is>
+          <t>Office of the United States Trade Representative</t>
+        </is>
+      </c>
+      <c r="L69" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M69" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N69" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O69" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P69" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q69" s="18" t="inlineStr">
+        <is>
+          <t>http://www.sice.oas.org/trade/nafta/naftatce.asp</t>
+        </is>
+      </c>
+      <c r="R69" s="18" t="inlineStr">
+        <is>
+          <t>The trade pact the 2018 USMCA replaced.</t>
+        </is>
+      </c>
+      <c r="S69" s="18" t="n"/>
+      <c r="T69" s="18" t="inlineStr">
+        <is>
+          <t>Organization of American States trade-information system. The USTR archive page has the same text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
+          <t>1 May</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>1853-05-01</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Argentine Nation</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="inlineStr">
+        <is>
+          <t>General Constituent Congress</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="n"/>
+      <c r="J70" s="18" t="n"/>
+      <c r="K70" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L70" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M70" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N70" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O70" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P70" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q70" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Argentina_1994</t>
+        </is>
+      </c>
+      <c r="R70" s="18" t="inlineStr">
+        <is>
+          <t>The constitution modeled on the American one.</t>
+        </is>
+      </c>
+      <c r="S70" s="18" t="n"/>
+      <c r="T70" s="18" t="inlineStr">
+        <is>
+          <t>Text as amended 1994.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>16 December</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>1965-12-16</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>UN General Assembly Resolution 2065 (XX): Question of the Falkland Islands (Malvinas)</t>
+        </is>
+      </c>
+      <c r="H71" s="18" t="inlineStr">
+        <is>
+          <t>United Nations General Assembly</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="n"/>
+      <c r="J71" s="18" t="n"/>
+      <c r="K71" s="18" t="inlineStr">
+        <is>
+          <t>UN document A/RES/2065(XX)</t>
+        </is>
+      </c>
+      <c r="L71" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M71" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N71" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O71" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P71" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q71" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/RES/2065(XX)</t>
+        </is>
+      </c>
+      <c r="R71" s="18" t="inlineStr">
+        <is>
+          <t>The UN call for Britain and Argentina to negotiate the islands' status.</t>
+        </is>
+      </c>
+      <c r="S71" s="18" t="n"/>
+      <c r="T71" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>25 May</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>1982-05-25</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t>Argentina's Falklands conflict, UN Security Council Resolution 502</t>
+        </is>
+      </c>
+      <c r="H72" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="n"/>
+      <c r="J72" s="18" t="n"/>
+      <c r="K72" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/502(1982)</t>
+        </is>
+      </c>
+      <c r="L72" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M72" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N72" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O72" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P72" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q72" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/502(1982)</t>
+        </is>
+      </c>
+      <c r="R72" s="18" t="inlineStr">
+        <is>
+          <t>The resolution demanding Argentina's withdrawal at the start of the 1982 war.</t>
+        </is>
+      </c>
+      <c r="S72" s="18" t="n"/>
+      <c r="T72" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>australia</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>1901</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="inlineStr">
+        <is>
+          <t>1 January</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>1901-01-01</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t>Commonwealth of Australia Constitution Act</t>
+        </is>
+      </c>
+      <c r="H73" s="18" t="inlineStr">
+        <is>
+          <t>Imperial Parliament</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="n"/>
+      <c r="J73" s="18" t="n"/>
+      <c r="K73" s="18" t="inlineStr">
+        <is>
+          <t>Museum of Australian Democracy / Australian government</t>
+        </is>
+      </c>
+      <c r="L73" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M73" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N73" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O73" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P73" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q73" s="18" t="inlineStr">
+        <is>
+          <t>https://www.legislation.gov.au/C1900A00063/latest/text</t>
+        </is>
+      </c>
+      <c r="R73" s="18" t="inlineStr">
+        <is>
+          <t>Australia's founding constitution.</t>
+        </is>
+      </c>
+      <c r="S73" s="18" t="n"/>
+      <c r="T73" s="18" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>australia</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>15 September</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="inlineStr">
+        <is>
+          <t>Joint Leaders Statement on AUKUS</t>
+        </is>
+      </c>
+      <c r="H74" s="18" t="inlineStr">
+        <is>
+          <t>Joe Biden, Scott Morrison and Boris Johnson</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="n"/>
+      <c r="J74" s="18" t="n"/>
+      <c r="K74" s="18" t="inlineStr">
+        <is>
+          <t>The White House</t>
+        </is>
+      </c>
+      <c r="L74" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M74" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N74" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O74" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P74" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q74" s="18" t="inlineStr">
+        <is>
+          <t>https://bidenwhitehouse.archives.gov/briefing-room/statements-releases/2021/09/15/joint-leaders-statement-on-aukus/</t>
+        </is>
+      </c>
+      <c r="R74" s="18" t="inlineStr">
+        <is>
+          <t>The submarine pact aimed at China.</t>
+        </is>
+      </c>
+      <c r="S74" s="18" t="n"/>
+      <c r="T74" s="18" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>brazil</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>5 October</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>1988-10-05</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G75" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Federative Republic of Brazil</t>
+        </is>
+      </c>
+      <c r="H75" s="18" t="inlineStr">
+        <is>
+          <t>Constituent Assembly of Brazil</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="n"/>
+      <c r="J75" s="18" t="n"/>
+      <c r="K75" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L75" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M75" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N75" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O75" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P75" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q75" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Brazil_2017</t>
+        </is>
+      </c>
+      <c r="R75" s="18" t="inlineStr">
+        <is>
+          <t>The 'citizen constitution' that ended military rule.</t>
+        </is>
+      </c>
+      <c r="S75" s="18" t="n"/>
+      <c r="T75" s="18" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>24 April</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>1955-04-24</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>Final Communiqué of the Asian-African Conference of Bandung</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="inlineStr">
+        <is>
+          <t>Asian-African Conference</t>
+        </is>
+      </c>
+      <c r="I76" s="18" t="n"/>
+      <c r="J76" s="18" t="n"/>
+      <c r="K76" s="18" t="inlineStr">
+        <is>
+          <t>Digital Archive, Indonesia / Library</t>
+        </is>
+      </c>
+      <c r="L76" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M76" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N76" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O76" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P76" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q76" s="18" t="inlineStr">
+        <is>
+          <t>https://www.bandungspirit.org/IMG/pdf/bandung_final_communique.pdf</t>
+        </is>
+      </c>
+      <c r="R76" s="18" t="inlineStr">
+        <is>
+          <t>The founding statement of the non-aligned movement.</t>
+        </is>
+      </c>
+      <c r="S76" s="18" t="n"/>
+      <c r="T76" s="18" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>18 August</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>1945-08-18</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G77" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Republic of Indonesia (as amended)</t>
+        </is>
+      </c>
+      <c r="H77" s="18" t="inlineStr">
+        <is>
+          <t>Republic of Indonesia</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="n"/>
+      <c r="J77" s="18" t="n"/>
+      <c r="K77" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L77" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M77" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N77" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O77" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P77" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q77" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Indonesia_2002</t>
+        </is>
+      </c>
+      <c r="R77" s="18" t="inlineStr">
+        <is>
+          <t>The Pancasila constitution; the 2002 amendments ended Suharto-era rule.</t>
+        </is>
+      </c>
+      <c r="S77" s="18" t="n"/>
+      <c r="T77" s="18" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>22 December</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>1947-12-22</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Italian Republic</t>
+        </is>
+      </c>
+      <c r="H78" s="18" t="inlineStr">
+        <is>
+          <t>Constituent Assembly of Italy</t>
+        </is>
+      </c>
+      <c r="I78" s="18" t="n"/>
+      <c r="J78" s="18" t="n"/>
+      <c r="K78" s="18" t="inlineStr">
+        <is>
+          <t>Senate of the Italian Republic, English translation</t>
+        </is>
+      </c>
+      <c r="L78" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M78" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N78" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O78" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P78" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q78" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Italy_2012</t>
+        </is>
+      </c>
+      <c r="R78" s="18" t="inlineStr">
+        <is>
+          <t>Postwar Italy's governing text, written to bar a return of fascism.</t>
+        </is>
+      </c>
+      <c r="S78" s="18" t="n"/>
+      <c r="T78" s="18" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>25 March</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>1957-03-25</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G79" s="18" t="inlineStr">
+        <is>
+          <t>Treaty establishing the European Economic Community (Treaty of Rome)</t>
+        </is>
+      </c>
+      <c r="H79" s="18" t="inlineStr">
+        <is>
+          <t>Six founding states, including Italy</t>
+        </is>
+      </c>
+      <c r="I79" s="18" t="n"/>
+      <c r="J79" s="18" t="n"/>
+      <c r="K79" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex</t>
+        </is>
+      </c>
+      <c r="L79" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M79" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N79" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O79" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P79" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q79" s="18" t="inlineStr">
+        <is>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:11957E/TXT</t>
+        </is>
+      </c>
+      <c r="R79" s="18" t="inlineStr">
+        <is>
+          <t>The treaty that began the common market, signed in Rome.</t>
+        </is>
+      </c>
+      <c r="S79" s="18" t="n"/>
+      <c r="T79" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex returns a script challenge. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="n">
+        <v>1890</v>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>1890</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>2 July</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr">
+        <is>
+          <t>1890-07-02</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>Sherman Antitrust Act</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="n"/>
+      <c r="J80" s="18" t="n"/>
+      <c r="K80" s="18" t="inlineStr">
+        <is>
+          <t>National Archives</t>
+        </is>
+      </c>
+      <c r="L80" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M80" s="18" t="inlineStr">
+        <is>
+          <t>regulation and the administrative state</t>
+        </is>
+      </c>
+      <c r="N80" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O80" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P80" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q80" s="18" t="inlineStr">
+        <is>
+          <t>https://www.archives.gov/milestone-documents/sherman-anti-trust-act</t>
+        </is>
+      </c>
+      <c r="R80" s="18" t="inlineStr">
+        <is>
+          <t>The first law against monopoly, the basis for every later action against big companies.</t>
+        </is>
+      </c>
+      <c r="S80" s="18" t="n"/>
+      <c r="T80" s="18" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B81" s="18" t="n">
+        <v>1930</v>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>19 June</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>1934-06-19</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>Communications Act of 1934</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="I81" s="18" t="n"/>
+      <c r="J81" s="18" t="n"/>
+      <c r="K81" s="18" t="inlineStr">
+        <is>
+          <t>Pub. L. 73-416, GovInfo</t>
+        </is>
+      </c>
+      <c r="L81" s="18" t="inlineStr">
+        <is>
+          <t>The Media</t>
+        </is>
+      </c>
+      <c r="M81" s="18" t="inlineStr">
+        <is>
+          <t>platforms and attention</t>
+        </is>
+      </c>
+      <c r="N81" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O81" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P81" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q81" s="18" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/COMPS-1409/pdf/COMPS-1409.pdf</t>
+        </is>
+      </c>
+      <c r="R81" s="18" t="inlineStr">
+        <is>
+          <t>The law that created the FCC and still frames broadcast and telecom regulation.</t>
+        </is>
+      </c>
+      <c r="S81" s="18" t="n"/>
+      <c r="T81" s="18" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>1 July</t>
+        </is>
+      </c>
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t>1945-07-01</t>
+        </is>
+      </c>
+      <c r="F82" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="inlineStr">
+        <is>
+          <t>As We May Think</t>
+        </is>
+      </c>
+      <c r="H82" s="18" t="inlineStr">
+        <is>
+          <t>Vannevar Bush</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="n"/>
+      <c r="J82" s="18" t="n"/>
+      <c r="K82" s="18" t="inlineStr">
+        <is>
+          <t>The Atlantic</t>
+        </is>
+      </c>
+      <c r="L82" s="18" t="inlineStr">
+        <is>
+          <t>The Media</t>
+        </is>
+      </c>
+      <c r="M82" s="18" t="inlineStr">
+        <is>
+          <t>information and misinformation</t>
+        </is>
+      </c>
+      <c r="N82" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O82" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P82" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q82" s="18" t="inlineStr">
+        <is>
+          <t>https://www.theatlantic.com/magazine/archive/1945/07/as-we-may-think/303881/</t>
+        </is>
+      </c>
+      <c r="R82" s="18" t="inlineStr">
+        <is>
+          <t>The essay that imagined the web and the personal machine for managing information.</t>
+        </is>
+      </c>
+      <c r="S82" s="18" t="n"/>
+      <c r="T82" s="18" t="inlineStr">
+        <is>
+          <t>The Atlantic refuses scripts. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B83" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="D83" s="18" t="inlineStr">
+        <is>
+          <t>31 August</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
+          <t>1955-08-31</t>
+        </is>
+      </c>
+      <c r="F83" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>A Proposal for the Dartmouth Summer Research Project on Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
+          <t>John McCarthy, Marvin Minsky, Nathaniel Rochester, Claude Shannon</t>
+        </is>
+      </c>
+      <c r="I83" s="18" t="n"/>
+      <c r="J83" s="18" t="n"/>
+      <c r="K83" s="18" t="inlineStr">
+        <is>
+          <t>Stanford University, John McCarthy archive</t>
+        </is>
+      </c>
+      <c r="L83" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M83" s="18" t="inlineStr">
+        <is>
+          <t>state capacity and competence</t>
+        </is>
+      </c>
+      <c r="N83" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O83" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P83" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q83" s="18" t="inlineStr">
+        <is>
+          <t>http://jmc.stanford.edu/articles/dartmouth/dartmouth.pdf</t>
+        </is>
+      </c>
+      <c r="R83" s="18" t="inlineStr">
+        <is>
+          <t>The proposal that gave the field its name.</t>
+        </is>
+      </c>
+      <c r="S83" s="18" t="n"/>
+      <c r="T83" s="18" t="inlineStr">
+        <is>
+          <t>PDF; text not machine-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="n">
+        <v>1970</v>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="inlineStr">
+        <is>
+          <t>31 December</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>1974-12-31</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>Privacy Act of 1974</t>
+        </is>
+      </c>
+      <c r="H84" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="n"/>
+      <c r="J84" s="18" t="n"/>
+      <c r="K84" s="18" t="inlineStr">
+        <is>
+          <t>Pub. L. 93-579, GovInfo</t>
+        </is>
+      </c>
+      <c r="L84" s="18" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="M84" s="18" t="inlineStr">
+        <is>
+          <t>surveillance</t>
+        </is>
+      </c>
+      <c r="N84" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O84" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P84" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q84" s="18" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/STATUTE-88/pdf/STATUTE-88-Pg1896.pdf</t>
+        </is>
+      </c>
+      <c r="R84" s="18" t="inlineStr">
+        <is>
+          <t>The first U.S. law on what the government may do with personal data.</t>
+        </is>
+      </c>
+      <c r="S84" s="18" t="n"/>
+      <c r="T84" s="18" t="inlineStr">
+        <is>
+          <t>PDF; text not machine-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B85" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="D85" s="18" t="inlineStr">
+        <is>
+          <t>8 February</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>1996-02-08</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>47 U.S. Code Section 230: Protection for private blocking and screening of offensive material</t>
+        </is>
+      </c>
+      <c r="H85" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="I85" s="18" t="n"/>
+      <c r="J85" s="18" t="n"/>
+      <c r="K85" s="18" t="inlineStr">
+        <is>
+          <t>Legal Information Institute, Cornell Law School</t>
+        </is>
+      </c>
+      <c r="L85" s="18" t="inlineStr">
+        <is>
+          <t>The Media</t>
+        </is>
+      </c>
+      <c r="M85" s="18" t="inlineStr">
+        <is>
+          <t>platforms and attention</t>
+        </is>
+      </c>
+      <c r="N85" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O85" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P85" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q85" s="18" t="inlineStr">
+        <is>
+          <t>https://www.law.cornell.edu/uscode/text/47/230</t>
+        </is>
+      </c>
+      <c r="R85" s="18" t="inlineStr">
+        <is>
+          <t>The liability shield for online platforms, the legal basis of the modern internet.</t>
+        </is>
+      </c>
+      <c r="S85" s="18" t="n"/>
+      <c r="T85" s="18" t="inlineStr">
+        <is>
+          <t>Cornell LII is a legal library. Passed as part of the Telecommunications Act, already in the matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>27 April</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G86" s="18" t="inlineStr">
+        <is>
+          <t>General Data Protection Regulation</t>
+        </is>
+      </c>
+      <c r="H86" s="18" t="inlineStr">
+        <is>
+          <t>European Parliament and Council</t>
+        </is>
+      </c>
+      <c r="I86" s="18" t="n"/>
+      <c r="J86" s="18" t="n"/>
+      <c r="K86" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex</t>
+        </is>
+      </c>
+      <c r="L86" s="18" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="M86" s="18" t="inlineStr">
+        <is>
+          <t>surveillance</t>
+        </is>
+      </c>
+      <c r="N86" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O86" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P86" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q86" s="18" t="inlineStr">
+        <is>
+          <t>https://eur-lex.europa.eu/eli/reg/2016/679/oj</t>
+        </is>
+      </c>
+      <c r="R86" s="18" t="inlineStr">
+        <is>
+          <t>The European model for data privacy that U.S. states and companies answer to.</t>
+        </is>
+      </c>
+      <c r="S86" s="18" t="n"/>
+      <c r="T86" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex returns a script challenge. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D87" s="18" t="inlineStr">
+        <is>
+          <t>30 October</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>2023-10-30</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G87" s="18" t="inlineStr">
+        <is>
+          <t>Executive Order 14110: Safe, Secure, and Trustworthy Development and Use of Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="H87" s="18" t="inlineStr">
+        <is>
+          <t>Joe Biden</t>
+        </is>
+      </c>
+      <c r="I87" s="18" t="n"/>
+      <c r="J87" s="18" t="n"/>
+      <c r="K87" s="18" t="inlineStr">
+        <is>
+          <t>Federal Register</t>
+        </is>
+      </c>
+      <c r="L87" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M87" s="18" t="inlineStr">
+        <is>
+          <t>regulation and the administrative state</t>
+        </is>
+      </c>
+      <c r="N87" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O87" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P87" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q87" s="18" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2023/11/01/2023-24283/safe-secure-and-trustworthy-development-and-use-of-artificial-intelligence</t>
+        </is>
+      </c>
+      <c r="R87" s="18" t="inlineStr">
+        <is>
+          <t>The first broad U.S. executive action on AI safety.</t>
+        </is>
+      </c>
+      <c r="S87" s="18" t="n"/>
+      <c r="T87" s="18" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>13 June</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G88" s="18" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2024/1689 (the AI Act)</t>
+        </is>
+      </c>
+      <c r="H88" s="18" t="inlineStr">
+        <is>
+          <t>European Parliament and Council</t>
+        </is>
+      </c>
+      <c r="I88" s="18" t="n"/>
+      <c r="J88" s="18" t="n"/>
+      <c r="K88" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex</t>
+        </is>
+      </c>
+      <c r="L88" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M88" s="18" t="inlineStr">
+        <is>
+          <t>regulation and the administrative state</t>
+        </is>
+      </c>
+      <c r="N88" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O88" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P88" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q88" s="18" t="inlineStr">
+        <is>
+          <t>https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
+        </is>
+      </c>
+      <c r="R88" s="18" t="inlineStr">
+        <is>
+          <t>The first comprehensive law on AI, in force in Europe.</t>
+        </is>
+      </c>
+      <c r="S88" s="18" t="n"/>
+      <c r="T88" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex returns a script challenge. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D89" s="18" t="inlineStr">
+        <is>
+          <t>23 January</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="F89" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G89" s="18" t="inlineStr">
+        <is>
+          <t>Executive Order 14179: Removing Barriers to American Leadership in Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="I89" s="18" t="n"/>
+      <c r="J89" s="18" t="n"/>
+      <c r="K89" s="18" t="inlineStr">
+        <is>
+          <t>Federal Register</t>
+        </is>
+      </c>
+      <c r="L89" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M89" s="18" t="inlineStr">
+        <is>
+          <t>regulation and the administrative state</t>
+        </is>
+      </c>
+      <c r="N89" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O89" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P89" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q89" s="18" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2025/01/31/2025-02172/removing-barriers-to-american-leadership-in-artificial-intelligence</t>
+        </is>
+      </c>
+      <c r="R89" s="18" t="inlineStr">
+        <is>
+          <t>Reverses the 2023 order; the swing in U.S. AI policy.</t>
+        </is>
+      </c>
+      <c r="S89" s="18" t="n"/>
+      <c r="T89" s="18" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr">
+        <is>
+          <t>5 December</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>1994-12-05</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G90" s="18" t="inlineStr">
+        <is>
+          <t>Memorandum on Security Assurances in connection with Ukraine's accession to the Treaty on the Non-Proliferation of Nuclear Weapons (Budapest Memorandum)</t>
+        </is>
+      </c>
+      <c r="H90" s="18" t="inlineStr">
+        <is>
+          <t>Russia, the United Kingdom, the United States and Ukraine</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="n"/>
+      <c r="J90" s="18" t="n"/>
+      <c r="K90" s="18" t="inlineStr">
+        <is>
+          <t>UN document A/49/765</t>
+        </is>
+      </c>
+      <c r="L90" s="18" t="inlineStr">
+        <is>
+          <t>The Bomb</t>
+        </is>
+      </c>
+      <c r="M90" s="18" t="inlineStr">
+        <is>
+          <t>arms control and treaties</t>
+        </is>
+      </c>
+      <c r="N90" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O90" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P90" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q90" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/49/765</t>
+        </is>
+      </c>
+      <c r="R90" s="18" t="inlineStr">
+        <is>
+          <t>Ukraine gave up its nuclear weapons for assurances Russia later broke.</t>
+        </is>
+      </c>
+      <c r="S90" s="18" t="n"/>
+      <c r="T90" s="18" t="inlineStr">
+        <is>
+          <t>UN viewers are JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B91" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="D91" s="18" t="inlineStr">
+        <is>
+          <t>27 May</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="inlineStr">
+        <is>
+          <t>1997-05-27</t>
+        </is>
+      </c>
+      <c r="F91" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G91" s="18" t="inlineStr">
+        <is>
+          <t>Founding Act on Mutual Relations, Cooperation and Security between NATO and the Russian Federation</t>
+        </is>
+      </c>
+      <c r="H91" s="18" t="inlineStr">
+        <is>
+          <t>NATO and Russia</t>
+        </is>
+      </c>
+      <c r="I91" s="18" t="n"/>
+      <c r="J91" s="18" t="n"/>
+      <c r="K91" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L91" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M91" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N91" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O91" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P91" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q91" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/official_texts_25468.htm</t>
+        </is>
+      </c>
+      <c r="R91" s="18" t="inlineStr">
+        <is>
+          <t>The agreement Russia now says NATO broke.</t>
+        </is>
+      </c>
+      <c r="S91" s="18" t="n"/>
+      <c r="T91" s="18" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D92" s="18" t="inlineStr">
+        <is>
+          <t>10 February</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="inlineStr">
+        <is>
+          <t>2007-02-10</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G92" s="18" t="inlineStr">
+        <is>
+          <t>Speech and the Following Discussion at the Munich Conference on Security Policy</t>
+        </is>
+      </c>
+      <c r="H92" s="18" t="inlineStr">
+        <is>
+          <t>Vladimir Putin</t>
+        </is>
+      </c>
+      <c r="I92" s="18" t="n"/>
+      <c r="J92" s="18" t="n"/>
+      <c r="K92" s="18" t="inlineStr">
+        <is>
+          <t>President of Russia, English</t>
+        </is>
+      </c>
+      <c r="L92" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M92" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N92" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O92" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P92" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q92" s="18" t="inlineStr">
+        <is>
+          <t>http://en.kremlin.ru/events/president/transcripts/24034</t>
+        </is>
+      </c>
+      <c r="R92" s="18" t="inlineStr">
+        <is>
+          <t>Putin's break with the West, years before Ukraine.</t>
+        </is>
+      </c>
+      <c r="S92" s="18" t="n"/>
+      <c r="T92" s="18" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="18" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D93" s="18" t="inlineStr">
+        <is>
+          <t>18 March</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="inlineStr">
+        <is>
+          <t>2014-03-18</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G93" s="18" t="inlineStr">
+        <is>
+          <t>Address by President of the Russian Federation (Crimea)</t>
+        </is>
+      </c>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>Vladimir Putin</t>
+        </is>
+      </c>
+      <c r="I93" s="18" t="n"/>
+      <c r="J93" s="18" t="n"/>
+      <c r="K93" s="18" t="inlineStr">
+        <is>
+          <t>President of Russia, English</t>
+        </is>
+      </c>
+      <c r="L93" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M93" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N93" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O93" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P93" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q93" s="18" t="inlineStr">
+        <is>
+          <t>http://en.kremlin.ru/events/president/news/20603</t>
+        </is>
+      </c>
+      <c r="R93" s="18" t="inlineStr">
+        <is>
+          <t>The annexation of Crimea.</t>
+        </is>
+      </c>
+      <c r="S93" s="18" t="n"/>
+      <c r="T93" s="18" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="18" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D94" s="18" t="inlineStr">
+        <is>
+          <t>24 February</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G94" s="18" t="inlineStr">
+        <is>
+          <t>Address by the President of the Russian Federation</t>
+        </is>
+      </c>
+      <c r="H94" s="18" t="inlineStr">
+        <is>
+          <t>Vladimir Putin</t>
+        </is>
+      </c>
+      <c r="I94" s="18" t="n"/>
+      <c r="J94" s="18" t="n"/>
+      <c r="K94" s="18" t="inlineStr">
+        <is>
+          <t>President of Russia, English</t>
+        </is>
+      </c>
+      <c r="L94" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M94" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N94" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O94" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P94" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q94" s="18" t="inlineStr">
+        <is>
+          <t>http://en.kremlin.ru/events/president/transcripts/67843</t>
+        </is>
+      </c>
+      <c r="R94" s="18" t="inlineStr">
+        <is>
+          <t>The announcement of the full invasion of Ukraine.</t>
+        </is>
+      </c>
+      <c r="S94" s="18" t="n"/>
+      <c r="T94" s="18" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="18" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="B95" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="D95" s="18" t="inlineStr">
+        <is>
+          <t>19 December</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="inlineStr">
+        <is>
+          <t>1984-12-19</t>
+        </is>
+      </c>
+      <c r="F95" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G95" s="18" t="inlineStr">
+        <is>
+          <t>Joint Declaration of the Government of the United Kingdom and the Government of the People's Republic of China on the Question of Hong Kong</t>
+        </is>
+      </c>
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>United Kingdom and the People's Republic of China</t>
+        </is>
+      </c>
+      <c r="I95" s="18" t="n"/>
+      <c r="J95" s="18" t="n"/>
+      <c r="K95" s="18" t="inlineStr">
+        <is>
+          <t>UN Treaty Series / UK Government</t>
+        </is>
+      </c>
+      <c r="L95" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M95" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N95" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O95" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P95" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q95" s="18" t="inlineStr">
+        <is>
+          <t>https://treaties.un.org/doc/Publication/UNTS/Volume%201399/volume-1399-I-23391-English.pdf</t>
+        </is>
+      </c>
+      <c r="R95" s="18" t="inlineStr">
+        <is>
+          <t>The 'one country, two systems' promise behind the Hong Kong protests.</t>
+        </is>
+      </c>
+      <c r="S95" s="18" t="n"/>
+      <c r="T95" s="18" t="inlineStr">
+        <is>
+          <t>PDF; text not machine-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="B96" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D96" s="18" t="inlineStr">
+        <is>
+          <t>20 July</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>2017-07-20</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G96" s="18" t="inlineStr">
+        <is>
+          <t>A Next Generation Artificial Intelligence Development Plan</t>
+        </is>
+      </c>
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>State Council of the People's Republic of China</t>
+        </is>
+      </c>
+      <c r="I96" s="18" t="n"/>
+      <c r="J96" s="18" t="n"/>
+      <c r="K96" s="18" t="inlineStr">
+        <is>
+          <t>DigiChina, Stanford University (translation)</t>
+        </is>
+      </c>
+      <c r="L96" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M96" s="18" t="inlineStr">
+        <is>
+          <t>state capacity and competence</t>
+        </is>
+      </c>
+      <c r="N96" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O96" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P96" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q96" s="18" t="inlineStr">
+        <is>
+          <t>https://digichina.stanford.edu/work/full-translation-chinas-new-generation-artificial-intelligence-development-plan-2017/</t>
+        </is>
+      </c>
+      <c r="R96" s="18" t="inlineStr">
+        <is>
+          <t>China's plan to lead the world in AI by 2030.</t>
+        </is>
+      </c>
+      <c r="S96" s="18" t="n"/>
+      <c r="T96" s="18" t="inlineStr">
+        <is>
+          <t>Translation hosted by a university project; no official English text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="B97" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D97" s="18" t="inlineStr">
+        <is>
+          <t>15 January</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="F97" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G97" s="18" t="inlineStr">
+        <is>
+          <t>Economic and Trade Agreement between the Government of the United States and the Government of the People's Republic of China (Phase One)</t>
+        </is>
+      </c>
+      <c r="H97" s="18" t="inlineStr">
+        <is>
+          <t>United States and China</t>
+        </is>
+      </c>
+      <c r="I97" s="18" t="n"/>
+      <c r="J97" s="18" t="n"/>
+      <c r="K97" s="18" t="inlineStr">
+        <is>
+          <t>Office of the United States Trade Representative</t>
+        </is>
+      </c>
+      <c r="L97" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M97" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N97" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O97" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P97" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q97" s="18" t="inlineStr">
+        <is>
+          <t>https://ustr.gov/phase-one</t>
+        </is>
+      </c>
+      <c r="R97" s="18" t="inlineStr">
+        <is>
+          <t>The 2020 trade truce, and the commitments China did not meet.</t>
+        </is>
+      </c>
+      <c r="S97" s="18" t="n"/>
+      <c r="T97" s="18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5455,35 +11367,35 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>A lens (a country, an alliance, a technology) is a tag on an object like Column E's Issue (Theme), but on a different axis: Column E says which American argument an object belongs to; a lens says who or what it is about. An object can have one theme and several lenses.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>The objects follow the same rules as every matrix object: a primary text, a verified outward link, the link checker. What differs is the selection rule: a row's Beginnings are spread across time before its start year; a lens's are the three nearest before the story's origin. One kind of data, two rules, both in code.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>For now lenses stay in editorial/lenses.json and these candidates carry a Lens column. A Lens column in the matrix itself (blank NTK Row allowed for purely foreign objects) is the likely end state. It changes the matrix schema, so it waits for a decision.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>A lens needs at least three linked objects before a story's origin to produce Beginnings. Fewer, and the page shows the origin alone: a thin lens is a to-do, not a failure.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -5527,7 +11439,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
@@ -5546,7 +11458,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
@@ -5565,7 +11477,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>
@@ -5622,7 +11534,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr"/>
     </row>
@@ -5641,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr"/>
     </row>
@@ -5660,7 +11572,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr"/>
     </row>
@@ -5717,7 +11629,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr"/>
     </row>
@@ -5736,7 +11648,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" t="inlineStr"/>
     </row>
@@ -5755,7 +11667,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="inlineStr"/>
     </row>
@@ -5774,7 +11686,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" t="inlineStr"/>
     </row>
@@ -5793,7 +11705,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E22" t="inlineStr"/>
     </row>
@@ -5812,7 +11724,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" t="inlineStr"/>
     </row>
@@ -5831,7 +11743,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" t="inlineStr"/>
     </row>
@@ -5850,7 +11762,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" t="inlineStr"/>
     </row>
@@ -5869,7 +11781,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E26" t="inlineStr"/>
     </row>
@@ -5888,7 +11800,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E27" t="inlineStr"/>
     </row>
@@ -5907,7 +11819,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E28" t="inlineStr"/>
     </row>
@@ -5926,7 +11838,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E29" t="inlineStr"/>
     </row>
@@ -5964,7 +11876,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" t="inlineStr"/>
     </row>
@@ -5983,7 +11895,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E32" t="inlineStr"/>
     </row>

--- a/editorial/NTK_Backstory_Candidates.xlsx
+++ b/editorial/NTK_Backstory_Candidates.xlsx
@@ -7,6 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Candidates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lens candidates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Lenses" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -15,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <color indexed="8"/>
@@ -36,6 +38,9 @@
       <b val="1"/>
       <color indexed="8"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -176,7 +181,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -235,6 +240,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2973,4 +2979,8927 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T97"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" style="17" min="1" max="1"/>
+    <col width="8" customWidth="1" style="17" min="2" max="2"/>
+    <col width="6" customWidth="1" style="17" min="3" max="3"/>
+    <col width="12" customWidth="1" style="17" min="4" max="4"/>
+    <col width="11" customWidth="1" style="17" min="5" max="5"/>
+    <col width="34" customWidth="1" style="17" min="6" max="6"/>
+    <col width="54" customWidth="1" style="17" min="7" max="7"/>
+    <col width="34" customWidth="1" style="17" min="8" max="8"/>
+    <col width="6" customWidth="1" style="17" min="9" max="9"/>
+    <col width="6" customWidth="1" style="17" min="10" max="10"/>
+    <col width="40" customWidth="1" style="17" min="11" max="11"/>
+    <col width="14" customWidth="1" style="17" min="12" max="12"/>
+    <col width="24" customWidth="1" style="17" min="13" max="13"/>
+    <col width="18" customWidth="1" style="17" min="14" max="14"/>
+    <col width="11" customWidth="1" style="17" min="15" max="15"/>
+    <col width="12" customWidth="1" style="17" min="16" max="16"/>
+    <col width="60" customWidth="1" style="17" min="17" max="17"/>
+    <col width="60" customWidth="1" style="17" min="18" max="18"/>
+    <col width="9" customWidth="1" style="17" min="19" max="19"/>
+    <col width="60" customWidth="1" style="17" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Decade</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Day / Month</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>Sort Date</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Issue (Theme)</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>Pg. No.</t>
+        </is>
+      </c>
+      <c r="J1" s="20" t="inlineStr">
+        <is>
+          <t>Vol.</t>
+        </is>
+      </c>
+      <c r="K1" s="20" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="L1" s="20" t="inlineStr">
+        <is>
+          <t>NTK Row</t>
+        </is>
+      </c>
+      <c r="M1" s="20" t="inlineStr">
+        <is>
+          <t>Sub-genre</t>
+        </is>
+      </c>
+      <c r="N1" s="20" t="inlineStr">
+        <is>
+          <t>Era</t>
+        </is>
+      </c>
+      <c r="O1" s="20" t="inlineStr">
+        <is>
+          <t>Date Status</t>
+        </is>
+      </c>
+      <c r="P1" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Q1" s="20" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="R1" s="20" t="inlineStr">
+        <is>
+          <t>Why it's here</t>
+        </is>
+      </c>
+      <c r="S1" s="20" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="T1" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n">
+        <v>1910</v>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>2 November</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>1917-11-02</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>Balfour Declaration</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="inlineStr">
+        <is>
+          <t>Arthur James Balfour</t>
+        </is>
+      </c>
+      <c r="I2" s="18" t="n"/>
+      <c r="J2" s="18" t="n"/>
+      <c r="K2" s="18" t="inlineStr">
+        <is>
+          <t>Letter to Lord Rothschild, British Foreign Office (Avalon Project, Yale)</t>
+        </is>
+      </c>
+      <c r="L2" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M2" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N2" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O2" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P2" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q2" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/balfour.asp</t>
+        </is>
+      </c>
+      <c r="R2" s="18" t="inlineStr">
+        <is>
+          <t>Britain's statement of support for a Jewish national home in Palestine; the earliest document most later ones answer.</t>
+        </is>
+      </c>
+      <c r="S2" s="18" t="n"/>
+      <c r="T2" s="18" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>29 November</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>1947-11-29</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>UN General Assembly Resolution 181 (II): Future Government of Palestine (the Partition Plan)</t>
+        </is>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
+        <is>
+          <t>United Nations General Assembly</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="18" t="n"/>
+      <c r="K3" s="18" t="inlineStr">
+        <is>
+          <t>UN Information System on the Question of Palestine (UNISPAL)</t>
+        </is>
+      </c>
+      <c r="L3" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N3" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O3" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P3" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q3" s="18" t="inlineStr">
+        <is>
+          <t>https://www.un.org/unispal/document/auto-insert-185393/</t>
+        </is>
+      </c>
+      <c r="R3" s="18" t="inlineStr">
+        <is>
+          <t>The UN vote to divide Palestine into a Jewish and an Arab state; the legal starting point for both sides' claims.</t>
+        </is>
+      </c>
+      <c r="S3" s="18" t="n"/>
+      <c r="T3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>14 May</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>1948-05-14</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>Declaration of the Establishment of the State of Israel</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Provisional Council of State (David Ben-Gurion)</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="18" t="n"/>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M4" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O4" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P4" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q4" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/israel.asp</t>
+        </is>
+      </c>
+      <c r="R4" s="18" t="inlineStr">
+        <is>
+          <t>Israel's founding statement, issued the day the British Mandate ended.</t>
+        </is>
+      </c>
+      <c r="S4" s="18" t="n"/>
+      <c r="T4" s="18" t="inlineStr">
+        <is>
+          <t>The Knesset's own page was down during the check, so this links Avalon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>22 November</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>1967-11-22</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 242</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="n"/>
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O5" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P5" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q5" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/un242.asp</t>
+        </is>
+      </c>
+      <c r="R5" s="18" t="inlineStr">
+        <is>
+          <t>The land-for-peace resolution after the Six-Day War; cited in nearly every later negotiation.</t>
+        </is>
+      </c>
+      <c r="S5" s="18" t="n"/>
+      <c r="T5" s="18" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>18 August</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>1988-08-18</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>Covenant of the Islamic Resistance Movement (Hamas)</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>Hamas</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>Hamas founding charter, English translation (Avalon Project, Yale)</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O6" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P6" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q6" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/hamas.asp</t>
+        </is>
+      </c>
+      <c r="R6" s="18" t="inlineStr">
+        <is>
+          <t>Hamas's founding text: the other side's own statement of aims, set beside Israel's Declaration.</t>
+        </is>
+      </c>
+      <c r="S6" s="18" t="n"/>
+      <c r="T6" s="18" t="inlineStr">
+        <is>
+          <t>SENSITIVE: your call whether to include. Hamas issued a revised document in 2017.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>13 September</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>1993-09-13</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Declaration of Principles on Interim Self-Government Arrangements (Oslo I)</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>Israel and the Palestine Liberation Organization</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M7" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O7" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P7" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q7" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/isrplo.asp</t>
+        </is>
+      </c>
+      <c r="R7" s="18" t="inlineStr">
+        <is>
+          <t>The first agreement in which Israel and the PLO recognized each other; the framework of the peace process.</t>
+        </is>
+      </c>
+      <c r="S7" s="18" t="n"/>
+      <c r="T7" s="18" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>1970</v>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>3 December</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>1979-12-03</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Islamic Republic of Iran (as amended 1989)</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>Islamic Republic of Iran</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N8" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O8" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P8" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q8" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Iran_1989</t>
+        </is>
+      </c>
+      <c r="R8" s="18" t="inlineStr">
+        <is>
+          <t>Iran's governing text since the revolution; defines the Supreme Leader's role the news keeps returning to.</t>
+        </is>
+      </c>
+      <c r="S8" s="18" t="n"/>
+      <c r="T8" s="18" t="inlineStr">
+        <is>
+          <t>Constitute is a repository of official translations, not a government site. Date is when the 1979 constitution was approved; the text is the 1989 amended version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>19 January</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>1981-01-19</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Algiers Accords: General Declaration</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Government of Algeria, for Iran and the United States</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>Iran-United States Claims Tribunal</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O9" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P9" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q9" s="18" t="inlineStr">
+        <is>
+          <t>https://iusct.com/wp-content/uploads/2021/02/1-General-Declaration_.pdf</t>
+        </is>
+      </c>
+      <c r="R9" s="18" t="inlineStr">
+        <is>
+          <t>The agreement that ended the hostage crisis; it also pledged non-interference in Iran's internal affairs.</t>
+        </is>
+      </c>
+      <c r="S9" s="18" t="n"/>
+      <c r="T9" s="18" t="inlineStr">
+        <is>
+          <t>Hosted by the tribunal the accords created.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>20 July</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>1987-07-20</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 598</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/598(1987)</t>
+        </is>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O10" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P10" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q10" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/598(1987)</t>
+        </is>
+      </c>
+      <c r="R10" s="18" t="inlineStr">
+        <is>
+          <t>The ceasefire resolution that ended the Iran-Iraq war.</t>
+        </is>
+      </c>
+      <c r="S10" s="18" t="n"/>
+      <c r="T10" s="18" t="inlineStr">
+        <is>
+          <t>The UN document viewer is JavaScript and the check could not read it. Open to confirm it is the right resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>14 July</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Joint Comprehensive Plan of Action</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>Iran, China, France, Germany, Russia, United Kingdom, United States and the EU</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Department of State, text of the agreement</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P11" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q11" s="18" t="inlineStr">
+        <is>
+          <t>https://2009-2017.state.gov/documents/organization/245317.pdf</t>
+        </is>
+      </c>
+      <c r="R11" s="18" t="inlineStr">
+        <is>
+          <t>The 2015 nuclear deal: what it limited, and what the 2018 withdrawal ended.</t>
+        </is>
+      </c>
+      <c r="S11" s="18" t="n"/>
+      <c r="T11" s="18" t="inlineStr">
+        <is>
+          <t>PDF opened (200); text not machine-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>8 May</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>2018-05-08</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>National Security Presidential Memorandum on Ceasing United States Participation in the JCPOA</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>Public Papers of the Presidents (American Presidency Project)</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N12" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O12" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P12" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q12" s="18" t="inlineStr">
+        <is>
+          <t>https://www.presidency.ucsb.edu/documents/national-security-presidential-memorandum-ceasing-united-states-participation-the-joint</t>
+        </is>
+      </c>
+      <c r="R12" s="18" t="inlineStr">
+        <is>
+          <t>The order that withdrew the United States from the deal; the proximate cause of later escalation.</t>
+        </is>
+      </c>
+      <c r="S12" s="18" t="n"/>
+      <c r="T12" s="18" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n">
+        <v>1810</v>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>28 April</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>1817-04-28</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>Rush-Bagot Agreement</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>Richard Rush and Charles Bagot</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>Exchange of notes; Treaty Law Division, Government of Canada</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O13" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P13" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q13" s="18" t="inlineStr">
+        <is>
+          <t>https://www.treaty-accord.gc.ca/text-texte.aspx?id=101662</t>
+        </is>
+      </c>
+      <c r="R13" s="18" t="inlineStr">
+        <is>
+          <t>The demilitarization of the Great Lakes; the first step toward the undefended border.</t>
+        </is>
+      </c>
+      <c r="S13" s="18" t="n"/>
+      <c r="T13" s="18" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>18 August</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>1940-08-18</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>Ogdensburg Agreement: Joint Statement on Defence</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>Franklin D. Roosevelt and W. L. Mackenzie King</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>Joint statement issued at Ogdensburg, New York (Ruhr University Bochum source collection)</t>
+        </is>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N14" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O14" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P14" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q14" s="18" t="inlineStr">
+        <is>
+          <t>https://www.ruhr-uni-bochum.de/gna/Quellensammlung/09/09_jointstatementissuedatOgdensburg_1940.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="18" t="inlineStr">
+        <is>
+          <t>The agreement that made the two countries one defence partnership.</t>
+        </is>
+      </c>
+      <c r="S14" s="18" t="n"/>
+      <c r="T14" s="18" t="inlineStr">
+        <is>
+          <t>Weakest host in the round: a German university's document collection, not an archive. Prefer a Library and Archives Canada or FDR Library copy if you know one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>17 April</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>1982-04-17</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>Constitution Act, 1982 (with the Canadian Charter of Rights and Freedoms)</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>Parliament of Canada</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>Justice Laws Website, Government of Canada</t>
+        </is>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O15" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P15" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q15" s="18" t="inlineStr">
+        <is>
+          <t>https://laws-lois.justice.gc.ca/eng/const/page-12.html</t>
+        </is>
+      </c>
+      <c r="R15" s="18" t="inlineStr">
+        <is>
+          <t>Canada's own founding text, patriated in 1982; the neighbour's constitutional model.</t>
+        </is>
+      </c>
+      <c r="S15" s="18" t="n"/>
+      <c r="T15" s="18" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>2 January</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>1988-01-02</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>Canada-United States Free Trade Agreement</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>Governments of Canada and the United States</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>Text of the agreement, Global Affairs Canada</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N16" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O16" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P16" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q16" s="18" t="inlineStr">
+        <is>
+          <t>https://www.international.gc.ca/trade-commerce/assets/pdfs/agreements-accords/cusfta-e.pdf</t>
+        </is>
+      </c>
+      <c r="R16" s="18" t="inlineStr">
+        <is>
+          <t>The agreement that began today's integrated North American economy.</t>
+        </is>
+      </c>
+      <c r="S16" s="18" t="n"/>
+      <c r="T16" s="18" t="inlineStr">
+        <is>
+          <t>10 MB PDF opened (200); text not machine-checked. Alternative: the U.S. House document at govinfo (H. Doc. 100-216).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>30 November</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>2018-11-30</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>United States-Mexico-Canada Agreement</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Governments of the United States, Mexico and Canada</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>Office of the United States Trade Representative</t>
+        </is>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M17" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N17" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O17" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P17" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q17" s="18" t="inlineStr">
+        <is>
+          <t>https://ustr.gov/trade-agreements/free-trade-agreements/united-states-mexico-canada-agreement/agreement-between</t>
+        </is>
+      </c>
+      <c r="R17" s="18" t="inlineStr">
+        <is>
+          <t>The trade pact now under strain.</t>
+        </is>
+      </c>
+      <c r="S17" s="18" t="n"/>
+      <c r="T17" s="18" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>1 February</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>Executive Order 14193: Imposing Duties To Address the Flow of Illicit Drugs Across Our Northern Border</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>Federal Register</t>
+        </is>
+      </c>
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N18" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O18" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P18" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q18" s="18" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2025/02/07/2025-02406/imposing-duties-to-address-the-flow-of-illicit-drugs-across-our-northern-border</t>
+        </is>
+      </c>
+      <c r="R18" s="18" t="inlineStr">
+        <is>
+          <t>The first tariffs on Canada of the second Trump term.</t>
+        </is>
+      </c>
+      <c r="S18" s="18" t="n"/>
+      <c r="T18" s="18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>4 April</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>1949-04-04</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>The North Atlantic Treaty</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>Parties to the North Atlantic Treaty</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M19" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N19" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O19" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P19" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q19" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/official_texts_17120.htm</t>
+        </is>
+      </c>
+      <c r="R19" s="18" t="inlineStr">
+        <is>
+          <t>The founding text, including the Article 5 mutual defence pledge.</t>
+        </is>
+      </c>
+      <c r="S19" s="18" t="n"/>
+      <c r="T19" s="18" t="inlineStr">
+        <is>
+          <t>The matrix already holds two 1949 speeches on the treaty with no link; this is the treaty itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>14 December</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>1967-12-14</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>The Future Tasks of the Alliance (the Harmel Report)</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>North Atlantic Council</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L20" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N20" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O20" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P20" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q20" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/official_texts_26700.htm</t>
+        </is>
+      </c>
+      <c r="R20" s="18" t="inlineStr">
+        <is>
+          <t>The statement that paired deterrence with detente and set NATO's course for decades.</t>
+        </is>
+      </c>
+      <c r="S20" s="18" t="n"/>
+      <c r="T20" s="18" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>12 September</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>2001-09-12</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>Statement by the North Atlantic Council (Article 5 and the 11 September attacks)</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>North Atlantic Council</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L21" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M21" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N21" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O21" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P21" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q21" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/official_texts_18553.htm</t>
+        </is>
+      </c>
+      <c r="R21" s="18" t="inlineStr">
+        <is>
+          <t>The first and only time Article 5 has been invoked.</t>
+        </is>
+      </c>
+      <c r="S21" s="18" t="n"/>
+      <c r="T21" s="18" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>5 September</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>Wales Summit Declaration</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>Heads of State and Government, North Atlantic Council</t>
+        </is>
+      </c>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L22" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M22" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N22" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O22" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P22" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q22" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/official_texts_112964.htm</t>
+        </is>
+      </c>
+      <c r="R22" s="18" t="inlineStr">
+        <is>
+          <t>The pledge to spend two percent of GDP on defence, after Russia's seizure of Crimea.</t>
+        </is>
+      </c>
+      <c r="S22" s="18" t="n"/>
+      <c r="T22" s="18" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>25 June</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>The Hague Summit Declaration</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>Heads of State and Government, North Atlantic Council</t>
+        </is>
+      </c>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L23" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M23" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N23" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O23" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P23" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q23" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/en/about-us/official-texts-and-resources/official-texts/2025/06/25/the-hague-summit-declaration</t>
+        </is>
+      </c>
+      <c r="R23" s="18" t="inlineStr">
+        <is>
+          <t>The new commitment: 3.5% of GDP on core defence plus 1.5% on related spending, by 2035.</t>
+        </is>
+      </c>
+      <c r="S23" s="18" t="n"/>
+      <c r="T23" s="18" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>1780</v>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>26 August</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>1789-08-26</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>Declaration of the Rights of Man and of the Citizen</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>National Constituent Assembly</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L24" s="18" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="M24" s="18" t="inlineStr">
+        <is>
+          <t>civil rights law</t>
+        </is>
+      </c>
+      <c r="N24" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O24" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P24" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q24" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/18th_century/rightsof.asp</t>
+        </is>
+      </c>
+      <c r="R24" s="18" t="inlineStr">
+        <is>
+          <t>France's founding statement of rights and popular sovereignty; the language of every later protest.</t>
+        </is>
+      </c>
+      <c r="S24" s="18" t="n"/>
+      <c r="T24" s="18" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>4 October</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>1958-10-04</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of 4 October 1958 (the Fifth Republic)</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>French Republic</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="inlineStr">
+        <is>
+          <t>Constitutional Council of France, English translation</t>
+        </is>
+      </c>
+      <c r="L25" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M25" s="18" t="inlineStr">
+        <is>
+          <t>executive power</t>
+        </is>
+      </c>
+      <c r="N25" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O25" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P25" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q25" s="18" t="inlineStr">
+        <is>
+          <t>https://www.conseil-constitutionnel.fr/en/constitution-of-4-october-1958</t>
+        </is>
+      </c>
+      <c r="R25" s="18" t="inlineStr">
+        <is>
+          <t>The text that gave France its strong presidency and Article 49.3, the tool used to pass the 2023 pension reform and budgets.</t>
+        </is>
+      </c>
+      <c r="S25" s="18" t="n"/>
+      <c r="T25" s="18" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>7 March</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>1966-03-07</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>Letter from President de Gaulle to President Johnson on France's withdrawal from NATO's integrated command</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>Charles de Gaulle</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>Foreign Relations of the United States, 1964-1968, Vol. XIII</t>
+        </is>
+      </c>
+      <c r="L26" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M26" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N26" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O26" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P26" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q26" s="18" t="inlineStr">
+        <is>
+          <t>https://history.state.gov/historicaldocuments/frus1964-68v13/d137</t>
+        </is>
+      </c>
+      <c r="R26" s="18" t="inlineStr">
+        <is>
+          <t>France leaves NATO's command structure but not the alliance.</t>
+        </is>
+      </c>
+      <c r="S26" s="18" t="n"/>
+      <c r="T26" s="18" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>14 February</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>2003-02-14</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>Statement by Dominique de Villepin to the UN Security Council on Iraq</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>Dominique de Villepin</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council verbatim record S/PV.4701</t>
+        </is>
+      </c>
+      <c r="L27" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M27" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N27" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O27" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P27" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q27" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/PV.4701</t>
+        </is>
+      </c>
+      <c r="R27" s="18" t="inlineStr">
+        <is>
+          <t>The French case against the Iraq war, and the sharpest moment of the transatlantic split.</t>
+        </is>
+      </c>
+      <c r="S27" s="18" t="n"/>
+      <c r="T27" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; could not be read. A text copy is at the Global Policy Forum archive: https://archive.globalpolicy.org/political-issues-in-iraq/important-documents-on-iraq/34911.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>17 April</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>Adresse aux Français (address on the pension reform)</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
+          <t>Emmanuel Macron</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>Elysee, official site</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M28" s="18" t="inlineStr">
+        <is>
+          <t>wages and bargaining power</t>
+        </is>
+      </c>
+      <c r="N28" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O28" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P28" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q28" s="18" t="inlineStr">
+        <is>
+          <t>https://www.elysee.fr/emmanuel-macron/2023/04/17/adresse-aux-francais-2</t>
+        </is>
+      </c>
+      <c r="R28" s="18" t="inlineStr">
+        <is>
+          <t>The president's answer to the 2023 strikes; a precedent for today's protests.</t>
+        </is>
+      </c>
+      <c r="S28" s="18" t="n"/>
+      <c r="T28" s="18" t="inlineStr">
+        <is>
+          <t>In French; no official English text found. Your call whether a French-language primary text is acceptable. School-protest history (the 1881-82 Ferry education laws) has no English official text I could verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>30 May</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>1968-05-30</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>Allocution radiodiffusée du général de Gaulle (30 May 1968)</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>Charles de Gaulle</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="18" t="inlineStr">
+        <is>
+          <t>Fondation Charles de Gaulle</t>
+        </is>
+      </c>
+      <c r="L29" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M29" s="18" t="inlineStr">
+        <is>
+          <t>executive power</t>
+        </is>
+      </c>
+      <c r="N29" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O29" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P29" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q29" s="18" t="inlineStr">
+        <is>
+          <t>http://www.charles-de-gaulle.org/announcement/30-mai-1968-declaration-radiodiffusee-du-general-de-gaulle-dans-lequel-il-annonce-la-dissolution-de-lassemblee-nationale-le-maintien-du-premier-ministre-le-remaniement-du-gouvernement-l/</t>
+        </is>
+      </c>
+      <c r="R29" s="18" t="inlineStr">
+        <is>
+          <t>The president answers the May 1968 student and strike revolt by dissolving the Assembly; the template for how France's presidents respond to the street.</t>
+        </is>
+      </c>
+      <c r="S29" s="18" t="n"/>
+      <c r="T29" s="18" t="inlineStr">
+        <is>
+          <t>In French from the Charles de Gaulle Foundation. An English translation is at the Virginia Tech teaching module (secondary host). No primary text of the Grenelle agreements or of the student movement could be verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>lebanon</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>22 October</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>1989-10-22</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>The Taif Agreement (National Reconciliation Accord)</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>Lebanese parliamentarians, meeting at Taif</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>UN Peacemaker / Lebanese Parliament</t>
+        </is>
+      </c>
+      <c r="L30" s="18" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="M30" s="18" t="inlineStr">
+        <is>
+          <t>civil rights law</t>
+        </is>
+      </c>
+      <c r="N30" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O30" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P30" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q30" s="18" t="inlineStr">
+        <is>
+          <t>https://www.un.int/lebanon/sites/www.un.int/files/Lebanon/the_taif_agreement_english_version_.pdf</t>
+        </is>
+      </c>
+      <c r="R30" s="18" t="inlineStr">
+        <is>
+          <t>Ended the civil war and set the sectarian power-sharing still in force.</t>
+        </is>
+      </c>
+      <c r="S30" s="18" t="n"/>
+      <c r="T30" s="18" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>lebanon</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>2 September</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>2004-09-02</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 1559</t>
+        </is>
+      </c>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/1559(2004)</t>
+        </is>
+      </c>
+      <c r="L31" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M31" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N31" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O31" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P31" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q31" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1559(2004)</t>
+        </is>
+      </c>
+      <c r="R31" s="18" t="inlineStr">
+        <is>
+          <t>Called for foreign forces to leave Lebanon and for militias, meaning Hezbollah, to disband.</t>
+        </is>
+      </c>
+      <c r="S31" s="18" t="n"/>
+      <c r="T31" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>lebanon</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>11 August</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>2006-08-11</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 1701</t>
+        </is>
+      </c>
+      <c r="H32" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L32" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M32" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N32" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O32" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P32" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q32" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="R32" s="18" t="inlineStr">
+        <is>
+          <t>Ended the 2006 Israel-Hezbollah war and set the terms the 2024 ceasefire still cites.</t>
+        </is>
+      </c>
+      <c r="S32" s="18" t="n"/>
+      <c r="T32" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>lebanon</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>1926</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>23 May</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>1926-05-23</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of Lebanon</t>
+        </is>
+      </c>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>Republic of Lebanon</t>
+        </is>
+      </c>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L33" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M33" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N33" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O33" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P33" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q33" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Lebanon_2004</t>
+        </is>
+      </c>
+      <c r="R33" s="18" t="inlineStr">
+        <is>
+          <t>The state's governing text; the sectarian quotas live in it and the Taif amendments.</t>
+        </is>
+      </c>
+      <c r="S33" s="18" t="n"/>
+      <c r="T33" s="18" t="inlineStr">
+        <is>
+          <t>Date is the original 1926 text; the page is the text as amended to 2004.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>syria</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>30 June</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>2012-06-30</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>Final Communiqué of the Action Group for Syria (Geneva Communiqué)</t>
+        </is>
+      </c>
+      <c r="H34" s="18" t="inlineStr">
+        <is>
+          <t>Action Group for Syria</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="18" t="inlineStr">
+        <is>
+          <t>United Nations</t>
+        </is>
+      </c>
+      <c r="L34" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M34" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N34" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O34" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P34" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q34" s="18" t="inlineStr">
+        <is>
+          <t>https://peacemaker.un.org/sites/default/files/document/files/2024/05/sy120630final20communique20of20the20action20group20for20syria.pdf</t>
+        </is>
+      </c>
+      <c r="R34" s="18" t="inlineStr">
+        <is>
+          <t>The plan for a political transition that was never carried out.</t>
+        </is>
+      </c>
+      <c r="S34" s="18" t="n"/>
+      <c r="T34" s="18" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>syria</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>27 September</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>2013-09-27</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 2118</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/2118(2013)</t>
+        </is>
+      </c>
+      <c r="L35" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M35" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N35" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O35" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P35" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q35" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2118(2013)</t>
+        </is>
+      </c>
+      <c r="R35" s="18" t="inlineStr">
+        <is>
+          <t>Required Syria to give up its chemical weapons after the Ghouta attack.</t>
+        </is>
+      </c>
+      <c r="S35" s="18" t="n"/>
+      <c r="T35" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>syria</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>18 December</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>2015-12-18</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 2254</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="n"/>
+      <c r="J36" s="18" t="n"/>
+      <c r="K36" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/2254(2015)</t>
+        </is>
+      </c>
+      <c r="L36" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M36" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N36" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O36" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P36" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q36" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2254(2015)</t>
+        </is>
+      </c>
+      <c r="R36" s="18" t="inlineStr">
+        <is>
+          <t>The UN road map for a ceasefire, a constitution and elections.</t>
+        </is>
+      </c>
+      <c r="S36" s="18" t="n"/>
+      <c r="T36" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>syria</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>12 December</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>2003-12-12</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>Syria Accountability and Lebanese Sovereignty Restoration Act of 2003</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="18" t="inlineStr">
+        <is>
+          <t>Pub. L. 108-175, GovInfo</t>
+        </is>
+      </c>
+      <c r="L37" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M37" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N37" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P37" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q37" s="18" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/PLAW-108publ175/pdf/PLAW-108publ175.pdf</t>
+        </is>
+      </c>
+      <c r="R37" s="18" t="inlineStr">
+        <is>
+          <t>The first U.S. sanctions law aimed at the Syrian government.</t>
+        </is>
+      </c>
+      <c r="S37" s="18" t="n"/>
+      <c r="T37" s="18" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>iraq</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>3 April</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>1991-04-03</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 687</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/687(1991)</t>
+        </is>
+      </c>
+      <c r="L38" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M38" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N38" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O38" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P38" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q38" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/687(1991)</t>
+        </is>
+      </c>
+      <c r="R38" s="18" t="inlineStr">
+        <is>
+          <t>The ceasefire terms after the Gulf War, including weapons inspections.</t>
+        </is>
+      </c>
+      <c r="S38" s="18" t="n"/>
+      <c r="T38" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>iraq</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>8 November</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>2002-11-08</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 1441</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/1441(2002)</t>
+        </is>
+      </c>
+      <c r="L39" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M39" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N39" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O39" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P39" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q39" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1441(2002)</t>
+        </is>
+      </c>
+      <c r="R39" s="18" t="inlineStr">
+        <is>
+          <t>The 'final opportunity' resolution on inspections, argued over before the 2003 invasion.</t>
+        </is>
+      </c>
+      <c r="S39" s="18" t="n"/>
+      <c r="T39" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>iraq</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>15 October</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>2005-10-15</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of Iraq</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>Republic of Iraq</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="n"/>
+      <c r="J40" s="18" t="n"/>
+      <c r="K40" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L40" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M40" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N40" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O40" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P40" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q40" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Iraq_2005</t>
+        </is>
+      </c>
+      <c r="R40" s="18" t="inlineStr">
+        <is>
+          <t>The post-invasion governing text; federalism and Islam's role are still contested.</t>
+        </is>
+      </c>
+      <c r="S40" s="18" t="n"/>
+      <c r="T40" s="18" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>iraq</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>17 November</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>2008-11-17</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>Agreement on the Withdrawal of United States Forces from Iraq (Status of Forces Agreement)</t>
+        </is>
+      </c>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>United States and Iraq</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="18" t="n"/>
+      <c r="K41" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Department of State</t>
+        </is>
+      </c>
+      <c r="L41" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M41" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N41" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O41" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P41" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q41" s="18" t="inlineStr">
+        <is>
+          <t>https://2009-2017.state.gov/documents/organization/122074.pdf</t>
+        </is>
+      </c>
+      <c r="R41" s="18" t="inlineStr">
+        <is>
+          <t>The agreement that set the 2011 U.S. withdrawal date.</t>
+        </is>
+      </c>
+      <c r="S41" s="18" t="n"/>
+      <c r="T41" s="18" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>saudi-arabia</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>23 January</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>1980-01-23</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>State of the Union Address (the Carter Doctrine)</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>Jimmy Carter</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="n"/>
+      <c r="J42" s="18" t="n"/>
+      <c r="K42" s="18" t="inlineStr">
+        <is>
+          <t>Public Papers of the Presidents (American Presidency Project)</t>
+        </is>
+      </c>
+      <c r="L42" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M42" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N42" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O42" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P42" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q42" s="18" t="inlineStr">
+        <is>
+          <t>https://www.presidency.ucsb.edu/documents/the-state-the-union-address-delivered-before-joint-session-the-congress</t>
+        </is>
+      </c>
+      <c r="R42" s="18" t="inlineStr">
+        <is>
+          <t>The U.S. pledge to defend the Persian Gulf, the basis of the American security role in Saudi Arabia.</t>
+        </is>
+      </c>
+      <c r="S42" s="18" t="n"/>
+      <c r="T42" s="18" t="inlineStr">
+        <is>
+          <t>An American text about the Gulf; kept under Saudi Arabia and Iran. Checked: the 23 January 1980 address, with the Persian Gulf passage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>saudi-arabia</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>1 March</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>1992-03-01</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>Basic Law of Governance of Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>Kingdom of Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="n"/>
+      <c r="J43" s="18" t="n"/>
+      <c r="K43" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L43" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M43" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N43" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O43" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P43" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q43" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Saudi_Arabia_2005</t>
+        </is>
+      </c>
+      <c r="R43" s="18" t="inlineStr">
+        <is>
+          <t>The kingdom's governing text: the Quran as constitution, the king's powers.</t>
+        </is>
+      </c>
+      <c r="S43" s="18" t="n"/>
+      <c r="T43" s="18" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>saudi-arabia</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>28 March</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>2002-03-28</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t>Arab Peace Initiative</t>
+        </is>
+      </c>
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>League of Arab States, proposed by Crown Prince Abdullah of Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="I44" s="18" t="n"/>
+      <c r="J44" s="18" t="n"/>
+      <c r="K44" s="18" t="inlineStr">
+        <is>
+          <t>League of Arab States, English text</t>
+        </is>
+      </c>
+      <c r="L44" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M44" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N44" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O44" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P44" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q44" s="18" t="inlineStr">
+        <is>
+          <t>https://www.un.org/unispal/document/auto-insert-181223/</t>
+        </is>
+      </c>
+      <c r="R44" s="18" t="inlineStr">
+        <is>
+          <t>The Saudi-led offer of normalization for a return to the 1967 lines; central again in Gaza diplomacy.</t>
+        </is>
+      </c>
+      <c r="S44" s="18" t="n"/>
+      <c r="T44" s="18" t="inlineStr">
+        <is>
+          <t>Letter from Lebanon to the UN transmitting the text (excerpts); a full copy is at palestineinarabic.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>saudi-arabia</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>25 April</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>2016-04-25</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>Saudi Vision 2030</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>Kingdom of Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="n"/>
+      <c r="J45" s="18" t="n"/>
+      <c r="K45" s="18" t="inlineStr">
+        <is>
+          <t>Vision 2030 official site</t>
+        </is>
+      </c>
+      <c r="L45" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M45" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N45" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O45" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P45" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q45" s="18" t="inlineStr">
+        <is>
+          <t>https://www.vision2030.gov.sa/media/rc0b5oy1/saudi_vision203.pdf</t>
+        </is>
+      </c>
+      <c r="R45" s="18" t="inlineStr">
+        <is>
+          <t>The economic plan to move beyond oil.</t>
+        </is>
+      </c>
+      <c r="S45" s="18" t="n"/>
+      <c r="T45" s="18" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>turkey</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>24 July</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>1923-07-24</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>Treaty of Lausanne</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="inlineStr">
+        <is>
+          <t>Allied Powers and Turkey</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="n"/>
+      <c r="J46" s="18" t="n"/>
+      <c r="K46" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Foreign Affairs of the Republic of Turkey</t>
+        </is>
+      </c>
+      <c r="L46" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M46" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N46" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O46" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P46" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q46" s="18" t="inlineStr">
+        <is>
+          <t>https://www.mfa.gov.tr/lausanne-peace-treaty-part-i_-political-clauses.en.mfa</t>
+        </is>
+      </c>
+      <c r="R46" s="18" t="inlineStr">
+        <is>
+          <t>The treaty that set modern Turkey's borders and minority rules.</t>
+        </is>
+      </c>
+      <c r="S46" s="18" t="n"/>
+      <c r="T46" s="18" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>turkey</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>7 November</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>1982-11-07</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Republic of Turkey (as amended)</t>
+        </is>
+      </c>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>Republic of Turkey</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="n"/>
+      <c r="J47" s="18" t="n"/>
+      <c r="K47" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L47" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M47" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N47" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O47" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P47" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q47" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Turkey_2017</t>
+        </is>
+      </c>
+      <c r="R47" s="18" t="inlineStr">
+        <is>
+          <t>The governing text; the 2017 amendments created the executive presidency.</t>
+        </is>
+      </c>
+      <c r="S47" s="18" t="n"/>
+      <c r="T47" s="18" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>south-africa</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>26 June</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>1955-06-26</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>The Freedom Charter</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>Congress of the People</t>
+        </is>
+      </c>
+      <c r="I48" s="18" t="n"/>
+      <c r="J48" s="18" t="n"/>
+      <c r="K48" s="18" t="inlineStr">
+        <is>
+          <t>African National Congress</t>
+        </is>
+      </c>
+      <c r="L48" s="18" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="M48" s="18" t="inlineStr">
+        <is>
+          <t>civil rights law</t>
+        </is>
+      </c>
+      <c r="N48" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O48" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P48" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q48" s="18" t="inlineStr">
+        <is>
+          <t>https://www.anc1912.org.za/the-freedom-charter-2/</t>
+        </is>
+      </c>
+      <c r="R48" s="18" t="inlineStr">
+        <is>
+          <t>The anti-apartheid movement's founding statement of rights.</t>
+        </is>
+      </c>
+      <c r="S48" s="18" t="n"/>
+      <c r="T48" s="18" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>south-africa</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>20 April</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>1964-04-20</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>Statement from the Dock at the Rivonia Trial</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>Nelson Mandela</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="n"/>
+      <c r="J49" s="18" t="n"/>
+      <c r="K49" s="18" t="inlineStr">
+        <is>
+          <t>African National Congress</t>
+        </is>
+      </c>
+      <c r="L49" s="18" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="M49" s="18" t="inlineStr">
+        <is>
+          <t>civil rights law</t>
+        </is>
+      </c>
+      <c r="N49" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O49" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P49" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q49" s="18" t="inlineStr">
+        <is>
+          <t>http://www.mandela.gov.za/mandela_speeches/before/640420_trial.htm</t>
+        </is>
+      </c>
+      <c r="R49" s="18" t="inlineStr">
+        <is>
+          <t>'An ideal for which I am prepared to die.'</t>
+        </is>
+      </c>
+      <c r="S49" s="18" t="n"/>
+      <c r="T49" s="18" t="inlineStr">
+        <is>
+          <t>Also on the UN site: https://static.un.org/en/events/mandeladay/court_statement_1964.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>south-africa</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>10 December</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>1996-12-10</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Republic of South Africa, 1996</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
+        <is>
+          <t>Constitutional Assembly of South Africa</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="n"/>
+      <c r="J50" s="18" t="n"/>
+      <c r="K50" s="18" t="inlineStr">
+        <is>
+          <t>Government of South Africa</t>
+        </is>
+      </c>
+      <c r="L50" s="18" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="M50" s="18" t="inlineStr">
+        <is>
+          <t>civil rights law</t>
+        </is>
+      </c>
+      <c r="N50" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O50" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P50" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q50" s="18" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/documents/constitution-republic-south-africa-1996</t>
+        </is>
+      </c>
+      <c r="R50" s="18" t="inlineStr">
+        <is>
+          <t>The post-apartheid constitution, a model for rights-based constitutions.</t>
+        </is>
+      </c>
+      <c r="S50" s="18" t="n"/>
+      <c r="T50" s="18" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>south-africa</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>29 December</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>2023-12-29</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t>Application Instituting Proceedings: South Africa v. Israel (Genocide Convention)</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>Republic of South Africa</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="18" t="n"/>
+      <c r="K51" s="18" t="inlineStr">
+        <is>
+          <t>International Court of Justice</t>
+        </is>
+      </c>
+      <c r="L51" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M51" s="18" t="inlineStr">
+        <is>
+          <t>Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="N51" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O51" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P51" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q51" s="18" t="inlineStr">
+        <is>
+          <t>https://www.icj-cij.org/sites/default/files/case-related/192/192-20231228-app-01-00-en.pdf</t>
+        </is>
+      </c>
+      <c r="R51" s="18" t="inlineStr">
+        <is>
+          <t>South Africa's case against Israel at the ICJ, now at the center of the Gaza argument.</t>
+        </is>
+      </c>
+      <c r="S51" s="18" t="n"/>
+      <c r="T51" s="18" t="inlineStr">
+        <is>
+          <t>PDF; text not machine-checked. The ICJ site refuses scripts; the case-file URL follows the court's own pattern. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="n">
+        <v>1210</v>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>15 June</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>1215-06-15</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>Magna Carta</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>King John and the barons of England</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="n"/>
+      <c r="J52" s="18" t="n"/>
+      <c r="K52" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L52" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M52" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N52" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O52" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P52" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q52" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/medieval/magframe.asp</t>
+        </is>
+      </c>
+      <c r="R52" s="18" t="inlineStr">
+        <is>
+          <t>The oldest text on limiting a ruler's power, behind the American Constitution.</t>
+        </is>
+      </c>
+      <c r="S52" s="18" t="n"/>
+      <c r="T52" s="18" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>1689</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>16 December</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>1689-12-16</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G53" s="18" t="inlineStr">
+        <is>
+          <t>The English Bill of Rights</t>
+        </is>
+      </c>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>Parliament of England</t>
+        </is>
+      </c>
+      <c r="I53" s="18" t="n"/>
+      <c r="J53" s="18" t="n"/>
+      <c r="K53" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L53" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M53" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N53" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O53" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P53" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q53" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/17th_century/england.asp</t>
+        </is>
+      </c>
+      <c r="R53" s="18" t="inlineStr">
+        <is>
+          <t>Parliament's limits on the Crown; a direct source for the American Bill of Rights.</t>
+        </is>
+      </c>
+      <c r="S53" s="18" t="n"/>
+      <c r="T53" s="18" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="n">
+        <v>1780</v>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>1783</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>3 September</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>1783-09-03</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G54" s="18" t="inlineStr">
+        <is>
+          <t>Treaty of Paris (1783)</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="inlineStr">
+        <is>
+          <t>Great Britain and the United States</t>
+        </is>
+      </c>
+      <c r="I54" s="18" t="n"/>
+      <c r="J54" s="18" t="n"/>
+      <c r="K54" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L54" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M54" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N54" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O54" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P54" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q54" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/18th_century/paris.asp</t>
+        </is>
+      </c>
+      <c r="R54" s="18" t="inlineStr">
+        <is>
+          <t>Britain recognizes the United States.</t>
+        </is>
+      </c>
+      <c r="S54" s="18" t="n"/>
+      <c r="T54" s="18" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>5 March</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>1946-03-05</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t>The Sinews of Peace (the 'Iron Curtain' speech)</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>Winston Churchill</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="n"/>
+      <c r="J55" s="18" t="n"/>
+      <c r="K55" s="18" t="inlineStr">
+        <is>
+          <t>The Churchill Centre / Winston Churchill Foundation</t>
+        </is>
+      </c>
+      <c r="L55" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M55" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N55" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O55" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P55" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q55" s="18" t="inlineStr">
+        <is>
+          <t>https://winstonchurchill.org/resources/speeches/1946-1963-elder-statesman/the-sinews-of-peace/</t>
+        </is>
+      </c>
+      <c r="R55" s="18" t="inlineStr">
+        <is>
+          <t>Britain's wartime leader calls for a Western alliance against the USSR.</t>
+        </is>
+      </c>
+      <c r="S55" s="18" t="n"/>
+      <c r="T55" s="18" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>29 March</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>2017-03-29</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t>Prime Minister's letter to President of the European Council triggering Article 50</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="inlineStr">
+        <is>
+          <t>Theresa May</t>
+        </is>
+      </c>
+      <c r="I56" s="18" t="n"/>
+      <c r="J56" s="18" t="n"/>
+      <c r="K56" s="18" t="inlineStr">
+        <is>
+          <t>UK Government</t>
+        </is>
+      </c>
+      <c r="L56" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M56" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N56" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O56" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P56" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q56" s="18" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/prime-ministers-letter-to-donald-tusk-triggering-article-50</t>
+        </is>
+      </c>
+      <c r="R56" s="18" t="inlineStr">
+        <is>
+          <t>The formal start of Britain's exit from the European Union.</t>
+        </is>
+      </c>
+      <c r="S56" s="18" t="n"/>
+      <c r="T56" s="18" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>23 May</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>1949-05-23</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t>Basic Law for the Federal Republic of Germany</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>Parliamentary Council</t>
+        </is>
+      </c>
+      <c r="I57" s="18" t="n"/>
+      <c r="J57" s="18" t="n"/>
+      <c r="K57" s="18" t="inlineStr">
+        <is>
+          <t>Federal Ministry of Justice, English translation</t>
+        </is>
+      </c>
+      <c r="L57" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M57" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N57" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O57" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P57" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q57" s="18" t="inlineStr">
+        <is>
+          <t>https://www.gesetze-im-internet.de/englisch_gg/</t>
+        </is>
+      </c>
+      <c r="R57" s="18" t="inlineStr">
+        <is>
+          <t>Postwar Germany's constitution, built to prevent another dictatorship.</t>
+        </is>
+      </c>
+      <c r="S57" s="18" t="n"/>
+      <c r="T57" s="18" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>22 January</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>1963-01-22</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G58" s="18" t="inlineStr">
+        <is>
+          <t>Treaty on Franco-German Cooperation (Élysée Treaty)</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="inlineStr">
+        <is>
+          <t>Konrad Adenauer and Charles de Gaulle</t>
+        </is>
+      </c>
+      <c r="I58" s="18" t="n"/>
+      <c r="J58" s="18" t="n"/>
+      <c r="K58" s="18" t="inlineStr">
+        <is>
+          <t>Federal Foreign Office / Elysee</t>
+        </is>
+      </c>
+      <c r="L58" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M58" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N58" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O58" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P58" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q58" s="18" t="inlineStr">
+        <is>
+          <t>https://www.cvce.eu/en/obj/treaty_between_the_french_republic_and_the_federal_republic_of_germany_on_french_german_cooperation_22_january_1963-en-68956f73-75cb-4749-a6e2-344c8aad84ba.html</t>
+        </is>
+      </c>
+      <c r="R58" s="18" t="inlineStr">
+        <is>
+          <t>Reconciliation between France and Germany, the core of the European project.</t>
+        </is>
+      </c>
+      <c r="S58" s="18" t="n"/>
+      <c r="T58" s="18" t="inlineStr">
+        <is>
+          <t>CVCE (University of Luxembourg's archive) showed a bot check. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>27 February</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>2022-02-27</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>Policy statement by Chancellor Olaf Scholz (the Zeitenwende speech)</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>Olaf Scholz</t>
+        </is>
+      </c>
+      <c r="I59" s="18" t="n"/>
+      <c r="J59" s="18" t="n"/>
+      <c r="K59" s="18" t="inlineStr">
+        <is>
+          <t>Federal Government of Germany</t>
+        </is>
+      </c>
+      <c r="L59" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M59" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N59" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O59" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P59" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q59" s="18" t="inlineStr">
+        <is>
+          <t>https://www.bundesregierung.de/breg-en/news/policy-statement-by-olaf-scholz-chancellor-of-the-federal-republic-of-germany-and-member-of-the-german-bundestag-27-february-2022-in-berlin-2008378</t>
+        </is>
+      </c>
+      <c r="R59" s="18" t="inlineStr">
+        <is>
+          <t>Germany's turn on defence spending after Russia's invasion of Ukraine.</t>
+        </is>
+      </c>
+      <c r="S59" s="18" t="n"/>
+      <c r="T59" s="18" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>japan</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>26 July</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>1945-07-26</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t>Potsdam Declaration: Proclamation Defining Terms for Japanese Surrender</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
+        <is>
+          <t>Truman, Churchill and Chiang Kai-shek</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="n"/>
+      <c r="J60" s="18" t="n"/>
+      <c r="K60" s="18" t="inlineStr">
+        <is>
+          <t>Avalon Project, Yale</t>
+        </is>
+      </c>
+      <c r="L60" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M60" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N60" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O60" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P60" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q60" s="18" t="inlineStr">
+        <is>
+          <t>https://avalon.law.yale.edu/20th_century/decade17.asp</t>
+        </is>
+      </c>
+      <c r="R60" s="18" t="inlineStr">
+        <is>
+          <t>The terms Japan accepted after the bombs.</t>
+        </is>
+      </c>
+      <c r="S60" s="18" t="n"/>
+      <c r="T60" s="18" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>japan</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>3 May</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>1947-05-03</t>
+        </is>
+      </c>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G61" s="18" t="inlineStr">
+        <is>
+          <t>The Constitution of Japan</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>Government of Japan</t>
+        </is>
+      </c>
+      <c r="I61" s="18" t="n"/>
+      <c r="J61" s="18" t="n"/>
+      <c r="K61" s="18" t="inlineStr">
+        <is>
+          <t>Prime Minister of Japan and His Cabinet</t>
+        </is>
+      </c>
+      <c r="L61" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M61" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N61" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O61" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P61" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q61" s="18" t="inlineStr">
+        <is>
+          <t>https://www.japaneselawtranslation.go.jp/en/laws/view/174</t>
+        </is>
+      </c>
+      <c r="R61" s="18" t="inlineStr">
+        <is>
+          <t>Article 9's renunciation of war, written under the Occupation.</t>
+        </is>
+      </c>
+      <c r="S61" s="18" t="n"/>
+      <c r="T61" s="18" t="inlineStr">
+        <is>
+          <t>Japan's official law-translation site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>japan</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>19 January</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>1960-01-19</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>Treaty of Mutual Cooperation and Security between Japan and the United States</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="inlineStr">
+        <is>
+          <t>Japan and the United States</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="n"/>
+      <c r="J62" s="18" t="n"/>
+      <c r="K62" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Foreign Affairs of Japan</t>
+        </is>
+      </c>
+      <c r="L62" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M62" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N62" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O62" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P62" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q62" s="18" t="inlineStr">
+        <is>
+          <t>https://www.mofa.go.jp/region/n-america/us/q&amp;a/ref/1.html</t>
+        </is>
+      </c>
+      <c r="R62" s="18" t="inlineStr">
+        <is>
+          <t>The bilateral security treaty still in force.</t>
+        </is>
+      </c>
+      <c r="S62" s="18" t="n"/>
+      <c r="T62" s="18" t="inlineStr">
+        <is>
+          <t>Japan's foreign ministry refuses scripts; URL not machine-checked. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>15 August</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>1947-08-15</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G63" s="18" t="inlineStr">
+        <is>
+          <t>Indian Independence Act 1947</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>Parliament of the United Kingdom</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="n"/>
+      <c r="J63" s="18" t="n"/>
+      <c r="K63" s="18" t="inlineStr">
+        <is>
+          <t>UK Parliament, legislation.gov.uk</t>
+        </is>
+      </c>
+      <c r="L63" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M63" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N63" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O63" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P63" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q63" s="18" t="inlineStr">
+        <is>
+          <t>https://www.legislation.gov.uk/ukpga/Geo6/10-11/30/contents/enacted</t>
+        </is>
+      </c>
+      <c r="R63" s="18" t="inlineStr">
+        <is>
+          <t>The law that ended British rule and created India and Pakistan.</t>
+        </is>
+      </c>
+      <c r="S63" s="18" t="n"/>
+      <c r="T63" s="18" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>26 January</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>1950-01-26</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of India</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>Constituent Assembly of India</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="n"/>
+      <c r="J64" s="18" t="n"/>
+      <c r="K64" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project / Government of India</t>
+        </is>
+      </c>
+      <c r="L64" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M64" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N64" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O64" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P64" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q64" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/India_2016</t>
+        </is>
+      </c>
+      <c r="R64" s="18" t="inlineStr">
+        <is>
+          <t>The world's largest democracy's governing text.</t>
+        </is>
+      </c>
+      <c r="S64" s="18" t="n"/>
+      <c r="T64" s="18" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>18 July</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>2005-07-18</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>Joint Statement by President Bush and Prime Minister Singh (civil nuclear cooperation)</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>George W. Bush and Manmohan Singh</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="n"/>
+      <c r="J65" s="18" t="n"/>
+      <c r="K65" s="18" t="inlineStr">
+        <is>
+          <t>The White House archives</t>
+        </is>
+      </c>
+      <c r="L65" s="18" t="inlineStr">
+        <is>
+          <t>The Bomb</t>
+        </is>
+      </c>
+      <c r="M65" s="18" t="inlineStr">
+        <is>
+          <t>arms control and treaties</t>
+        </is>
+      </c>
+      <c r="N65" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O65" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P65" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q65" s="18" t="inlineStr">
+        <is>
+          <t>https://georgewbush-whitehouse.archives.gov/news/releases/2005/07/20050718-6.html</t>
+        </is>
+      </c>
+      <c r="R65" s="18" t="inlineStr">
+        <is>
+          <t>The U.S.-India nuclear deal that ended India's nuclear isolation.</t>
+        </is>
+      </c>
+      <c r="S65" s="18" t="n"/>
+      <c r="T65" s="18" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>2 February</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>1848-02-02</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>Treaty of Guadalupe Hidalgo</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>United States and Mexico</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="n"/>
+      <c r="J66" s="18" t="n"/>
+      <c r="K66" s="18" t="inlineStr">
+        <is>
+          <t>National Archives</t>
+        </is>
+      </c>
+      <c r="L66" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M66" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N66" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O66" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P66" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q66" s="18" t="inlineStr">
+        <is>
+          <t>https://www.archives.gov/milestone-documents/treaty-of-guadalupe-hidalgo</t>
+        </is>
+      </c>
+      <c r="R66" s="18" t="inlineStr">
+        <is>
+          <t>The treaty that ended the Mexican-American War and moved the border.</t>
+        </is>
+      </c>
+      <c r="S66" s="18" t="n"/>
+      <c r="T66" s="18" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="n">
+        <v>1910</v>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>16 January</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>1917-01-16</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="inlineStr">
+        <is>
+          <t>The Zimmermann Telegram</t>
+        </is>
+      </c>
+      <c r="H67" s="18" t="inlineStr">
+        <is>
+          <t>Arthur Zimmermann</t>
+        </is>
+      </c>
+      <c r="I67" s="18" t="n"/>
+      <c r="J67" s="18" t="n"/>
+      <c r="K67" s="18" t="inlineStr">
+        <is>
+          <t>National Archives</t>
+        </is>
+      </c>
+      <c r="L67" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M67" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N67" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O67" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P67" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q67" s="18" t="inlineStr">
+        <is>
+          <t>https://www.archives.gov/education/lessons/zimmermann</t>
+        </is>
+      </c>
+      <c r="R67" s="18" t="inlineStr">
+        <is>
+          <t>Germany's offer to Mexico that helped bring the United States into World War I.</t>
+        </is>
+      </c>
+      <c r="S67" s="18" t="n"/>
+      <c r="T67" s="18" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="n">
+        <v>1910</v>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>5 February</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>1917-02-05</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of Mexico, 1917</t>
+        </is>
+      </c>
+      <c r="H68" s="18" t="inlineStr">
+        <is>
+          <t>Constituent Congress of Mexico</t>
+        </is>
+      </c>
+      <c r="I68" s="18" t="n"/>
+      <c r="J68" s="18" t="n"/>
+      <c r="K68" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L68" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M68" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N68" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O68" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P68" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q68" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Mexico_2015</t>
+        </is>
+      </c>
+      <c r="R68" s="18" t="inlineStr">
+        <is>
+          <t>The first constitution to write in social rights, land and labor.</t>
+        </is>
+      </c>
+      <c r="S68" s="18" t="n"/>
+      <c r="T68" s="18" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>1 January</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>1994-01-01</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>North American Free Trade Agreement</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>Governments of the United States, Mexico and Canada</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="n"/>
+      <c r="J69" s="18" t="n"/>
+      <c r="K69" s="18" t="inlineStr">
+        <is>
+          <t>Office of the United States Trade Representative</t>
+        </is>
+      </c>
+      <c r="L69" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M69" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N69" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O69" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P69" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q69" s="18" t="inlineStr">
+        <is>
+          <t>http://www.sice.oas.org/trade/nafta/naftatce.asp</t>
+        </is>
+      </c>
+      <c r="R69" s="18" t="inlineStr">
+        <is>
+          <t>The trade pact the 2018 USMCA replaced.</t>
+        </is>
+      </c>
+      <c r="S69" s="18" t="n"/>
+      <c r="T69" s="18" t="inlineStr">
+        <is>
+          <t>Organization of American States trade-information system. The USTR archive page has the same text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
+          <t>1 May</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>1853-05-01</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Argentine Nation</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="inlineStr">
+        <is>
+          <t>General Constituent Congress</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="n"/>
+      <c r="J70" s="18" t="n"/>
+      <c r="K70" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L70" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M70" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N70" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O70" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P70" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q70" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Argentina_1994</t>
+        </is>
+      </c>
+      <c r="R70" s="18" t="inlineStr">
+        <is>
+          <t>The constitution modeled on the American one.</t>
+        </is>
+      </c>
+      <c r="S70" s="18" t="n"/>
+      <c r="T70" s="18" t="inlineStr">
+        <is>
+          <t>Text as amended 1994.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>16 December</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>1965-12-16</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>UN General Assembly Resolution 2065 (XX): Question of the Falkland Islands (Malvinas)</t>
+        </is>
+      </c>
+      <c r="H71" s="18" t="inlineStr">
+        <is>
+          <t>United Nations General Assembly</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="n"/>
+      <c r="J71" s="18" t="n"/>
+      <c r="K71" s="18" t="inlineStr">
+        <is>
+          <t>UN document A/RES/2065(XX)</t>
+        </is>
+      </c>
+      <c r="L71" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M71" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N71" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O71" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P71" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q71" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/RES/2065(XX)</t>
+        </is>
+      </c>
+      <c r="R71" s="18" t="inlineStr">
+        <is>
+          <t>The UN call for Britain and Argentina to negotiate the islands' status.</t>
+        </is>
+      </c>
+      <c r="S71" s="18" t="n"/>
+      <c r="T71" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>25 May</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>1982-05-25</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t>Argentina's Falklands conflict, UN Security Council Resolution 502</t>
+        </is>
+      </c>
+      <c r="H72" s="18" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="n"/>
+      <c r="J72" s="18" t="n"/>
+      <c r="K72" s="18" t="inlineStr">
+        <is>
+          <t>UN document S/RES/502(1982)</t>
+        </is>
+      </c>
+      <c r="L72" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M72" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N72" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O72" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P72" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q72" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/502(1982)</t>
+        </is>
+      </c>
+      <c r="R72" s="18" t="inlineStr">
+        <is>
+          <t>The resolution demanding Argentina's withdrawal at the start of the 1982 war.</t>
+        </is>
+      </c>
+      <c r="S72" s="18" t="n"/>
+      <c r="T72" s="18" t="inlineStr">
+        <is>
+          <t>UN viewer is JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>australia</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>1901</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="inlineStr">
+        <is>
+          <t>1 January</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>1901-01-01</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t>Commonwealth of Australia Constitution Act</t>
+        </is>
+      </c>
+      <c r="H73" s="18" t="inlineStr">
+        <is>
+          <t>Imperial Parliament</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="n"/>
+      <c r="J73" s="18" t="n"/>
+      <c r="K73" s="18" t="inlineStr">
+        <is>
+          <t>Museum of Australian Democracy / Australian government</t>
+        </is>
+      </c>
+      <c r="L73" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M73" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N73" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O73" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P73" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q73" s="18" t="inlineStr">
+        <is>
+          <t>https://www.legislation.gov.au/C1900A00063/latest/text</t>
+        </is>
+      </c>
+      <c r="R73" s="18" t="inlineStr">
+        <is>
+          <t>Australia's founding constitution.</t>
+        </is>
+      </c>
+      <c r="S73" s="18" t="n"/>
+      <c r="T73" s="18" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>australia</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>15 September</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="inlineStr">
+        <is>
+          <t>Joint Leaders Statement on AUKUS</t>
+        </is>
+      </c>
+      <c r="H74" s="18" t="inlineStr">
+        <is>
+          <t>Joe Biden, Scott Morrison and Boris Johnson</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="n"/>
+      <c r="J74" s="18" t="n"/>
+      <c r="K74" s="18" t="inlineStr">
+        <is>
+          <t>The White House</t>
+        </is>
+      </c>
+      <c r="L74" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M74" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N74" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O74" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P74" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q74" s="18" t="inlineStr">
+        <is>
+          <t>https://bidenwhitehouse.archives.gov/briefing-room/statements-releases/2021/09/15/joint-leaders-statement-on-aukus/</t>
+        </is>
+      </c>
+      <c r="R74" s="18" t="inlineStr">
+        <is>
+          <t>The submarine pact aimed at China.</t>
+        </is>
+      </c>
+      <c r="S74" s="18" t="n"/>
+      <c r="T74" s="18" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>brazil</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>5 October</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>1988-10-05</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G75" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Federative Republic of Brazil</t>
+        </is>
+      </c>
+      <c r="H75" s="18" t="inlineStr">
+        <is>
+          <t>Constituent Assembly of Brazil</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="n"/>
+      <c r="J75" s="18" t="n"/>
+      <c r="K75" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L75" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M75" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N75" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O75" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P75" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q75" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Brazil_2017</t>
+        </is>
+      </c>
+      <c r="R75" s="18" t="inlineStr">
+        <is>
+          <t>The 'citizen constitution' that ended military rule.</t>
+        </is>
+      </c>
+      <c r="S75" s="18" t="n"/>
+      <c r="T75" s="18" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>24 April</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>1955-04-24</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>Final Communiqué of the Asian-African Conference of Bandung</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="inlineStr">
+        <is>
+          <t>Asian-African Conference</t>
+        </is>
+      </c>
+      <c r="I76" s="18" t="n"/>
+      <c r="J76" s="18" t="n"/>
+      <c r="K76" s="18" t="inlineStr">
+        <is>
+          <t>Digital Archive, Indonesia / Library</t>
+        </is>
+      </c>
+      <c r="L76" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M76" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N76" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O76" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P76" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q76" s="18" t="inlineStr">
+        <is>
+          <t>https://www.bandungspirit.org/IMG/pdf/bandung_final_communique.pdf</t>
+        </is>
+      </c>
+      <c r="R76" s="18" t="inlineStr">
+        <is>
+          <t>The founding statement of the non-aligned movement.</t>
+        </is>
+      </c>
+      <c r="S76" s="18" t="n"/>
+      <c r="T76" s="18" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>18 August</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>1945-08-18</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G77" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Republic of Indonesia (as amended)</t>
+        </is>
+      </c>
+      <c r="H77" s="18" t="inlineStr">
+        <is>
+          <t>Republic of Indonesia</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="n"/>
+      <c r="J77" s="18" t="n"/>
+      <c r="K77" s="18" t="inlineStr">
+        <is>
+          <t>Constitute Project, English translation</t>
+        </is>
+      </c>
+      <c r="L77" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M77" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N77" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O77" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P77" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q77" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Indonesia_2002</t>
+        </is>
+      </c>
+      <c r="R77" s="18" t="inlineStr">
+        <is>
+          <t>The Pancasila constitution; the 2002 amendments ended Suharto-era rule.</t>
+        </is>
+      </c>
+      <c r="S77" s="18" t="n"/>
+      <c r="T77" s="18" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>22 December</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>1947-12-22</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t>Constitution of the Italian Republic</t>
+        </is>
+      </c>
+      <c r="H78" s="18" t="inlineStr">
+        <is>
+          <t>Constituent Assembly of Italy</t>
+        </is>
+      </c>
+      <c r="I78" s="18" t="n"/>
+      <c r="J78" s="18" t="n"/>
+      <c r="K78" s="18" t="inlineStr">
+        <is>
+          <t>Senate of the Italian Republic, English translation</t>
+        </is>
+      </c>
+      <c r="L78" s="18" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M78" s="18" t="inlineStr">
+        <is>
+          <t>constitutional restraints</t>
+        </is>
+      </c>
+      <c r="N78" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O78" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P78" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q78" s="18" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Italy_2012</t>
+        </is>
+      </c>
+      <c r="R78" s="18" t="inlineStr">
+        <is>
+          <t>Postwar Italy's governing text, written to bar a return of fascism.</t>
+        </is>
+      </c>
+      <c r="S78" s="18" t="n"/>
+      <c r="T78" s="18" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>25 March</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>1957-03-25</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G79" s="18" t="inlineStr">
+        <is>
+          <t>Treaty establishing the European Economic Community (Treaty of Rome)</t>
+        </is>
+      </c>
+      <c r="H79" s="18" t="inlineStr">
+        <is>
+          <t>Six founding states, including Italy</t>
+        </is>
+      </c>
+      <c r="I79" s="18" t="n"/>
+      <c r="J79" s="18" t="n"/>
+      <c r="K79" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex</t>
+        </is>
+      </c>
+      <c r="L79" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M79" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N79" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O79" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P79" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q79" s="18" t="inlineStr">
+        <is>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:11957E/TXT</t>
+        </is>
+      </c>
+      <c r="R79" s="18" t="inlineStr">
+        <is>
+          <t>The treaty that began the common market, signed in Rome.</t>
+        </is>
+      </c>
+      <c r="S79" s="18" t="n"/>
+      <c r="T79" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex returns a script challenge. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="n">
+        <v>1890</v>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>1890</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>2 July</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr">
+        <is>
+          <t>1890-07-02</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>Sherman Antitrust Act</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="n"/>
+      <c r="J80" s="18" t="n"/>
+      <c r="K80" s="18" t="inlineStr">
+        <is>
+          <t>National Archives</t>
+        </is>
+      </c>
+      <c r="L80" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M80" s="18" t="inlineStr">
+        <is>
+          <t>regulation and the administrative state</t>
+        </is>
+      </c>
+      <c r="N80" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O80" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P80" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q80" s="18" t="inlineStr">
+        <is>
+          <t>https://www.archives.gov/milestone-documents/sherman-anti-trust-act</t>
+        </is>
+      </c>
+      <c r="R80" s="18" t="inlineStr">
+        <is>
+          <t>The first law against monopoly, the basis for every later action against big companies.</t>
+        </is>
+      </c>
+      <c r="S80" s="18" t="n"/>
+      <c r="T80" s="18" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B81" s="18" t="n">
+        <v>1930</v>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>19 June</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>1934-06-19</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>Communications Act of 1934</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="I81" s="18" t="n"/>
+      <c r="J81" s="18" t="n"/>
+      <c r="K81" s="18" t="inlineStr">
+        <is>
+          <t>Pub. L. 73-416, GovInfo</t>
+        </is>
+      </c>
+      <c r="L81" s="18" t="inlineStr">
+        <is>
+          <t>The Media</t>
+        </is>
+      </c>
+      <c r="M81" s="18" t="inlineStr">
+        <is>
+          <t>platforms and attention</t>
+        </is>
+      </c>
+      <c r="N81" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O81" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P81" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q81" s="18" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/COMPS-1409/pdf/COMPS-1409.pdf</t>
+        </is>
+      </c>
+      <c r="R81" s="18" t="inlineStr">
+        <is>
+          <t>The law that created the FCC and still frames broadcast and telecom regulation.</t>
+        </is>
+      </c>
+      <c r="S81" s="18" t="n"/>
+      <c r="T81" s="18" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>1 July</t>
+        </is>
+      </c>
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t>1945-07-01</t>
+        </is>
+      </c>
+      <c r="F82" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="inlineStr">
+        <is>
+          <t>As We May Think</t>
+        </is>
+      </c>
+      <c r="H82" s="18" t="inlineStr">
+        <is>
+          <t>Vannevar Bush</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="n"/>
+      <c r="J82" s="18" t="n"/>
+      <c r="K82" s="18" t="inlineStr">
+        <is>
+          <t>The Atlantic</t>
+        </is>
+      </c>
+      <c r="L82" s="18" t="inlineStr">
+        <is>
+          <t>The Media</t>
+        </is>
+      </c>
+      <c r="M82" s="18" t="inlineStr">
+        <is>
+          <t>information and misinformation</t>
+        </is>
+      </c>
+      <c r="N82" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O82" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P82" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q82" s="18" t="inlineStr">
+        <is>
+          <t>https://www.theatlantic.com/magazine/archive/1945/07/as-we-may-think/303881/</t>
+        </is>
+      </c>
+      <c r="R82" s="18" t="inlineStr">
+        <is>
+          <t>The essay that imagined the web and the personal machine for managing information.</t>
+        </is>
+      </c>
+      <c r="S82" s="18" t="n"/>
+      <c r="T82" s="18" t="inlineStr">
+        <is>
+          <t>The Atlantic refuses scripts. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B83" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="D83" s="18" t="inlineStr">
+        <is>
+          <t>31 August</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
+          <t>1955-08-31</t>
+        </is>
+      </c>
+      <c r="F83" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>A Proposal for the Dartmouth Summer Research Project on Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
+          <t>John McCarthy, Marvin Minsky, Nathaniel Rochester, Claude Shannon</t>
+        </is>
+      </c>
+      <c r="I83" s="18" t="n"/>
+      <c r="J83" s="18" t="n"/>
+      <c r="K83" s="18" t="inlineStr">
+        <is>
+          <t>Stanford University, John McCarthy archive</t>
+        </is>
+      </c>
+      <c r="L83" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M83" s="18" t="inlineStr">
+        <is>
+          <t>state capacity and competence</t>
+        </is>
+      </c>
+      <c r="N83" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O83" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P83" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q83" s="18" t="inlineStr">
+        <is>
+          <t>http://jmc.stanford.edu/articles/dartmouth/dartmouth.pdf</t>
+        </is>
+      </c>
+      <c r="R83" s="18" t="inlineStr">
+        <is>
+          <t>The proposal that gave the field its name.</t>
+        </is>
+      </c>
+      <c r="S83" s="18" t="n"/>
+      <c r="T83" s="18" t="inlineStr">
+        <is>
+          <t>PDF; text not machine-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="n">
+        <v>1970</v>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="inlineStr">
+        <is>
+          <t>31 December</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>1974-12-31</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>Privacy Act of 1974</t>
+        </is>
+      </c>
+      <c r="H84" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="n"/>
+      <c r="J84" s="18" t="n"/>
+      <c r="K84" s="18" t="inlineStr">
+        <is>
+          <t>Pub. L. 93-579, GovInfo</t>
+        </is>
+      </c>
+      <c r="L84" s="18" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="M84" s="18" t="inlineStr">
+        <is>
+          <t>surveillance</t>
+        </is>
+      </c>
+      <c r="N84" s="18" t="inlineStr">
+        <is>
+          <t>Addition, pre-1981</t>
+        </is>
+      </c>
+      <c r="O84" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P84" s="18" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q84" s="18" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/STATUTE-88/pdf/STATUTE-88-Pg1896.pdf</t>
+        </is>
+      </c>
+      <c r="R84" s="18" t="inlineStr">
+        <is>
+          <t>The first U.S. law on what the government may do with personal data.</t>
+        </is>
+      </c>
+      <c r="S84" s="18" t="n"/>
+      <c r="T84" s="18" t="inlineStr">
+        <is>
+          <t>PDF; text not machine-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B85" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="D85" s="18" t="inlineStr">
+        <is>
+          <t>8 February</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>1996-02-08</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>47 U.S. Code Section 230: Protection for private blocking and screening of offensive material</t>
+        </is>
+      </c>
+      <c r="H85" s="18" t="inlineStr">
+        <is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="I85" s="18" t="n"/>
+      <c r="J85" s="18" t="n"/>
+      <c r="K85" s="18" t="inlineStr">
+        <is>
+          <t>Legal Information Institute, Cornell Law School</t>
+        </is>
+      </c>
+      <c r="L85" s="18" t="inlineStr">
+        <is>
+          <t>The Media</t>
+        </is>
+      </c>
+      <c r="M85" s="18" t="inlineStr">
+        <is>
+          <t>platforms and attention</t>
+        </is>
+      </c>
+      <c r="N85" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O85" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P85" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q85" s="18" t="inlineStr">
+        <is>
+          <t>https://www.law.cornell.edu/uscode/text/47/230</t>
+        </is>
+      </c>
+      <c r="R85" s="18" t="inlineStr">
+        <is>
+          <t>The liability shield for online platforms, the legal basis of the modern internet.</t>
+        </is>
+      </c>
+      <c r="S85" s="18" t="n"/>
+      <c r="T85" s="18" t="inlineStr">
+        <is>
+          <t>Cornell LII is a legal library. Passed as part of the Telecommunications Act, already in the matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>27 April</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Civil Rights</t>
+        </is>
+      </c>
+      <c r="G86" s="18" t="inlineStr">
+        <is>
+          <t>General Data Protection Regulation</t>
+        </is>
+      </c>
+      <c r="H86" s="18" t="inlineStr">
+        <is>
+          <t>European Parliament and Council</t>
+        </is>
+      </c>
+      <c r="I86" s="18" t="n"/>
+      <c r="J86" s="18" t="n"/>
+      <c r="K86" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex</t>
+        </is>
+      </c>
+      <c r="L86" s="18" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="M86" s="18" t="inlineStr">
+        <is>
+          <t>surveillance</t>
+        </is>
+      </c>
+      <c r="N86" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O86" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P86" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q86" s="18" t="inlineStr">
+        <is>
+          <t>https://eur-lex.europa.eu/eli/reg/2016/679/oj</t>
+        </is>
+      </c>
+      <c r="R86" s="18" t="inlineStr">
+        <is>
+          <t>The European model for data privacy that U.S. states and companies answer to.</t>
+        </is>
+      </c>
+      <c r="S86" s="18" t="n"/>
+      <c r="T86" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex returns a script challenge. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D87" s="18" t="inlineStr">
+        <is>
+          <t>30 October</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>2023-10-30</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G87" s="18" t="inlineStr">
+        <is>
+          <t>Executive Order 14110: Safe, Secure, and Trustworthy Development and Use of Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="H87" s="18" t="inlineStr">
+        <is>
+          <t>Joe Biden</t>
+        </is>
+      </c>
+      <c r="I87" s="18" t="n"/>
+      <c r="J87" s="18" t="n"/>
+      <c r="K87" s="18" t="inlineStr">
+        <is>
+          <t>Federal Register</t>
+        </is>
+      </c>
+      <c r="L87" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M87" s="18" t="inlineStr">
+        <is>
+          <t>regulation and the administrative state</t>
+        </is>
+      </c>
+      <c r="N87" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O87" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P87" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q87" s="18" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2023/11/01/2023-24283/safe-secure-and-trustworthy-development-and-use-of-artificial-intelligence</t>
+        </is>
+      </c>
+      <c r="R87" s="18" t="inlineStr">
+        <is>
+          <t>The first broad U.S. executive action on AI safety.</t>
+        </is>
+      </c>
+      <c r="S87" s="18" t="n"/>
+      <c r="T87" s="18" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>13 June</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G88" s="18" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2024/1689 (the AI Act)</t>
+        </is>
+      </c>
+      <c r="H88" s="18" t="inlineStr">
+        <is>
+          <t>European Parliament and Council</t>
+        </is>
+      </c>
+      <c r="I88" s="18" t="n"/>
+      <c r="J88" s="18" t="n"/>
+      <c r="K88" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex</t>
+        </is>
+      </c>
+      <c r="L88" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M88" s="18" t="inlineStr">
+        <is>
+          <t>regulation and the administrative state</t>
+        </is>
+      </c>
+      <c r="N88" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O88" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P88" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q88" s="18" t="inlineStr">
+        <is>
+          <t>https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
+        </is>
+      </c>
+      <c r="R88" s="18" t="inlineStr">
+        <is>
+          <t>The first comprehensive law on AI, in force in Europe.</t>
+        </is>
+      </c>
+      <c r="S88" s="18" t="n"/>
+      <c r="T88" s="18" t="inlineStr">
+        <is>
+          <t>EUR-Lex returns a script challenge. Open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D89" s="18" t="inlineStr">
+        <is>
+          <t>23 January</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="F89" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G89" s="18" t="inlineStr">
+        <is>
+          <t>Executive Order 14179: Removing Barriers to American Leadership in Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="I89" s="18" t="n"/>
+      <c r="J89" s="18" t="n"/>
+      <c r="K89" s="18" t="inlineStr">
+        <is>
+          <t>Federal Register</t>
+        </is>
+      </c>
+      <c r="L89" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M89" s="18" t="inlineStr">
+        <is>
+          <t>regulation and the administrative state</t>
+        </is>
+      </c>
+      <c r="N89" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O89" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P89" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q89" s="18" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2025/01/31/2025-02172/removing-barriers-to-american-leadership-in-artificial-intelligence</t>
+        </is>
+      </c>
+      <c r="R89" s="18" t="inlineStr">
+        <is>
+          <t>Reverses the 2023 order; the swing in U.S. AI policy.</t>
+        </is>
+      </c>
+      <c r="S89" s="18" t="n"/>
+      <c r="T89" s="18" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr">
+        <is>
+          <t>5 December</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>1994-12-05</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G90" s="18" t="inlineStr">
+        <is>
+          <t>Memorandum on Security Assurances in connection with Ukraine's accession to the Treaty on the Non-Proliferation of Nuclear Weapons (Budapest Memorandum)</t>
+        </is>
+      </c>
+      <c r="H90" s="18" t="inlineStr">
+        <is>
+          <t>Russia, the United Kingdom, the United States and Ukraine</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="n"/>
+      <c r="J90" s="18" t="n"/>
+      <c r="K90" s="18" t="inlineStr">
+        <is>
+          <t>UN document A/49/765</t>
+        </is>
+      </c>
+      <c r="L90" s="18" t="inlineStr">
+        <is>
+          <t>The Bomb</t>
+        </is>
+      </c>
+      <c r="M90" s="18" t="inlineStr">
+        <is>
+          <t>arms control and treaties</t>
+        </is>
+      </c>
+      <c r="N90" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O90" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P90" s="18" t="inlineStr">
+        <is>
+          <t>needs-check</t>
+        </is>
+      </c>
+      <c r="Q90" s="18" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/49/765</t>
+        </is>
+      </c>
+      <c r="R90" s="18" t="inlineStr">
+        <is>
+          <t>Ukraine gave up its nuclear weapons for assurances Russia later broke.</t>
+        </is>
+      </c>
+      <c r="S90" s="18" t="n"/>
+      <c r="T90" s="18" t="inlineStr">
+        <is>
+          <t>UN viewers are JavaScript; open to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B91" s="18" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="D91" s="18" t="inlineStr">
+        <is>
+          <t>27 May</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="inlineStr">
+        <is>
+          <t>1997-05-27</t>
+        </is>
+      </c>
+      <c r="F91" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G91" s="18" t="inlineStr">
+        <is>
+          <t>Founding Act on Mutual Relations, Cooperation and Security between NATO and the Russian Federation</t>
+        </is>
+      </c>
+      <c r="H91" s="18" t="inlineStr">
+        <is>
+          <t>NATO and Russia</t>
+        </is>
+      </c>
+      <c r="I91" s="18" t="n"/>
+      <c r="J91" s="18" t="n"/>
+      <c r="K91" s="18" t="inlineStr">
+        <is>
+          <t>NATO official texts</t>
+        </is>
+      </c>
+      <c r="L91" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M91" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N91" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O91" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P91" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q91" s="18" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/official_texts_25468.htm</t>
+        </is>
+      </c>
+      <c r="R91" s="18" t="inlineStr">
+        <is>
+          <t>The agreement Russia now says NATO broke.</t>
+        </is>
+      </c>
+      <c r="S91" s="18" t="n"/>
+      <c r="T91" s="18" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D92" s="18" t="inlineStr">
+        <is>
+          <t>10 February</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="inlineStr">
+        <is>
+          <t>2007-02-10</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G92" s="18" t="inlineStr">
+        <is>
+          <t>Speech and the Following Discussion at the Munich Conference on Security Policy</t>
+        </is>
+      </c>
+      <c r="H92" s="18" t="inlineStr">
+        <is>
+          <t>Vladimir Putin</t>
+        </is>
+      </c>
+      <c r="I92" s="18" t="n"/>
+      <c r="J92" s="18" t="n"/>
+      <c r="K92" s="18" t="inlineStr">
+        <is>
+          <t>President of Russia, English</t>
+        </is>
+      </c>
+      <c r="L92" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M92" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N92" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O92" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P92" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q92" s="18" t="inlineStr">
+        <is>
+          <t>http://en.kremlin.ru/events/president/transcripts/24034</t>
+        </is>
+      </c>
+      <c r="R92" s="18" t="inlineStr">
+        <is>
+          <t>Putin's break with the West, years before Ukraine.</t>
+        </is>
+      </c>
+      <c r="S92" s="18" t="n"/>
+      <c r="T92" s="18" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="18" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D93" s="18" t="inlineStr">
+        <is>
+          <t>18 March</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="inlineStr">
+        <is>
+          <t>2014-03-18</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G93" s="18" t="inlineStr">
+        <is>
+          <t>Address by President of the Russian Federation (Crimea)</t>
+        </is>
+      </c>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>Vladimir Putin</t>
+        </is>
+      </c>
+      <c r="I93" s="18" t="n"/>
+      <c r="J93" s="18" t="n"/>
+      <c r="K93" s="18" t="inlineStr">
+        <is>
+          <t>President of Russia, English</t>
+        </is>
+      </c>
+      <c r="L93" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M93" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N93" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O93" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P93" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q93" s="18" t="inlineStr">
+        <is>
+          <t>http://en.kremlin.ru/events/president/news/20603</t>
+        </is>
+      </c>
+      <c r="R93" s="18" t="inlineStr">
+        <is>
+          <t>The annexation of Crimea.</t>
+        </is>
+      </c>
+      <c r="S93" s="18" t="n"/>
+      <c r="T93" s="18" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="18" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D94" s="18" t="inlineStr">
+        <is>
+          <t>24 February</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G94" s="18" t="inlineStr">
+        <is>
+          <t>Address by the President of the Russian Federation</t>
+        </is>
+      </c>
+      <c r="H94" s="18" t="inlineStr">
+        <is>
+          <t>Vladimir Putin</t>
+        </is>
+      </c>
+      <c r="I94" s="18" t="n"/>
+      <c r="J94" s="18" t="n"/>
+      <c r="K94" s="18" t="inlineStr">
+        <is>
+          <t>President of Russia, English</t>
+        </is>
+      </c>
+      <c r="L94" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M94" s="18" t="inlineStr">
+        <is>
+          <t>military intervention</t>
+        </is>
+      </c>
+      <c r="N94" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O94" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P94" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q94" s="18" t="inlineStr">
+        <is>
+          <t>http://en.kremlin.ru/events/president/transcripts/67843</t>
+        </is>
+      </c>
+      <c r="R94" s="18" t="inlineStr">
+        <is>
+          <t>The announcement of the full invasion of Ukraine.</t>
+        </is>
+      </c>
+      <c r="S94" s="18" t="n"/>
+      <c r="T94" s="18" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="18" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="B95" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="D95" s="18" t="inlineStr">
+        <is>
+          <t>19 December</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="inlineStr">
+        <is>
+          <t>1984-12-19</t>
+        </is>
+      </c>
+      <c r="F95" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G95" s="18" t="inlineStr">
+        <is>
+          <t>Joint Declaration of the Government of the United Kingdom and the Government of the People's Republic of China on the Question of Hong Kong</t>
+        </is>
+      </c>
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>United Kingdom and the People's Republic of China</t>
+        </is>
+      </c>
+      <c r="I95" s="18" t="n"/>
+      <c r="J95" s="18" t="n"/>
+      <c r="K95" s="18" t="inlineStr">
+        <is>
+          <t>UN Treaty Series / UK Government</t>
+        </is>
+      </c>
+      <c r="L95" s="18" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="M95" s="18" t="inlineStr">
+        <is>
+          <t>alliances and commitments</t>
+        </is>
+      </c>
+      <c r="N95" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O95" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P95" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q95" s="18" t="inlineStr">
+        <is>
+          <t>https://treaties.un.org/doc/Publication/UNTS/Volume%201399/volume-1399-I-23391-English.pdf</t>
+        </is>
+      </c>
+      <c r="R95" s="18" t="inlineStr">
+        <is>
+          <t>The 'one country, two systems' promise behind the Hong Kong protests.</t>
+        </is>
+      </c>
+      <c r="S95" s="18" t="n"/>
+      <c r="T95" s="18" t="inlineStr">
+        <is>
+          <t>PDF; text not machine-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="B96" s="18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D96" s="18" t="inlineStr">
+        <is>
+          <t>20 July</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>2017-07-20</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G96" s="18" t="inlineStr">
+        <is>
+          <t>A Next Generation Artificial Intelligence Development Plan</t>
+        </is>
+      </c>
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>State Council of the People's Republic of China</t>
+        </is>
+      </c>
+      <c r="I96" s="18" t="n"/>
+      <c r="J96" s="18" t="n"/>
+      <c r="K96" s="18" t="inlineStr">
+        <is>
+          <t>DigiChina, Stanford University (translation)</t>
+        </is>
+      </c>
+      <c r="L96" s="18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="M96" s="18" t="inlineStr">
+        <is>
+          <t>state capacity and competence</t>
+        </is>
+      </c>
+      <c r="N96" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O96" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P96" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q96" s="18" t="inlineStr">
+        <is>
+          <t>https://digichina.stanford.edu/work/full-translation-chinas-new-generation-artificial-intelligence-development-plan-2017/</t>
+        </is>
+      </c>
+      <c r="R96" s="18" t="inlineStr">
+        <is>
+          <t>China's plan to lead the world in AI by 2030.</t>
+        </is>
+      </c>
+      <c r="S96" s="18" t="n"/>
+      <c r="T96" s="18" t="inlineStr">
+        <is>
+          <t>Translation hosted by a university project; no official English text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="B97" s="18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D97" s="18" t="inlineStr">
+        <is>
+          <t>15 January</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="F97" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: The Government and the Economy</t>
+        </is>
+      </c>
+      <c r="G97" s="18" t="inlineStr">
+        <is>
+          <t>Economic and Trade Agreement between the Government of the United States and the Government of the People's Republic of China (Phase One)</t>
+        </is>
+      </c>
+      <c r="H97" s="18" t="inlineStr">
+        <is>
+          <t>United States and China</t>
+        </is>
+      </c>
+      <c r="I97" s="18" t="n"/>
+      <c r="J97" s="18" t="n"/>
+      <c r="K97" s="18" t="inlineStr">
+        <is>
+          <t>Office of the United States Trade Representative</t>
+        </is>
+      </c>
+      <c r="L97" s="18" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="M97" s="18" t="inlineStr">
+        <is>
+          <t>trade and globalization</t>
+        </is>
+      </c>
+      <c r="N97" s="18" t="inlineStr">
+        <is>
+          <t>Extension 1981-2026</t>
+        </is>
+      </c>
+      <c r="O97" s="18" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P97" s="18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q97" s="18" t="inlineStr">
+        <is>
+          <t>https://ustr.gov/phase-one</t>
+        </is>
+      </c>
+      <c r="R97" s="18" t="inlineStr">
+        <is>
+          <t>The 2020 trade truce, and the commitments China did not meet.</t>
+        </is>
+      </c>
+      <c r="S97" s="18" t="n"/>
+      <c r="T97" s="18" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="17" min="1" max="1"/>
+    <col width="70" customWidth="1" style="17" min="2" max="2"/>
+    <col width="18" customWidth="1" style="17" min="3" max="3"/>
+    <col width="16" customWidth="1" style="17" min="4" max="4"/>
+    <col width="40" customWidth="1" style="17" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>WHY LENSES ARE A SEPARATE LIST (decided 2026-10-06; see docs/decisions.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A lens (a country, an alliance, a technology) is a tag on an object like Column E's Issue (Theme), but on a different axis: Column E says which American argument an object belongs to; a lens says who or what it is about. An object can have one theme and several lenses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>The objects follow the same rules as every matrix object: a primary text, a verified outward link, the link checker. What differs is the selection rule: a row's Beginnings are spread across time before its start year; a lens's are the three nearest before the story's origin. One kind of data, two rules, both in code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>For now lenses stay in editorial/lenses.json and these candidates carry a Lens column. A Lens column in the matrix itself (blank NTK Row allowed for purely foreign objects) is the likely end state. It changes the matrix schema, so it waits for a decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>A lens needs at least three linked objects before a story's origin to produce Beginnings. Fewer, and the page shows the origin alone: a thin lens is a to-do, not a failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Matches by</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Linked objects in the matrix today</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Candidates in this round</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>title: telecommunications, fairness doctrine, patriot act, internet, computer, privacy, section 230, antitrust, sherman act, wiretap</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>title: china, chinese communist, taiwan, formosa, shanghai; row: Taiwan</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>title: soviet, moscow, russia, kremlin</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>title: iran, iranian, persian gulf</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>title: israel, israeli, zionism, zionist; sub-genre: Israel-Palestine policy</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>lebanon</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>title: lebanon, lebanese, beirut</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>syria</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>title: syria, syrian</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>iraq</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>title: iraq, iraqi, kuwait, gulf war; listed ids: 2003-02-05-address-to-the-united-nations-security-council</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>title: canada, canadian</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>nato</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>title: nato, north atlantic</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>title: argentina, argentine</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>australia</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>title: australia, australian</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>brazil</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>title: brazil, brazilian</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>title: france, french</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>title: germany, german, germans</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>title: india, indian subcontinent, indian ocean</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>title: indonesia, indonesian</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>title: italy, italian</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>japan</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>title: japan, japanese</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>title: mexico, mexican, mexicans</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>saudi-arabia</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>title: saudi, saudi arabia</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>south-africa</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>title: south africa, south african, apartheid</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>south-korea</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>title: south korea, south korean, korea, korean; row: Korea</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>turkey</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>title: turkey, turkish, ottoman</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>title: great britain, britain, british, england, united kingdom</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/editorial/NTK_Backstory_Candidates.xlsx
+++ b/editorial/NTK_Backstory_Candidates.xlsx
@@ -2987,7 +2987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T97"/>
+  <dimension ref="A1:T105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" style="17" min="1" max="1"/>
@@ -5666,12 +5666,12 @@
       </c>
       <c r="P31" s="18" t="inlineStr">
         <is>
-          <t>needs-check</t>
+          <t>live-pdf</t>
         </is>
       </c>
       <c r="Q31" s="18" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1559(2004)</t>
+          <t>https://documents.un.org/doc/undoc/gen/n04/498/92/pdf/n0449892.pdf</t>
         </is>
       </c>
       <c r="R31" s="18" t="inlineStr">
@@ -5682,7 +5682,7 @@
       <c r="S31" s="18" t="n"/>
       <c r="T31" s="18" t="inlineStr">
         <is>
-          <t>UN viewer is JavaScript; open to confirm.</t>
+          <t>UN viewer is JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read.</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="P32" s="18" t="inlineStr">
         <is>
-          <t>needs-check</t>
+          <t>live-pdf</t>
         </is>
       </c>
       <c r="Q32" s="18" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+          <t>https://documents.un.org/doc/undoc/gen/n06/465/03/pdf/n0646503.pdf</t>
         </is>
       </c>
       <c r="R32" s="18" t="inlineStr">
@@ -5770,7 +5770,7 @@
       <c r="S32" s="18" t="n"/>
       <c r="T32" s="18" t="inlineStr">
         <is>
-          <t>UN viewer is JavaScript; open to confirm.</t>
+          <t>UN viewer is JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read.</t>
         </is>
       </c>
     </row>
@@ -10722,12 +10722,12 @@
       </c>
       <c r="P90" s="18" t="inlineStr">
         <is>
-          <t>needs-check</t>
+          <t>live-pdf</t>
         </is>
       </c>
       <c r="Q90" s="18" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/A/49/765</t>
+          <t>https://documents.un.org/doc/undoc/gen/n94/507/64/pdf/n9450764.pdf</t>
         </is>
       </c>
       <c r="R90" s="18" t="inlineStr">
@@ -10738,7 +10738,7 @@
       <c r="S90" s="18" t="n"/>
       <c r="T90" s="18" t="inlineStr">
         <is>
-          <t>UN viewers are JavaScript; open to confirm.</t>
+          <t>UN viewers are JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read.</t>
         </is>
       </c>
     </row>
@@ -11337,6 +11337,646 @@
       </c>
       <c r="S97" s="18" t="n"/>
       <c r="T97" s="18" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>sudan</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>31 March</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2005-03-31</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 1593</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>United Nations Official Document System</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>https://documents.un.org/doc/undoc/gen/n05/292/73/pdf/n0529273.pdf</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>The Council referred Darfur to the International Criminal Court; the Janjaweed it named are the forerunners of today's RSF.</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>sudan</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>17 August</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2019-08-17</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Constitutional Charter for the 2019 Transitional Period</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Transitional Military Council and the Forces of Freedom and Change</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Constitute Project</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Sudan_2019</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>The power-sharing deal after Bashir fell that put the army, the RSF and civilians in one transitional government.</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>sudan</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>28 October</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2021-10-28</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Security Council Press Statement on Sudan (SC/14678)</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>UN Meetings Coverage and Press Releases</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>https://press.un.org/en/2021/sc14678.doc.htm</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>The Council's response to the October 2021 military takeover that ended the civilian-led transition.</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>sudan</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>8 December</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2022-12-08</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Security Council Press Statement on Sudan (SC/15132)</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>UN Meetings Coverage and Press Releases</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>https://press.un.org/en/2022/sc15132.doc.htm</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>The Council welcomed the December 2022 framework agreement whose unsettled security reform set the army and RSF against each other.</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>venezuela</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>15 December</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1999-12-15</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Constitution of the Bolivarian Republic of Venezuela (1999, rev. 2009)</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>People of Venezuela (Constituent Assembly)</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Constitute Project</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Venezuela_2009</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Chavez's constitution, the legal frame of the state Maduro inherited.</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>venezuela</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>5 August</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2019-08-05</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Executive Order 13884: Blocking Property of the Government of Venezuela</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Federal Register (GovInfo)</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/FR-2019-08-07/pdf/2019-17052.pdf</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>The United States froze all property of the Venezuelan government in its jurisdiction.</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>venezuela</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>30 July</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Carter Center Statement on Venezuela Election</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>The Carter Center</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>The Carter Center</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>https://www.cartercenter.org/news/pr/2024/venezuela-073024.html</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>The invited observer said the 2024 presidential election cannot be considered democratic.</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>venezuela</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3 January</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Truth Social Posts of January 3, 2026</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>The American Presidency Project</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>https://www.presidency.ucsb.edu/node/394200</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>The president's announcement that U.S. forces captured Maduro: the day the Venezuela clock starts.</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11425,479 +12065,479 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>title: telecommunications, fairness doctrine, patriot act, internet, computer, privacy, section 230, antitrust, sherman act, wiretap</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>china</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>title: china, chinese communist, taiwan, formosa, shanghai; row: Taiwan</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>russia</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>title: soviet, moscow, russia, kremlin</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>iran</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>title: iran, iranian, persian gulf</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>israel</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>title: israel, israeli, zionism, zionist; sub-genre: Israel-Palestine policy</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>lebanon</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>title: lebanon, lebanese, beirut</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>syria</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>title: syria, syrian</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>iraq</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>title: iraq, iraqi, kuwait, gulf war; listed ids: 2003-02-05-address-to-the-united-nations-security-council</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>canada</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>title: canada, canadian</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>nato</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>title: nato, north atlantic</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>argentina</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>title: argentina, argentine</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>australia</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>title: australia, australian</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>brazil</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>title: brazil, brazilian</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>title: france, french</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>title: germany, german, germans</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>india</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>title: india, indian subcontinent, indian ocean</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>indonesia</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t>title: indonesia, indonesian</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" s="1" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>title: italy, italian</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" s="1" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>japan</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>title: japan, japanese</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" s="1" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>mexico</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>title: mexico, mexican, mexicans</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" s="1" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>saudi-arabia</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr">
         <is>
           <t>title: saudi, saudi arabia</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>south-africa</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>title: south africa, south african, apartheid</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" s="1" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>south-korea</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>title: south korea, south korean, korea, korean; row: Korea</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" s="1" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>turkey</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>title: turkey, turkish, ottoman</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" s="1" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>uk</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>title: great britain, britain, british, england, united kingdom</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/editorial/NTK_Backstory_Candidates.xlsx
+++ b/editorial/NTK_Backstory_Candidates.xlsx
@@ -2987,7 +2987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T105"/>
+  <dimension ref="A1:T110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" style="17" min="1" max="1"/>
@@ -3195,8 +3195,16 @@
           <t>Britain's statement of support for a Jewish national home in Palestine; the earliest document most later ones answer.</t>
         </is>
       </c>
-      <c r="S2" s="18" t="n"/>
-      <c r="T2" s="18" t="inlineStr"/>
+      <c r="S2" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T2" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
@@ -3279,8 +3287,16 @@
           <t>The UN vote to divide Palestine into a Jewish and an Arab state; the legal starting point for both sides' claims.</t>
         </is>
       </c>
-      <c r="S3" s="18" t="n"/>
-      <c r="T3" s="18" t="inlineStr"/>
+      <c r="S3" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T3" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
@@ -3363,10 +3379,14 @@
           <t>Israel's founding statement, issued the day the British Mandate ended.</t>
         </is>
       </c>
-      <c r="S4" s="18" t="n"/>
+      <c r="S4" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T4" s="18" t="inlineStr">
         <is>
-          <t>The Knesset's own page was down during the check, so this links Avalon.</t>
+          <t>The Knesset's own page was down during the check, so this links Avalon. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -3451,8 +3471,16 @@
           <t>The land-for-peace resolution after the Six-Day War; cited in nearly every later negotiation.</t>
         </is>
       </c>
-      <c r="S5" s="18" t="n"/>
-      <c r="T5" s="18" t="inlineStr"/>
+      <c r="S5" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T5" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
@@ -3535,10 +3563,14 @@
           <t>Hamas's founding text: the other side's own statement of aims, set beside Israel's Declaration.</t>
         </is>
       </c>
-      <c r="S6" s="18" t="n"/>
+      <c r="S6" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T6" s="18" t="inlineStr">
         <is>
-          <t>SENSITIVE: your call whether to include. Hamas issued a revised document in 2017.</t>
+          <t>SENSITIVE: your call whether to include. Hamas issued a revised document in 2017. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -3623,8 +3655,16 @@
           <t>The first agreement in which Israel and the PLO recognized each other; the framework of the peace process.</t>
         </is>
       </c>
-      <c r="S7" s="18" t="n"/>
-      <c r="T7" s="18" t="inlineStr"/>
+      <c r="S7" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T7" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
@@ -3707,10 +3747,14 @@
           <t>Iran's governing text since the revolution; defines the Supreme Leader's role the news keeps returning to.</t>
         </is>
       </c>
-      <c r="S8" s="18" t="n"/>
+      <c r="S8" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T8" s="18" t="inlineStr">
         <is>
-          <t>Constitute is a repository of official translations, not a government site. Date is when the 1979 constitution was approved; the text is the 1989 amended version.</t>
+          <t>Constitute is a repository of official translations, not a government site. Date is when the 1979 constitution was approved; the text is the 1989 amended version. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -3795,10 +3839,14 @@
           <t>The agreement that ended the hostage crisis; it also pledged non-interference in Iran's internal affairs.</t>
         </is>
       </c>
-      <c r="S9" s="18" t="n"/>
+      <c r="S9" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T9" s="18" t="inlineStr">
         <is>
-          <t>Hosted by the tribunal the accords created.</t>
+          <t>Hosted by the tribunal the accords created. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -3971,10 +4019,14 @@
           <t>The 2015 nuclear deal: what it limited, and what the 2018 withdrawal ended.</t>
         </is>
       </c>
-      <c r="S11" s="18" t="n"/>
+      <c r="S11" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T11" s="18" t="inlineStr">
         <is>
-          <t>PDF opened (200); text not machine-checked.</t>
+          <t>PDF opened (200); text not machine-checked. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -4059,8 +4111,16 @@
           <t>The order that withdrew the United States from the deal; the proximate cause of later escalation.</t>
         </is>
       </c>
-      <c r="S12" s="18" t="n"/>
-      <c r="T12" s="18" t="inlineStr"/>
+      <c r="S12" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T12" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
@@ -4399,10 +4459,14 @@
           <t>The agreement that began today's integrated North American economy.</t>
         </is>
       </c>
-      <c r="S16" s="18" t="n"/>
+      <c r="S16" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T16" s="18" t="inlineStr">
         <is>
-          <t>10 MB PDF opened (200); text not machine-checked. Alternative: the U.S. House document at govinfo (H. Doc. 100-216).</t>
+          <t>10 MB PDF opened (200); text not machine-checked. Alternative: the U.S. House document at govinfo (H. Doc. 100-216). Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -4487,8 +4551,16 @@
           <t>The trade pact now under strain.</t>
         </is>
       </c>
-      <c r="S17" s="18" t="n"/>
-      <c r="T17" s="18" t="inlineStr"/>
+      <c r="S17" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T17" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
@@ -4571,8 +4643,16 @@
           <t>The first tariffs on Canada of the second Trump term.</t>
         </is>
       </c>
-      <c r="S18" s="18" t="n"/>
-      <c r="T18" s="18" t="inlineStr"/>
+      <c r="S18" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T18" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
@@ -5595,8 +5675,16 @@
           <t>Ended the civil war and set the sectarian power-sharing still in force.</t>
         </is>
       </c>
-      <c r="S30" s="18" t="n"/>
-      <c r="T30" s="18" t="inlineStr"/>
+      <c r="S30" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T30" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
@@ -5679,10 +5767,14 @@
           <t>Called for foreign forces to leave Lebanon and for militias, meaning Hezbollah, to disband.</t>
         </is>
       </c>
-      <c r="S31" s="18" t="n"/>
+      <c r="S31" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T31" s="18" t="inlineStr">
         <is>
-          <t>UN viewer is JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read.</t>
+          <t>UN viewer is JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -5767,10 +5859,14 @@
           <t>Ended the 2006 Israel-Hezbollah war and set the terms the 2024 ceasefire still cites.</t>
         </is>
       </c>
-      <c r="S32" s="18" t="n"/>
+      <c r="S32" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T32" s="18" t="inlineStr">
         <is>
-          <t>UN viewer is JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read.</t>
+          <t>UN viewer is JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -6203,8 +6299,16 @@
           <t>The first U.S. sanctions law aimed at the Syrian government.</t>
         </is>
       </c>
-      <c r="S37" s="18" t="n"/>
-      <c r="T37" s="18" t="inlineStr"/>
+      <c r="S37" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T37" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
@@ -10735,10 +10839,14 @@
           <t>Ukraine gave up its nuclear weapons for assurances Russia later broke.</t>
         </is>
       </c>
-      <c r="S90" s="18" t="n"/>
+      <c r="S90" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T90" s="18" t="inlineStr">
         <is>
-          <t>UN viewers are JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read.</t>
+          <t>UN viewers are JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -10823,8 +10931,16 @@
           <t>The agreement Russia now says NATO broke.</t>
         </is>
       </c>
-      <c r="S91" s="18" t="n"/>
-      <c r="T91" s="18" t="inlineStr"/>
+      <c r="S91" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T91" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
@@ -10907,8 +11023,16 @@
           <t>Putin's break with the West, years before Ukraine.</t>
         </is>
       </c>
-      <c r="S92" s="18" t="n"/>
-      <c r="T92" s="18" t="inlineStr"/>
+      <c r="S92" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T92" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
@@ -10991,8 +11115,16 @@
           <t>The annexation of Crimea.</t>
         </is>
       </c>
-      <c r="S93" s="18" t="n"/>
-      <c r="T93" s="18" t="inlineStr"/>
+      <c r="S93" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T93" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
@@ -11075,8 +11207,16 @@
           <t>The announcement of the full invasion of Ukraine.</t>
         </is>
       </c>
-      <c r="S94" s="18" t="n"/>
-      <c r="T94" s="18" t="inlineStr"/>
+      <c r="S94" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T94" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
@@ -11339,642 +11479,1107 @@
       <c r="T97" s="18" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="1" t="inlineStr">
         <is>
           <t>sudan</t>
         </is>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="1" t="inlineStr">
         <is>
           <t>31 March</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E98" s="1" t="inlineStr">
         <is>
           <t>2005-03-31</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="1" t="inlineStr">
         <is>
           <t>Contemporary Challenges: Foreign Policy</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G98" s="1" t="inlineStr">
         <is>
           <t>UN Security Council Resolution 1593</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H98" s="1" t="inlineStr">
         <is>
           <t>United Nations Security Council</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K98" s="1" t="inlineStr">
         <is>
           <t>United Nations Official Document System</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L98" s="1" t="inlineStr">
         <is>
           <t>America Abroad</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="N98" s="1" t="inlineStr">
         <is>
           <t>Addition, post-1981</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="O98" s="1" t="inlineStr">
         <is>
           <t>researched</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="P98" s="1" t="inlineStr">
         <is>
           <t>live-pdf</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="Q98" s="1" t="inlineStr">
         <is>
           <t>https://documents.un.org/doc/undoc/gen/n05/292/73/pdf/n0529273.pdf</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="R98" s="1" t="inlineStr">
         <is>
           <t>The Council referred Darfur to the International Criminal Court; the Janjaweed it named are the forerunners of today's RSF.</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T98" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="1" t="inlineStr">
         <is>
           <t>sudan</t>
         </is>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" s="1" t="inlineStr">
         <is>
           <t>17 August</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E99" s="1" t="inlineStr">
         <is>
           <t>2019-08-17</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" s="1" t="inlineStr">
         <is>
           <t>Contemporary Challenges: Foreign Policy</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G99" s="1" t="inlineStr">
         <is>
           <t>Constitutional Charter for the 2019 Transitional Period</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99" s="1" t="inlineStr">
         <is>
           <t>Transitional Military Council and the Forces of Freedom and Change</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="K99" s="1" t="inlineStr">
         <is>
           <t>Constitute Project</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="L99" s="1" t="inlineStr">
         <is>
           <t>America Abroad</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="N99" s="1" t="inlineStr">
         <is>
           <t>Addition, post-1981</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="O99" s="1" t="inlineStr">
         <is>
           <t>researched</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="P99" s="1" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="Q99" s="1" t="inlineStr">
         <is>
           <t>https://www.constituteproject.org/constitution/Sudan_2019</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="R99" s="1" t="inlineStr">
         <is>
           <t>The power-sharing deal after Bashir fell that put the army, the RSF and civilians in one transitional government.</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T99" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="1" t="inlineStr">
         <is>
           <t>sudan</t>
         </is>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="1" t="inlineStr">
         <is>
           <t>28 October</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E100" s="1" t="inlineStr">
         <is>
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="1" t="inlineStr">
         <is>
           <t>Contemporary Challenges: Foreign Policy</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G100" s="1" t="inlineStr">
         <is>
           <t>Security Council Press Statement on Sudan (SC/14678)</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H100" s="1" t="inlineStr">
         <is>
           <t>United Nations Security Council</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K100" s="1" t="inlineStr">
         <is>
           <t>UN Meetings Coverage and Press Releases</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="L100" s="1" t="inlineStr">
         <is>
           <t>America Abroad</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
+      <c r="N100" s="1" t="inlineStr">
         <is>
           <t>Addition, post-1981</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="O100" s="1" t="inlineStr">
         <is>
           <t>researched</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="P100" s="1" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="Q100" s="1" t="inlineStr">
         <is>
           <t>https://press.un.org/en/2021/sc14678.doc.htm</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="R100" s="1" t="inlineStr">
         <is>
           <t>The Council's response to the October 2021 military takeover that ended the civilian-led transition.</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T100" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="1" t="inlineStr">
         <is>
           <t>sudan</t>
         </is>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="1" t="inlineStr">
         <is>
           <t>8 December</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" s="1" t="inlineStr">
         <is>
           <t>2022-12-08</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" s="1" t="inlineStr">
         <is>
           <t>Contemporary Challenges: Foreign Policy</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G101" s="1" t="inlineStr">
         <is>
           <t>Security Council Press Statement on Sudan (SC/15132)</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H101" s="1" t="inlineStr">
         <is>
           <t>United Nations Security Council</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="K101" s="1" t="inlineStr">
         <is>
           <t>UN Meetings Coverage and Press Releases</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="L101" s="1" t="inlineStr">
         <is>
           <t>America Abroad</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
+      <c r="N101" s="1" t="inlineStr">
         <is>
           <t>Addition, post-1981</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="O101" s="1" t="inlineStr">
         <is>
           <t>researched</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="P101" s="1" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr">
+      <c r="Q101" s="1" t="inlineStr">
         <is>
           <t>https://press.un.org/en/2022/sc15132.doc.htm</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr">
+      <c r="R101" s="1" t="inlineStr">
         <is>
           <t>The Council welcomed the December 2022 framework agreement whose unsettled security reform set the army and RSF against each other.</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T101" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="1" t="inlineStr">
         <is>
           <t>venezuela</t>
         </is>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" s="1" t="n">
         <v>1990</v>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="1" t="inlineStr">
         <is>
           <t>15 December</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E102" s="1" t="inlineStr">
         <is>
           <t>1999-12-15</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="1" t="inlineStr">
         <is>
           <t>Contemporary Challenges: Foreign Policy</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G102" s="1" t="inlineStr">
         <is>
           <t>Constitution of the Bolivarian Republic of Venezuela (1999, rev. 2009)</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" s="1" t="inlineStr">
         <is>
           <t>People of Venezuela (Constituent Assembly)</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="K102" s="1" t="inlineStr">
         <is>
           <t>Constitute Project</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="L102" s="1" t="inlineStr">
         <is>
           <t>America Abroad</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
+      <c r="N102" s="1" t="inlineStr">
         <is>
           <t>Addition, post-1981</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="O102" s="1" t="inlineStr">
         <is>
           <t>researched</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
+      <c r="P102" s="1" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr">
+      <c r="Q102" s="1" t="inlineStr">
         <is>
           <t>https://www.constituteproject.org/constitution/Venezuela_2009</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="R102" s="1" t="inlineStr">
         <is>
           <t>Chavez's constitution, the legal frame of the state Maduro inherited.</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T102" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="1" t="inlineStr">
         <is>
           <t>venezuela</t>
         </is>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="1" t="inlineStr">
         <is>
           <t>5 August</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="1" t="inlineStr">
         <is>
           <t>2019-08-05</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="1" t="inlineStr">
         <is>
           <t>Contemporary Challenges: Foreign Policy</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>Executive Order 13884: Blocking Property of the Government of Venezuela</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H103" s="1" t="inlineStr">
         <is>
           <t>Donald J. Trump</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="K103" s="1" t="inlineStr">
         <is>
           <t>Federal Register (GovInfo)</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="L103" s="1" t="inlineStr">
         <is>
           <t>America Abroad</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
+      <c r="N103" s="1" t="inlineStr">
         <is>
           <t>Addition, post-1981</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="O103" s="1" t="inlineStr">
         <is>
           <t>researched</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="P103" s="1" t="inlineStr">
         <is>
           <t>live-pdf</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr">
+      <c r="Q103" s="1" t="inlineStr">
         <is>
           <t>https://www.govinfo.gov/content/pkg/FR-2019-08-07/pdf/2019-17052.pdf</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="R103" s="1" t="inlineStr">
         <is>
           <t>The United States froze all property of the Venezuelan government in its jurisdiction.</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T103" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="1" t="inlineStr">
         <is>
           <t>venezuela</t>
         </is>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="1" t="inlineStr">
         <is>
           <t>30 July</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E104" s="1" t="inlineStr">
         <is>
           <t>2024-07-30</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" s="1" t="inlineStr">
         <is>
           <t>Contemporary Challenges: Foreign Policy</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G104" s="1" t="inlineStr">
         <is>
           <t>Carter Center Statement on Venezuela Election</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H104" s="1" t="inlineStr">
         <is>
           <t>The Carter Center</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K104" s="1" t="inlineStr">
         <is>
           <t>The Carter Center</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="L104" s="1" t="inlineStr">
         <is>
           <t>America Abroad</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
+      <c r="N104" s="1" t="inlineStr">
         <is>
           <t>Addition, post-1981</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="O104" s="1" t="inlineStr">
         <is>
           <t>researched</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="P104" s="1" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
+      <c r="Q104" s="1" t="inlineStr">
         <is>
           <t>https://www.cartercenter.org/news/pr/2024/venezuela-073024.html</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="R104" s="1" t="inlineStr">
         <is>
           <t>The invited observer said the 2024 presidential election cannot be considered democratic.</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T104" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="1" t="inlineStr">
         <is>
           <t>venezuela</t>
         </is>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" s="1" t="inlineStr">
         <is>
           <t>3 January</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E105" s="1" t="inlineStr">
         <is>
           <t>2026-01-03</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" s="1" t="inlineStr">
         <is>
           <t>Contemporary Challenges: Foreign Policy</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G105" s="1" t="inlineStr">
         <is>
           <t>Truth Social Posts of January 3, 2026</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H105" s="1" t="inlineStr">
         <is>
           <t>Donald J. Trump</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="K105" s="1" t="inlineStr">
         <is>
           <t>The American Presidency Project</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="L105" s="1" t="inlineStr">
         <is>
           <t>America Abroad</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
+      <c r="N105" s="1" t="inlineStr">
         <is>
           <t>Addition, post-1981</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="O105" s="1" t="inlineStr">
         <is>
           <t>researched</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="P105" s="1" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="Q105" s="1" t="inlineStr">
         <is>
           <t>https://www.presidency.ucsb.edu/node/394200</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="R105" s="1" t="inlineStr">
         <is>
           <t>The president's announcement that U.S. forces captured Maduro: the day the Venezuela clock starts.</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>2026-10-21: found for the live-conflict page; link fetched and read.</t>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T105" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr">
+        <is>
+          <t>20 January</t>
+        </is>
+      </c>
+      <c r="E106" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="F106" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>Principled and pragmatic: Canada's path (address to the World Economic Forum)</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="inlineStr">
+        <is>
+          <t>Mark Carney</t>
+        </is>
+      </c>
+      <c r="K106" s="1" t="inlineStr">
+        <is>
+          <t>Prime Minister of Canada</t>
+        </is>
+      </c>
+      <c r="L106" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N106" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O106" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P106" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q106" s="1" t="inlineStr">
+        <is>
+          <t>https://www.pm.gc.ca/en/news/speeches/2026/01/20/principled-and-pragmatic-canadas-path-prime-minister-carney-addresses</t>
+        </is>
+      </c>
+      <c r="R106" s="1" t="inlineStr">
+        <is>
+          <t>Carney's Davos case that middle powers must act together against economic coercion by great powers.</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T106" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: added at the editor's request for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t>6 June</t>
+        </is>
+      </c>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t>2004-06-06</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G107" s="1" t="inlineStr">
+        <is>
+          <t>Cabinet Resolution Regarding the Disengagement Plan</t>
+        </is>
+      </c>
+      <c r="H107" s="1" t="inlineStr">
+        <is>
+          <t>Government of Israel</t>
+        </is>
+      </c>
+      <c r="K107" s="1" t="inlineStr">
+        <is>
+          <t>UN Peacemaker</t>
+        </is>
+      </c>
+      <c r="L107" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N107" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O107" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P107" s="1" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q107" s="1" t="inlineStr">
+        <is>
+          <t>https://peacemaker.un.org/sites/default/files/document/files/2024/05/israeloptcabinetresolutionregardingdisengagementplan2004.pdf</t>
+        </is>
+      </c>
+      <c r="R107" s="1" t="inlineStr">
+        <is>
+          <t>Israel's decision to withdraw its settlements and forces from Gaza, carried out in 2005.</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T107" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: added at the editor's request for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>19 September</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>2007-09-19</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t>Security Cabinet declares Gaza hostile territory</t>
+        </is>
+      </c>
+      <c r="H108" s="1" t="inlineStr">
+        <is>
+          <t>Israel Ministry of Foreign Affairs</t>
+        </is>
+      </c>
+      <c r="K108" s="1" t="inlineStr">
+        <is>
+          <t>UNISPAL (United Nations)</t>
+        </is>
+      </c>
+      <c r="L108" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N108" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O108" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P108" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q108" s="1" t="inlineStr">
+        <is>
+          <t>https://www.un.org/unispal/document/auto-insert-195603</t>
+        </is>
+      </c>
+      <c r="R108" s="1" t="inlineStr">
+        <is>
+          <t>After Hamas took control of Gaza, Israel declared it hostile territory and restricted fuel, electricity and movement.</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T108" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: added at the editor's request for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
+        <is>
+          <t>21 June</t>
+        </is>
+      </c>
+      <c r="E109" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="F109" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G109" s="1" t="inlineStr">
+        <is>
+          <t>Address to the Nation on United States Airstrikes on Iran</t>
+        </is>
+      </c>
+      <c r="H109" s="1" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="K109" s="1" t="inlineStr">
+        <is>
+          <t>Daily Compilation of Presidential Documents (GovInfo)</t>
+        </is>
+      </c>
+      <c r="L109" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N109" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O109" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P109" s="1" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q109" s="1" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/DCPD-202500711/pdf/DCPD-202500711.pdf</t>
+        </is>
+      </c>
+      <c r="R109" s="1" t="inlineStr">
+        <is>
+          <t>The first American strikes on Iran's nuclear sites, eight months before the war this page counts.</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T109" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: added at the editor's request for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>28 February</t>
+        </is>
+      </c>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>Remarks Announcing Major Combat Operations in Iran in Palm Beach, Florida</t>
+        </is>
+      </c>
+      <c r="H110" s="1" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="K110" s="1" t="inlineStr">
+        <is>
+          <t>The American Presidency Project</t>
+        </is>
+      </c>
+      <c r="L110" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N110" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O110" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P110" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q110" s="1" t="inlineStr">
+        <is>
+          <t>https://www.presidency.ucsb.edu/documents/remarks-announcing-major-combat-operations-iran-palm-beach-florida</t>
+        </is>
+      </c>
+      <c r="R110" s="1" t="inlineStr">
+        <is>
+          <t>The announcement of the war with Iran: the day this page counts from.</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T110" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: added at the editor's request for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>

--- a/editorial/NTK_Backstory_Candidates.xlsx
+++ b/editorial/NTK_Backstory_Candidates.xlsx
@@ -2987,7 +2987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T97"/>
+  <dimension ref="A1:T110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" style="17" min="1" max="1"/>
@@ -3195,8 +3195,16 @@
           <t>Britain's statement of support for a Jewish national home in Palestine; the earliest document most later ones answer.</t>
         </is>
       </c>
-      <c r="S2" s="18" t="n"/>
-      <c r="T2" s="18" t="inlineStr"/>
+      <c r="S2" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T2" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
@@ -3279,8 +3287,16 @@
           <t>The UN vote to divide Palestine into a Jewish and an Arab state; the legal starting point for both sides' claims.</t>
         </is>
       </c>
-      <c r="S3" s="18" t="n"/>
-      <c r="T3" s="18" t="inlineStr"/>
+      <c r="S3" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T3" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
@@ -3363,10 +3379,14 @@
           <t>Israel's founding statement, issued the day the British Mandate ended.</t>
         </is>
       </c>
-      <c r="S4" s="18" t="n"/>
+      <c r="S4" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T4" s="18" t="inlineStr">
         <is>
-          <t>The Knesset's own page was down during the check, so this links Avalon.</t>
+          <t>The Knesset's own page was down during the check, so this links Avalon. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -3451,8 +3471,16 @@
           <t>The land-for-peace resolution after the Six-Day War; cited in nearly every later negotiation.</t>
         </is>
       </c>
-      <c r="S5" s="18" t="n"/>
-      <c r="T5" s="18" t="inlineStr"/>
+      <c r="S5" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T5" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
@@ -3535,10 +3563,14 @@
           <t>Hamas's founding text: the other side's own statement of aims, set beside Israel's Declaration.</t>
         </is>
       </c>
-      <c r="S6" s="18" t="n"/>
+      <c r="S6" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T6" s="18" t="inlineStr">
         <is>
-          <t>SENSITIVE: your call whether to include. Hamas issued a revised document in 2017.</t>
+          <t>SENSITIVE: your call whether to include. Hamas issued a revised document in 2017. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -3623,8 +3655,16 @@
           <t>The first agreement in which Israel and the PLO recognized each other; the framework of the peace process.</t>
         </is>
       </c>
-      <c r="S7" s="18" t="n"/>
-      <c r="T7" s="18" t="inlineStr"/>
+      <c r="S7" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T7" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
@@ -3707,10 +3747,14 @@
           <t>Iran's governing text since the revolution; defines the Supreme Leader's role the news keeps returning to.</t>
         </is>
       </c>
-      <c r="S8" s="18" t="n"/>
+      <c r="S8" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T8" s="18" t="inlineStr">
         <is>
-          <t>Constitute is a repository of official translations, not a government site. Date is when the 1979 constitution was approved; the text is the 1989 amended version.</t>
+          <t>Constitute is a repository of official translations, not a government site. Date is when the 1979 constitution was approved; the text is the 1989 amended version. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -3795,10 +3839,14 @@
           <t>The agreement that ended the hostage crisis; it also pledged non-interference in Iran's internal affairs.</t>
         </is>
       </c>
-      <c r="S9" s="18" t="n"/>
+      <c r="S9" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T9" s="18" t="inlineStr">
         <is>
-          <t>Hosted by the tribunal the accords created.</t>
+          <t>Hosted by the tribunal the accords created. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -3971,10 +4019,14 @@
           <t>The 2015 nuclear deal: what it limited, and what the 2018 withdrawal ended.</t>
         </is>
       </c>
-      <c r="S11" s="18" t="n"/>
+      <c r="S11" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T11" s="18" t="inlineStr">
         <is>
-          <t>PDF opened (200); text not machine-checked.</t>
+          <t>PDF opened (200); text not machine-checked. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -4059,8 +4111,16 @@
           <t>The order that withdrew the United States from the deal; the proximate cause of later escalation.</t>
         </is>
       </c>
-      <c r="S12" s="18" t="n"/>
-      <c r="T12" s="18" t="inlineStr"/>
+      <c r="S12" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T12" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
@@ -4399,10 +4459,14 @@
           <t>The agreement that began today's integrated North American economy.</t>
         </is>
       </c>
-      <c r="S16" s="18" t="n"/>
+      <c r="S16" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T16" s="18" t="inlineStr">
         <is>
-          <t>10 MB PDF opened (200); text not machine-checked. Alternative: the U.S. House document at govinfo (H. Doc. 100-216).</t>
+          <t>10 MB PDF opened (200); text not machine-checked. Alternative: the U.S. House document at govinfo (H. Doc. 100-216). Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -4487,8 +4551,16 @@
           <t>The trade pact now under strain.</t>
         </is>
       </c>
-      <c r="S17" s="18" t="n"/>
-      <c r="T17" s="18" t="inlineStr"/>
+      <c r="S17" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T17" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
@@ -4571,8 +4643,16 @@
           <t>The first tariffs on Canada of the second Trump term.</t>
         </is>
       </c>
-      <c r="S18" s="18" t="n"/>
-      <c r="T18" s="18" t="inlineStr"/>
+      <c r="S18" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T18" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
@@ -5595,8 +5675,16 @@
           <t>Ended the civil war and set the sectarian power-sharing still in force.</t>
         </is>
       </c>
-      <c r="S30" s="18" t="n"/>
-      <c r="T30" s="18" t="inlineStr"/>
+      <c r="S30" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T30" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
@@ -5666,12 +5754,12 @@
       </c>
       <c r="P31" s="18" t="inlineStr">
         <is>
-          <t>needs-check</t>
+          <t>live-pdf</t>
         </is>
       </c>
       <c r="Q31" s="18" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1559(2004)</t>
+          <t>https://documents.un.org/doc/undoc/gen/n04/498/92/pdf/n0449892.pdf</t>
         </is>
       </c>
       <c r="R31" s="18" t="inlineStr">
@@ -5679,10 +5767,14 @@
           <t>Called for foreign forces to leave Lebanon and for militias, meaning Hezbollah, to disband.</t>
         </is>
       </c>
-      <c r="S31" s="18" t="n"/>
+      <c r="S31" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T31" s="18" t="inlineStr">
         <is>
-          <t>UN viewer is JavaScript; open to confirm.</t>
+          <t>UN viewer is JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5846,12 @@
       </c>
       <c r="P32" s="18" t="inlineStr">
         <is>
-          <t>needs-check</t>
+          <t>live-pdf</t>
         </is>
       </c>
       <c r="Q32" s="18" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+          <t>https://documents.un.org/doc/undoc/gen/n06/465/03/pdf/n0646503.pdf</t>
         </is>
       </c>
       <c r="R32" s="18" t="inlineStr">
@@ -5767,10 +5859,14 @@
           <t>Ended the 2006 Israel-Hezbollah war and set the terms the 2024 ceasefire still cites.</t>
         </is>
       </c>
-      <c r="S32" s="18" t="n"/>
+      <c r="S32" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T32" s="18" t="inlineStr">
         <is>
-          <t>UN viewer is JavaScript; open to confirm.</t>
+          <t>UN viewer is JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -6203,8 +6299,16 @@
           <t>The first U.S. sanctions law aimed at the Syrian government.</t>
         </is>
       </c>
-      <c r="S37" s="18" t="n"/>
-      <c r="T37" s="18" t="inlineStr"/>
+      <c r="S37" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T37" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
@@ -10722,12 +10826,12 @@
       </c>
       <c r="P90" s="18" t="inlineStr">
         <is>
-          <t>needs-check</t>
+          <t>live-pdf</t>
         </is>
       </c>
       <c r="Q90" s="18" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/A/49/765</t>
+          <t>https://documents.un.org/doc/undoc/gen/n94/507/64/pdf/n9450764.pdf</t>
         </is>
       </c>
       <c r="R90" s="18" t="inlineStr">
@@ -10735,10 +10839,14 @@
           <t>Ukraine gave up its nuclear weapons for assurances Russia later broke.</t>
         </is>
       </c>
-      <c r="S90" s="18" t="n"/>
+      <c r="S90" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="T90" s="18" t="inlineStr">
         <is>
-          <t>UN viewers are JavaScript; open to confirm.</t>
+          <t>UN viewers are JavaScript; open to confirm. 2026-10-21: link moved from the docs.un.org viewer to the UN PDF, read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
         </is>
       </c>
     </row>
@@ -10823,8 +10931,16 @@
           <t>The agreement Russia now says NATO broke.</t>
         </is>
       </c>
-      <c r="S91" s="18" t="n"/>
-      <c r="T91" s="18" t="inlineStr"/>
+      <c r="S91" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T91" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
@@ -10907,8 +11023,16 @@
           <t>Putin's break with the West, years before Ukraine.</t>
         </is>
       </c>
-      <c r="S92" s="18" t="n"/>
-      <c r="T92" s="18" t="inlineStr"/>
+      <c r="S92" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T92" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
@@ -10991,8 +11115,16 @@
           <t>The annexation of Crimea.</t>
         </is>
       </c>
-      <c r="S93" s="18" t="n"/>
-      <c r="T93" s="18" t="inlineStr"/>
+      <c r="S93" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T93" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
@@ -11075,8 +11207,16 @@
           <t>The announcement of the full invasion of Ukraine.</t>
         </is>
       </c>
-      <c r="S94" s="18" t="n"/>
-      <c r="T94" s="18" t="inlineStr"/>
+      <c r="S94" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T94" s="18" t="inlineStr">
+        <is>
+          <t>Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
@@ -11337,6 +11477,1111 @@
       </c>
       <c r="S97" s="18" t="n"/>
       <c r="T97" s="18" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>sudan</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>31 March</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>2005-03-31</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>UN Security Council Resolution 1593</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="K98" s="1" t="inlineStr">
+        <is>
+          <t>United Nations Official Document System</t>
+        </is>
+      </c>
+      <c r="L98" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N98" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O98" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P98" s="1" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q98" s="1" t="inlineStr">
+        <is>
+          <t>https://documents.un.org/doc/undoc/gen/n05/292/73/pdf/n0529273.pdf</t>
+        </is>
+      </c>
+      <c r="R98" s="1" t="inlineStr">
+        <is>
+          <t>The Council referred Darfur to the International Criminal Court; the Janjaweed it named are the forerunners of today's RSF.</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T98" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>sudan</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
+        <is>
+          <t>17 August</t>
+        </is>
+      </c>
+      <c r="E99" s="1" t="inlineStr">
+        <is>
+          <t>2019-08-17</t>
+        </is>
+      </c>
+      <c r="F99" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t>Constitutional Charter for the 2019 Transitional Period</t>
+        </is>
+      </c>
+      <c r="H99" s="1" t="inlineStr">
+        <is>
+          <t>Transitional Military Council and the Forces of Freedom and Change</t>
+        </is>
+      </c>
+      <c r="K99" s="1" t="inlineStr">
+        <is>
+          <t>Constitute Project</t>
+        </is>
+      </c>
+      <c r="L99" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N99" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O99" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P99" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q99" s="1" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Sudan_2019</t>
+        </is>
+      </c>
+      <c r="R99" s="1" t="inlineStr">
+        <is>
+          <t>The power-sharing deal after Bashir fell that put the army, the RSF and civilians in one transitional government.</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T99" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>sudan</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>28 October</t>
+        </is>
+      </c>
+      <c r="E100" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-28</t>
+        </is>
+      </c>
+      <c r="F100" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G100" s="1" t="inlineStr">
+        <is>
+          <t>Security Council Press Statement on Sudan (SC/14678)</t>
+        </is>
+      </c>
+      <c r="H100" s="1" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="K100" s="1" t="inlineStr">
+        <is>
+          <t>UN Meetings Coverage and Press Releases</t>
+        </is>
+      </c>
+      <c r="L100" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N100" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O100" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P100" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q100" s="1" t="inlineStr">
+        <is>
+          <t>https://press.un.org/en/2021/sc14678.doc.htm</t>
+        </is>
+      </c>
+      <c r="R100" s="1" t="inlineStr">
+        <is>
+          <t>The Council's response to the October 2021 military takeover that ended the civilian-led transition.</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T100" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>sudan</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr">
+        <is>
+          <t>8 December</t>
+        </is>
+      </c>
+      <c r="E101" s="1" t="inlineStr">
+        <is>
+          <t>2022-12-08</t>
+        </is>
+      </c>
+      <c r="F101" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G101" s="1" t="inlineStr">
+        <is>
+          <t>Security Council Press Statement on Sudan (SC/15132)</t>
+        </is>
+      </c>
+      <c r="H101" s="1" t="inlineStr">
+        <is>
+          <t>United Nations Security Council</t>
+        </is>
+      </c>
+      <c r="K101" s="1" t="inlineStr">
+        <is>
+          <t>UN Meetings Coverage and Press Releases</t>
+        </is>
+      </c>
+      <c r="L101" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N101" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O101" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P101" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q101" s="1" t="inlineStr">
+        <is>
+          <t>https://press.un.org/en/2022/sc15132.doc.htm</t>
+        </is>
+      </c>
+      <c r="R101" s="1" t="inlineStr">
+        <is>
+          <t>The Council welcomed the December 2022 framework agreement whose unsettled security reform set the army and RSF against each other.</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T101" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>venezuela</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t>15 December</t>
+        </is>
+      </c>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
+          <t>1999-12-15</t>
+        </is>
+      </c>
+      <c r="F102" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G102" s="1" t="inlineStr">
+        <is>
+          <t>Constitution of the Bolivarian Republic of Venezuela (1999, rev. 2009)</t>
+        </is>
+      </c>
+      <c r="H102" s="1" t="inlineStr">
+        <is>
+          <t>People of Venezuela (Constituent Assembly)</t>
+        </is>
+      </c>
+      <c r="K102" s="1" t="inlineStr">
+        <is>
+          <t>Constitute Project</t>
+        </is>
+      </c>
+      <c r="L102" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N102" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O102" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P102" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q102" s="1" t="inlineStr">
+        <is>
+          <t>https://www.constituteproject.org/constitution/Venezuela_2009</t>
+        </is>
+      </c>
+      <c r="R102" s="1" t="inlineStr">
+        <is>
+          <t>Chavez's constitution, the legal frame of the state Maduro inherited.</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T102" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>venezuela</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr">
+        <is>
+          <t>5 August</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t>2019-08-05</t>
+        </is>
+      </c>
+      <c r="F103" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G103" s="1" t="inlineStr">
+        <is>
+          <t>Executive Order 13884: Blocking Property of the Government of Venezuela</t>
+        </is>
+      </c>
+      <c r="H103" s="1" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="K103" s="1" t="inlineStr">
+        <is>
+          <t>Federal Register (GovInfo)</t>
+        </is>
+      </c>
+      <c r="L103" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N103" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O103" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P103" s="1" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q103" s="1" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/FR-2019-08-07/pdf/2019-17052.pdf</t>
+        </is>
+      </c>
+      <c r="R103" s="1" t="inlineStr">
+        <is>
+          <t>The United States froze all property of the Venezuelan government in its jurisdiction.</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T103" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>venezuela</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>30 July</t>
+        </is>
+      </c>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>Carter Center Statement on Venezuela Election</t>
+        </is>
+      </c>
+      <c r="H104" s="1" t="inlineStr">
+        <is>
+          <t>The Carter Center</t>
+        </is>
+      </c>
+      <c r="K104" s="1" t="inlineStr">
+        <is>
+          <t>The Carter Center</t>
+        </is>
+      </c>
+      <c r="L104" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N104" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O104" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P104" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q104" s="1" t="inlineStr">
+        <is>
+          <t>https://www.cartercenter.org/news/pr/2024/venezuela-073024.html</t>
+        </is>
+      </c>
+      <c r="R104" s="1" t="inlineStr">
+        <is>
+          <t>The invited observer said the 2024 presidential election cannot be considered democratic.</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T104" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>venezuela</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>3 January</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>Truth Social Posts of January 3, 2026</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="K105" s="1" t="inlineStr">
+        <is>
+          <t>The American Presidency Project</t>
+        </is>
+      </c>
+      <c r="L105" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N105" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O105" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P105" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q105" s="1" t="inlineStr">
+        <is>
+          <t>https://www.presidency.ucsb.edu/node/394200</t>
+        </is>
+      </c>
+      <c r="R105" s="1" t="inlineStr">
+        <is>
+          <t>The president's announcement that U.S. forces captured Maduro: the day the Venezuela clock starts.</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T105" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: found for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr">
+        <is>
+          <t>20 January</t>
+        </is>
+      </c>
+      <c r="E106" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="F106" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>Principled and pragmatic: Canada's path (address to the World Economic Forum)</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="inlineStr">
+        <is>
+          <t>Mark Carney</t>
+        </is>
+      </c>
+      <c r="K106" s="1" t="inlineStr">
+        <is>
+          <t>Prime Minister of Canada</t>
+        </is>
+      </c>
+      <c r="L106" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N106" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O106" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P106" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q106" s="1" t="inlineStr">
+        <is>
+          <t>https://www.pm.gc.ca/en/news/speeches/2026/01/20/principled-and-pragmatic-canadas-path-prime-minister-carney-addresses</t>
+        </is>
+      </c>
+      <c r="R106" s="1" t="inlineStr">
+        <is>
+          <t>Carney's Davos case that middle powers must act together against economic coercion by great powers.</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T106" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: added at the editor's request for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t>6 June</t>
+        </is>
+      </c>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t>2004-06-06</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G107" s="1" t="inlineStr">
+        <is>
+          <t>Cabinet Resolution Regarding the Disengagement Plan</t>
+        </is>
+      </c>
+      <c r="H107" s="1" t="inlineStr">
+        <is>
+          <t>Government of Israel</t>
+        </is>
+      </c>
+      <c r="K107" s="1" t="inlineStr">
+        <is>
+          <t>UN Peacemaker</t>
+        </is>
+      </c>
+      <c r="L107" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N107" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O107" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P107" s="1" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q107" s="1" t="inlineStr">
+        <is>
+          <t>https://peacemaker.un.org/sites/default/files/document/files/2024/05/israeloptcabinetresolutionregardingdisengagementplan2004.pdf</t>
+        </is>
+      </c>
+      <c r="R107" s="1" t="inlineStr">
+        <is>
+          <t>Israel's decision to withdraw its settlements and forces from Gaza, carried out in 2005.</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T107" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: added at the editor's request for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>19 September</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>2007-09-19</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t>Security Cabinet declares Gaza hostile territory</t>
+        </is>
+      </c>
+      <c r="H108" s="1" t="inlineStr">
+        <is>
+          <t>Israel Ministry of Foreign Affairs</t>
+        </is>
+      </c>
+      <c r="K108" s="1" t="inlineStr">
+        <is>
+          <t>UNISPAL (United Nations)</t>
+        </is>
+      </c>
+      <c r="L108" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N108" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O108" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P108" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q108" s="1" t="inlineStr">
+        <is>
+          <t>https://www.un.org/unispal/document/auto-insert-195603</t>
+        </is>
+      </c>
+      <c r="R108" s="1" t="inlineStr">
+        <is>
+          <t>After Hamas took control of Gaza, Israel declared it hostile territory and restricted fuel, electricity and movement.</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T108" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: added at the editor's request for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
+        <is>
+          <t>21 June</t>
+        </is>
+      </c>
+      <c r="E109" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="F109" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G109" s="1" t="inlineStr">
+        <is>
+          <t>Address to the Nation on United States Airstrikes on Iran</t>
+        </is>
+      </c>
+      <c r="H109" s="1" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="K109" s="1" t="inlineStr">
+        <is>
+          <t>Daily Compilation of Presidential Documents (GovInfo)</t>
+        </is>
+      </c>
+      <c r="L109" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N109" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O109" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P109" s="1" t="inlineStr">
+        <is>
+          <t>live-pdf</t>
+        </is>
+      </c>
+      <c r="Q109" s="1" t="inlineStr">
+        <is>
+          <t>https://www.govinfo.gov/content/pkg/DCPD-202500711/pdf/DCPD-202500711.pdf</t>
+        </is>
+      </c>
+      <c r="R109" s="1" t="inlineStr">
+        <is>
+          <t>The first American strikes on Iran's nuclear sites, eight months before the war this page counts.</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T109" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: added at the editor's request for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>28 February</t>
+        </is>
+      </c>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="inlineStr">
+        <is>
+          <t>Contemporary Challenges: Foreign Policy</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>Remarks Announcing Major Combat Operations in Iran in Palm Beach, Florida</t>
+        </is>
+      </c>
+      <c r="H110" s="1" t="inlineStr">
+        <is>
+          <t>Donald J. Trump</t>
+        </is>
+      </c>
+      <c r="K110" s="1" t="inlineStr">
+        <is>
+          <t>The American Presidency Project</t>
+        </is>
+      </c>
+      <c r="L110" s="1" t="inlineStr">
+        <is>
+          <t>America Abroad</t>
+        </is>
+      </c>
+      <c r="N110" s="1" t="inlineStr">
+        <is>
+          <t>Addition, post-1981</t>
+        </is>
+      </c>
+      <c r="O110" s="1" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+      <c r="P110" s="1" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="Q110" s="1" t="inlineStr">
+        <is>
+          <t>https://www.presidency.ucsb.edu/documents/remarks-announcing-major-combat-operations-iran-palm-beach-florida</t>
+        </is>
+      </c>
+      <c r="R110" s="1" t="inlineStr">
+        <is>
+          <t>The announcement of the war with Iran: the day this page counts from.</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T110" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-21: added at the editor's request for the live-conflict page; link fetched and read. Approved by the editor 2026-10-21 for the live-conflict pages (T-0099).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11425,479 +12670,479 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>title: telecommunications, fairness doctrine, patriot act, internet, computer, privacy, section 230, antitrust, sherman act, wiretap</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>china</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>title: china, chinese communist, taiwan, formosa, shanghai; row: Taiwan</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>russia</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>title: soviet, moscow, russia, kremlin</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>iran</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>title: iran, iranian, persian gulf</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>israel</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>title: israel, israeli, zionism, zionist; sub-genre: Israel-Palestine policy</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>lebanon</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>title: lebanon, lebanese, beirut</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>syria</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>title: syria, syrian</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>iraq</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>title: iraq, iraqi, kuwait, gulf war; listed ids: 2003-02-05-address-to-the-united-nations-security-council</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>canada</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>title: canada, canadian</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>nato</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>title: nato, north atlantic</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>argentina</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>title: argentina, argentine</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>australia</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>title: australia, australian</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>brazil</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>title: brazil, brazilian</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>title: france, french</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>title: germany, german, germans</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>india</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>title: india, indian subcontinent, indian ocean</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>indonesia</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t>title: indonesia, indonesian</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" s="1" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>title: italy, italian</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" s="1" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>japan</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>title: japan, japanese</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" s="1" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>mexico</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>title: mexico, mexican, mexicans</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" s="1" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>saudi-arabia</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr">
         <is>
           <t>title: saudi, saudi arabia</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>south-africa</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>title: south africa, south african, apartheid</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" s="1" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>south-korea</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>title: south korea, south korean, korea, korean; row: Korea</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" s="1" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>turkey</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>title: turkey, turkish, ottoman</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" s="1" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>uk</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>title: great britain, britain, british, england, united kingdom</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
